--- a/database/real_estate_brokers.xlsx
+++ b/database/real_estate_brokers.xlsx
@@ -17,8 +17,8 @@
     <sheet name="データ辞書" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全社一覧'!$A$1:$T$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'関東'!$A$1:$T$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全社一覧'!$A$1:$T$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'関東'!$A$1:$T$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'北海道・東北'!$A$1:$T$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'近畿'!$A$1:$T$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'中国・四国'!$A$1:$T$2</definedName>
@@ -177,8 +177,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_9e7587520fcb" displayName="T_9e7587520fcb" ref="A1:T21" headerRowCount="1">
-  <autoFilter ref="A1:T21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_9e7587520fcb" displayName="T_9e7587520fcb" ref="A1:T31" headerRowCount="1">
+  <autoFilter ref="A1:T31"/>
   <tableColumns count="20">
     <tableColumn id="1" name="会社ID"/>
     <tableColumn id="2" name="会社名"/>
@@ -206,8 +206,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_92ae89f64a96" displayName="T_92ae89f64a96" ref="A1:T12" headerRowCount="1">
-  <autoFilter ref="A1:T12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_92ae89f64a96" displayName="T_92ae89f64a96" ref="A1:T22" headerRowCount="1">
+  <autoFilter ref="A1:T22"/>
   <tableColumns count="20">
     <tableColumn id="1" name="会社ID"/>
     <tableColumn id="2" name="会社名"/>
@@ -668,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:T31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -798,32 +798,32 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>RE-0001</t>
+          <t>RE-0013</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>三井不動産リアルティ株式会社</t>
+          <t>株式会社穴吹ハウジングサービス</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>関東</t>
+          <t>中国・四国</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>香川県</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>東京都千代田区</t>
+          <t>香川県高松市</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>全国</t>
+          <t>中国・四国・関西・九州・関東ほか</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・事業用・賃貸管理・資産活用</t>
+          <t>マンション管理・土地売買・戸建賃貸・資産活用</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -848,32 +848,32 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://www.mf-realty.jp/</t>
+          <t>https://www.anabuki-housing.co.jp/</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>https://pro.mf-realty.jp/otherInquiry/input/</t>
+          <t>https://www.anabuki-housing.co.jp/contact/form/?contact_type_group_cd=f</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>https://pro.mf-realty.jp/</t>
+          <t>https://www.anabuki-housing.co.jp/service/for_asset-management/</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>0120-921-582</t>
+          <t>0800-500-5505</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>居住用仲介と投資・収益不動産の専門サービスを展開</t>
+          <t>管理・資産活用・不動産売買をグループネットワークで支援</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>https://pro.mf-realty.jp/ | https://pro.mf-realty.jp/otherInquiry/input/</t>
+          <t>https://www.anabuki-housing.co.jp/service/for_asset-management/ | https://www.anabuki-housing.co.jp/contact/form/?contact_type_group_cd=f</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -888,49 +888,49 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>投資用戸建てを含む物件種別は個別検索で追加確認可能</t>
+          <t>2026年1月にフォーム不具合告知があったため送信可否を定期確認</t>
         </is>
       </c>
     </row>
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>RE-0002</t>
+          <t>RE-0016</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>住友不動産ステップ株式会社</t>
+          <t>GLC株式会社</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>関東</t>
+          <t>九州・沖縄</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>東京都新宿区</t>
+          <t>福岡県福岡市博多区</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>全国</t>
+          <t>東京・福岡・熊本・沖縄</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・一棟マンション・アパート・ビル</t>
+          <t>一棟賃貸マンション・土地活用・賃貸管理</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -950,32 +950,32 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://www.stepon.co.jp/</t>
+          <t>https://goodlife-c.jp/</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>https://www.stepon.co.jp/contact/</t>
+          <t>https://www.goodlife-c.jp/contact/investment/</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>https://www.stepon.co.jp/pro/</t>
+          <t>https://goodlife-c.jp/sales/category/fukuoka/</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>0120-566-742</t>
+          <t>092-471-4123</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>全国ネットワークで居住用・投資用不動産を仲介</t>
+          <t>一棟賃貸マンションの開発・運用・売却を一体支援</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>https://www.stepon.co.jp/pro/area_13/list_13_115/cs_25_06/ | https://www.stepon.co.jp/</t>
+          <t>https://goodlife-c.jp/index.php | https://www.goodlife-c.jp/contact/investment/ | https://goodlife-c.jp/sales/category/fukuoka/</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -995,39 +995,39 @@
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>問い合わせURLは総合窓口。物件ページにも資料請求フォームあり</t>
+          <t>戸建て仲介ではなく収益マンション特化として分類</t>
         </is>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>RE-0003</t>
+          <t>RE-0015</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>東急リバブル株式会社</t>
+          <t>株式会社三好不動産</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>関東</t>
+          <t>九州・沖縄</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>東京都渋谷区</t>
+          <t>福岡県福岡市中央区</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>首都圏・札幌・仙台・名古屋・関西・福岡ほか</t>
+          <t>福岡中心・首都圏</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・一棟収益・事業用・賃貸</t>
+          <t>一棟賃貸・分譲マンション・土地・賃貸管理・相続</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1052,32 +1052,32 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://www.livable.co.jp/</t>
+          <t>https://www.miyoshi.co.jp/</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>https://www.livable.co.jp/branch/toushi-support/</t>
+          <t>https://www.miyoshi.co.jp/contact/</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>https://www.livable.co.jp/fudosan-toushi-baikyaku/</t>
+          <t>https://www.miyoshi.co.jp/company/bases/</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0120-992-151</t>
+          <t>0120-78-1000</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>投資サポートセンターと全国店舗網を持つ</t>
+          <t>福岡で一棟・分譲マンション・戸建ての資産管理窓口を展開</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>https://www.livable.co.jp/branch/toushi-support/ | https://www.livable.co.jp/fudosan-toushi-baikyaku/</t>
+          <t>https://www.miyoshi.co.jp/company/bases/ | https://www.miyoshi.co.jp/enterprises/management/rental/rent_house/</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -1097,39 +1097,39 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>投資用不動産専用窓口あり</t>
+          <t>投資物件の売買メニューは部署別に追加調査</t>
         </is>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>RE-0004</t>
+          <t>RE-0017</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>野村不動産ソリューションズ株式会社</t>
+          <t>株式会社ハウスドゥ・ジャパン</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>関東</t>
+          <t>全国</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>京都府</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>東京都新宿区</t>
+          <t>京都府京都市中京区</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>首都圏・関西・名古屋ほか</t>
+          <t>全国</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・一棟マンション・アパート・事業用</t>
+          <t>マンション・土地・事業用・買取・リースバック</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -1154,17 +1154,17 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>https://www.nomura-solutions.co.jp/</t>
+          <t>https://www.housedo.com/</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>https://www.nomu.com/pro/contact/</t>
+          <t>https://www.housedo.com/contact/</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>https://www.nomu.com/pro/house/</t>
+          <t>https://www.housedo.com/house/</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ノムコム・プロで投資用戸建て・収益物件を掲載</t>
+          <t>全国店舗網と戸建て売買・買取サービス</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>https://www.nomu.com/pro/house/area/1311/ | https://www.nomu.com/pro/contents/knowhow/20240919.html</t>
+          <t>https://www.housedo.com/</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>一部確認</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>問い合わせ先は物件・担当センターごとに異なる</t>
+          <t>収益不動産の取扱は店舗単位で追加確認</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>RE-0006</t>
+          <t>RE-0014</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>株式会社オープンハウス</t>
+          <t>株式会社大京穴吹不動産</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>関東</t>
+          <t>全国</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>東京・神奈川・埼玉・千葉・愛知・大阪・兵庫・福岡ほか</t>
+          <t>全国主要都市</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>新築戸建て・土地・マンション・国内外投資</t>
+          <t>マンション・土地・一棟レジデンス・事業用・賃貸管理</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1358,32 +1358,32 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://oh.openhouse-group.com/</t>
+          <t>https://www.daikyo-anabuki.co.jp/</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>https://oh.openhouse-group.com/contact/</t>
+          <t>https://www.daikyo-anabuki.co.jp/contact/</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>https://oh.openhouse-group.com/s-kodate/</t>
+          <t>https://www.daikyo-anabuki.co.jp/sumai/invesment/</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>03-6213-0775</t>
+          <t>0120-988-264</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>都市部の戸建て供給とグループの不動産投資事業</t>
+          <t>全国店舗網と売買・賃貸・投資事業用窓口を持つ</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>https://oh.openhouse-group.com/company/about/ | https://oh.openhouse-group.com/s-kodate/saitama/ | https://wm.openhouse-group.com/</t>
+          <t>https://www.daikyo-anabuki.co.jp/contact/ | https://www.daikyo-anabuki.co.jp/company/</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>確認済み</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1403,44 +1403,44 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>国内収益物件の一般顧客向け窓口はグループ各社も確認</t>
+          <t>法人向け投資・事業用窓口は専用問い合わせ先</t>
         </is>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RE-0007</t>
+          <t>RE-0012</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>株式会社オープンハウス・リアルエステート</t>
+          <t>株式会社常口アトム</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>関東</t>
+          <t>北海道・東北</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>東京都千代田区</t>
+          <t>北海道札幌市中央区</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>首都圏・関西・名古屋</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>一棟マンション・アパート・ビル・土地</t>
+          <t>マンション・土地・賃貸管理・リフォーム</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1460,32 +1460,32 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://ohre.openhouse-group.com/</t>
+          <t>https://www.jogjog.com/</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>https://ohre.openhouse-group.com/</t>
+          <t>https://www.jogjog.com/inquiry/</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>https://shueki.ohd.openhouse-group.com/</t>
+          <t>https://www.jogjog.com/kikaku/investment/</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>03-6854-7452</t>
+          <t>011-272-0059</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>収益不動産の仕入れ・再生・売買に対応</t>
+          <t>北海道の総合不動産会社で投資相談窓口を持つ</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>https://ohre.openhouse-group.com/ | https://shueki.ohd.openhouse-group.com/</t>
+          <t>https://www.jogjog.com/kikaku/investment/ | https://www.jogjog.com/inquiry/</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>一部確認</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1505,39 +1505,39 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>戸建ての直接取扱は追加確認</t>
+          <t>売買戸建ての具体的掲載URLは追加確認</t>
         </is>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>RE-0008</t>
+          <t>RE-0011</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>株式会社ランドネット</t>
+          <t>株式会社永大ハウス工業</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>関東</t>
+          <t>北海道・東北</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>宮城県</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>東京都豊島区</t>
+          <t>宮城県仙台市若林区</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>東京・横浜・大阪・福岡ほか</t>
+          <t>仙台市・宮城県全域</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>中古マンション・賃貸管理・買取・リフォーム</t>
+          <t>中古マンション・土地・法人向け不動産</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1562,32 +1562,32 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://landnet.co.jp/</t>
+          <t>https://eidaihouse.com/</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>https://landnet.co.jp/contact/</t>
+          <t>https://eidaihouse.com/baikyaku</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>https://landnet.co.jp/housing-search/</t>
+          <t>https://eidaihouse.com/search?bk_sbt_kbn%5B0%5D=14</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0120-012-461</t>
+          <t>0120-18-4646</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>投資用中古マンションと居住用不動産をワンストップで扱う</t>
+          <t>宮城県に密着し戸建てから投資物件まで対応</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>https://landnet.co.jp/ | https://landnet.co.jp/contact/ | https://landnet.co.jp/housing-search/kanagawa/yamato-shi</t>
+          <t>https://eidaihouse.com/ | https://eidaihouse.com/search?bk_sbt_kbn%5B0%5D=14 | https://eidaihouse.com/baikyaku-business</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1607,44 +1607,44 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>戸建て掲載状況はエリアにより異なる</t>
+          <t>宮城県の地域密着候補として優先</t>
         </is>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>RE-0009</t>
+          <t>RE-0010</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>武蔵コーポレーション株式会社</t>
+          <t>株式会社福屋不動産販売</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>関東</t>
+          <t>近畿</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>埼玉県さいたま市大宮区</t>
+          <t>大阪府大阪市北区</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>関東中心</t>
+          <t>関西・首都圏・福岡</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>一棟アパート・マンション・ビル・賃貸管理</t>
+          <t>マンション・土地・事業用</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1664,32 +1664,32 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://www.musashi-corporation.com/</t>
+          <t>https://www.fukuya-k.co.jp/</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>https://www.musashi-corporation.com/qa/investment_consultation.php</t>
+          <t>https://www.fukuya-k.co.jp/contact</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>https://www.musashi-corporation.com/sell-feature/</t>
+          <t>https://www.fukuya-k.co.jp/kansai/investment/</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>048-788-5636</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>収益不動産の売買・管理・出口戦略に特化</t>
+          <t>戸建てと投資・収益用物件の双方を地域店舗で扱う</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>https://www.musashi-corporation.com/sell-feature/ | https://www.musashi-corporation.com/qa/investment_consultation.php</t>
+          <t>https://www.fukuya-k.co.jp/shutoken/investment/tokyo/nerima-ku | https://www.fukuya-k.co.jp/kansai/ikkodate/hyogo/station/kyoguchi_6613050</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1709,44 +1709,44 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>居住用戸建て仲介は対象外として整理</t>
+          <t>問い合わせ先は取扱店舗選択式</t>
         </is>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>RE-0010</t>
+          <t>RE-0009</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>株式会社福屋不動産販売</t>
+          <t>武蔵コーポレーション株式会社</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>近畿</t>
+          <t>関東</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>大阪府大阪市北区</t>
+          <t>埼玉県さいたま市大宮区</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>関西・首都圏・福岡</t>
+          <t>関東中心</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・事業用</t>
+          <t>一棟アパート・マンション・ビル・賃貸管理</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1766,32 +1766,32 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://www.fukuya-k.co.jp/</t>
+          <t>https://www.musashi-corporation.com/</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>https://www.fukuya-k.co.jp/contact</t>
+          <t>https://www.musashi-corporation.com/qa/investment_consultation.php</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>https://www.fukuya-k.co.jp/kansai/investment/</t>
+          <t>https://www.musashi-corporation.com/sell-feature/</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>048-788-5636</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>戸建てと投資・収益用物件の双方を地域店舗で扱う</t>
+          <t>収益不動産の売買・管理・出口戦略に特化</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>https://www.fukuya-k.co.jp/shutoken/investment/tokyo/nerima-ku | https://www.fukuya-k.co.jp/kansai/ikkodate/hyogo/station/kyoguchi_6613050</t>
+          <t>https://www.musashi-corporation.com/sell-feature/ | https://www.musashi-corporation.com/qa/investment_consultation.php</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1811,39 +1811,39 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>問い合わせ先は取扱店舗選択式</t>
+          <t>居住用戸建て仲介は対象外として整理</t>
         </is>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>RE-0011</t>
+          <t>RE-0019</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>株式会社永大ハウス工業</t>
+          <t>みずほ不動産販売株式会社</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>北海道・東北</t>
+          <t>関東</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>宮城県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>宮城県仙台市若林区</t>
+          <t>東京都中央区</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>仙台市・宮城県全域</t>
+          <t>首都圏・北海道・東北・中部・関西・中国・九州</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>中古マンション・土地・法人向け不動産</t>
+          <t>マンション・土地・事業用・相続・資産活用</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1868,32 +1868,32 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://eidaihouse.com/</t>
+          <t>https://www.mizuho-re.co.jp/</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>https://eidaihouse.com/baikyaku</t>
+          <t>https://www.mizuho-re.co.jp/contact/</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>https://eidaihouse.com/search?bk_sbt_kbn%5B0%5D=14</t>
+          <t>https://www.mizuho-re.co.jp/buy/investment/</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0120-18-4646</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>宮城県に密着し戸建てから投資物件まで対応</t>
+          <t>全国拠点と金融グループ連携による不動産仲介</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>https://eidaihouse.com/ | https://eidaihouse.com/search?bk_sbt_kbn%5B0%5D=14 | https://eidaihouse.com/baikyaku-business</t>
+          <t>https://www.mizuho-re.co.jp/</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1903,109 +1903,109 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>一部確認</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>宮城県の地域密着候補として優先</t>
+          <t>投資用サービスURLは定期リンク確認が必要</t>
         </is>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>RE-0012</t>
+          <t>RE-MLIT-13-00000114</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>株式会社常口アトム</t>
+          <t>レイモンド不動産 株式会社</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>北海道・東北</t>
+          <t>関東</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>北海道札幌市中央区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・賃貸管理・リフォーム</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>https://www.jogjog.com/</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>https://www.jogjog.com/inquiry/</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>https://www.jogjog.com/kikaku/investment/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>011-272-0059</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>北海道の総合不動産会社で投資相談窓口を持つ</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>https://www.jogjog.com/kikaku/investment/ | https://www.jogjog.com/inquiry/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -2015,39 +2015,39 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>売買戸建ての具体的掲載URLは追加確認</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000114号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>RE-0013</t>
+          <t>RE-0001</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>株式会社穴吹ハウジングサービス</t>
+          <t>三井不動産リアルティ株式会社</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>中国・四国</t>
+          <t>関東</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>香川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>香川県高松市</t>
+          <t>東京都千代田区</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>中国・四国・関西・九州・関東ほか</t>
+          <t>全国</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>マンション管理・土地売買・戸建賃貸・資産活用</t>
+          <t>マンション・土地・事業用・賃貸管理・資産活用</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2072,32 +2072,32 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://www.anabuki-housing.co.jp/</t>
+          <t>https://www.mf-realty.jp/</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>https://www.anabuki-housing.co.jp/contact/form/?contact_type_group_cd=f</t>
+          <t>https://pro.mf-realty.jp/otherInquiry/input/</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>https://www.anabuki-housing.co.jp/service/for_asset-management/</t>
+          <t>https://pro.mf-realty.jp/</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0800-500-5505</t>
+          <t>0120-921-582</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>管理・資産活用・不動産売買をグループネットワークで支援</t>
+          <t>居住用仲介と投資・収益不動産の専門サービスを展開</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>https://www.anabuki-housing.co.jp/service/for_asset-management/ | https://www.anabuki-housing.co.jp/contact/form/?contact_type_group_cd=f</t>
+          <t>https://pro.mf-realty.jp/ | https://pro.mf-realty.jp/otherInquiry/input/</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2112,29 +2112,29 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2026年1月にフォーム不具合告知があったため送信可否を定期確認</t>
+          <t>投資用戸建てを含む物件種別は個別検索で追加確認可能</t>
         </is>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>RE-0014</t>
+          <t>RE-0018</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>株式会社大京穴吹不動産</t>
+          <t>三菱UFJ不動産販売株式会社</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>全国</t>
+          <t>関東</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>東京都渋谷区</t>
+          <t>東京都千代田区</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>全国主要都市</t>
+          <t>首都圏・名古屋・関西</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・一棟レジデンス・事業用・賃貸管理</t>
+          <t>マンション・土地・投資事業用・相続</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2174,32 +2174,32 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>https://www.daikyo-anabuki.co.jp/</t>
+          <t>https://www.sumai1.com/</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>https://www.daikyo-anabuki.co.jp/contact/</t>
+          <t>https://www.sumai1.com/contact/</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>https://www.daikyo-anabuki.co.jp/sumai/invesment/</t>
+          <t>https://www.sumai1.com/buyers/investment/</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0120-988-264</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>全国店舗網と売買・賃貸・投資事業用窓口を持つ</t>
+          <t>金融グループ系の仲介・資産承継・投資用不動産対応</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>https://www.daikyo-anabuki.co.jp/contact/ | https://www.daikyo-anabuki.co.jp/company/</t>
+          <t>https://www.sumai1.com/</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2209,49 +2209,49 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>一部確認</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>法人向け投資・事業用窓口は専用問い合わせ先</t>
+          <t>サービスURLと問い合わせURLの定期リンク確認が必要</t>
         </is>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>RE-0015</t>
+          <t>RE-0002</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>株式会社三好不動産</t>
+          <t>住友不動産ステップ株式会社</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>九州・沖縄</t>
+          <t>関東</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>福岡県福岡市中央区</t>
+          <t>東京都新宿区</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>福岡中心・首都圏</t>
+          <t>全国</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>一棟賃貸・分譲マンション・土地・賃貸管理・相続</t>
+          <t>マンション・土地・一棟マンション・アパート・ビル</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://www.miyoshi.co.jp/</t>
+          <t>https://www.stepon.co.jp/</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>https://www.miyoshi.co.jp/contact/</t>
+          <t>https://www.stepon.co.jp/contact/</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>https://www.miyoshi.co.jp/company/bases/</t>
+          <t>https://www.stepon.co.jp/pro/</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0120-78-1000</t>
+          <t>0120-566-742</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>福岡で一棟・分譲マンション・戸建ての資産管理窓口を展開</t>
+          <t>全国ネットワークで居住用・投資用不動産を仲介</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>https://www.miyoshi.co.jp/company/bases/ | https://www.miyoshi.co.jp/enterprises/management/rental/rent_house/</t>
+          <t>https://www.stepon.co.jp/pro/area_13/list_13_115/cs_25_06/ | https://www.stepon.co.jp/</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2321,99 +2321,99 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>投資物件の売買メニューは部署別に追加調査</t>
+          <t>問い合わせURLは総合窓口。物件ページにも資料請求フォームあり</t>
         </is>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>RE-0016</t>
+          <t>RE-MLIT-13-00000212</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>GLC株式会社</t>
+          <t>日本不動産 株式会社</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>九州・沖縄</t>
+          <t>関東</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>福岡県福岡市博多区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>東京・福岡・熊本・沖縄</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>一棟賃貸マンション・土地活用・賃貸管理</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>https://goodlife-c.jp/</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>https://www.goodlife-c.jp/contact/investment/</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>https://goodlife-c.jp/sales/category/fukuoka/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>092-471-4123</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>一棟賃貸マンションの開発・運用・売却を一体支援</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>https://goodlife-c.jp/index.php | https://www.goodlife-c.jp/contact/investment/ | https://goodlife-c.jp/sales/category/fukuoka/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2423,44 +2423,44 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>戸建て仲介ではなく収益マンション特化として分類</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000212号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>RE-0017</t>
+          <t>RE-MLIT-13-00000170</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>株式会社ハウスドゥ・ジャパン</t>
+          <t>有限会社 マルミ商事</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>全国</t>
+          <t>関東</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>京都府</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>京都府京都市中京区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>全国</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2470,27 +2470,27 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・事業用・買取・リースバック</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>https://www.housedo.com/</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>https://www.housedo.com/contact/</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>https://www.housedo.com/house/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2500,44 +2500,44 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>全国店舗網と戸建て売買・買取サービス</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>https://www.housedo.com/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>収益不動産の取扱は店舗単位で追加確認</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000170号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>RE-0018</t>
+          <t>RE-0003</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>三菱UFJ不動産販売株式会社</t>
+          <t>東急リバブル株式会社</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>東京都千代田区</t>
+          <t>東京都渋谷区</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>首都圏・名古屋・関西</t>
+          <t>首都圏・札幌・仙台・名古屋・関西・福岡ほか</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・投資事業用・相続</t>
+          <t>マンション・土地・一棟収益・事業用・賃貸</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2582,32 +2582,32 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>https://www.sumai1.com/</t>
+          <t>https://www.livable.co.jp/</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>https://www.sumai1.com/contact/</t>
+          <t>https://www.livable.co.jp/branch/toushi-support/</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>https://www.sumai1.com/buyers/investment/</t>
+          <t>https://www.livable.co.jp/fudosan-toushi-baikyaku/</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>0120-992-151</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>金融グループ系の仲介・資産承継・投資用不動産対応</t>
+          <t>投資サポートセンターと全国店舗網を持つ</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>https://www.sumai1.com/</t>
+          <t>https://www.livable.co.jp/branch/toushi-support/ | https://www.livable.co.jp/fudosan-toushi-baikyaku/</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2617,29 +2617,29 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>確認済み</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>サービスURLと問い合わせURLの定期リンク確認が必要</t>
+          <t>投資用不動産専用窓口あり</t>
         </is>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>RE-0019</t>
+          <t>RE-MLIT-13-00000044</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>みずほ不動産販売株式会社</t>
+          <t>栗城建設興業 株式会社</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2654,47 +2654,47 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>東京都中央区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>首都圏・北海道・東北・中部・関西・中国・九州</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・事業用・相続・資産活用</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mizuho-re.co.jp/</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mizuho-re.co.jp/contact/</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mizuho-re.co.jp/buy/investment/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2704,139 +2704,1159 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>全国拠点と金融グループ連携による不動産仲介</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>https://www.mizuho-re.co.jp/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>投資用サービスURLは定期リンク確認が必要</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000044号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>RE-MLIT-13-00000164</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>株式会社 なかやま不動産</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 東京都; 免許番号: 第000164号; 自動追加日: 2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-13-00000098</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>株式会社 三和不動産鑑定事務所</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 東京都; 免許番号: 第000098号; 自動追加日: 2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-13-00000001</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>株式会社 三富不動産</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 東京都; 免許番号: 第000001号; 自動追加日: 2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-13-00000093</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>株式会社 伊藤商会</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 東京都; 免許番号: 第000093号; 自動追加日: 2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-13-00000060</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>株式会社 長岡建設</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 東京都; 免許番号: 第000060号; 自動追加日: 2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>RE-0020</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>株式会社GA technologies（RENOSY）</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>関東</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>東京都</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>東京都港区</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>全国オンライン中心</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>投資用マンション・賃貸管理・売却</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>https://www.renosy.com/</t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr">
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>https://www.renosy.com/contact</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
+      <c r="M26" s="3" t="inlineStr">
         <is>
           <t>https://www.renosy.com/asset</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>オンラインを中心とした不動産投資サービス</t>
         </is>
       </c>
-      <c r="P21" s="3" t="inlineStr">
+      <c r="P26" s="3" t="inlineStr">
         <is>
           <t>https://www.renosy.com/</t>
         </is>
       </c>
-      <c r="Q21" s="2" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="R21" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>一部確認</t>
         </is>
       </c>
-      <c r="S21" s="2" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="T21" s="2" t="inlineStr">
+      <c r="T26" s="2" t="inlineStr">
         <is>
           <t>戸建て仲介ではなく区分マンション投資中心</t>
         </is>
       </c>
     </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>RE-0006</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>株式会社オープンハウス</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>東京都渋谷区</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>東京・神奈川・埼玉・千葉・愛知・大阪・兵庫・福岡ほか</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>新築戸建て・土地・マンション・国内外投資</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>https://oh.openhouse-group.com/</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>https://oh.openhouse-group.com/contact/</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>https://oh.openhouse-group.com/s-kodate/</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>03-6213-0775</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>都市部の戸建て供給とグループの不動産投資事業</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>https://oh.openhouse-group.com/company/about/ | https://oh.openhouse-group.com/s-kodate/saitama/ | https://wm.openhouse-group.com/</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>国内収益物件の一般顧客向け窓口はグループ各社も確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>RE-0007</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>株式会社オープンハウス・リアルエステート</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>東京都千代田区</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>首都圏・関西・名古屋</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>一棟マンション・アパート・ビル・土地</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>https://ohre.openhouse-group.com/</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>https://ohre.openhouse-group.com/</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>https://shueki.ohd.openhouse-group.com/</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>03-6854-7452</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>収益不動産の仕入れ・再生・売買に対応</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>https://ohre.openhouse-group.com/ | https://shueki.ohd.openhouse-group.com/</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>確認済み</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>戸建ての直接取扱は追加確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>RE-0008</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ランドネット</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>東京都豊島区</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>東京・横浜・大阪・福岡ほか</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>中古マンション・賃貸管理・買取・リフォーム</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>https://landnet.co.jp/</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>https://landnet.co.jp/contact/</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>https://landnet.co.jp/housing-search/</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>0120-012-461</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>投資用中古マンションと居住用不動産をワンストップで扱う</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>https://landnet.co.jp/ | https://landnet.co.jp/contact/ | https://landnet.co.jp/housing-search/kanagawa/yamato-shi</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>確認済み</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>戸建て掲載状況はエリアにより異なる</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-13-00000218</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>西武建設 株式会社</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 東京都; 免許番号: 第000218号; 自動追加日: 2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>RE-0004</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>野村不動産ソリューションズ株式会社</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>東京都新宿区</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>首都圏・関西・名古屋ほか</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>マンション・土地・一棟マンション・アパート・事業用</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nomura-solutions.co.jp/</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nomu.com/pro/contact/</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nomu.com/pro/house/</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>ノムコム・プロで投資用戸建て・収益物件を掲載</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nomu.com/pro/house/area/1311/ | https://www.nomu.com/pro/contents/knowhow/20240919.html</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>確認済み</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>問い合わせ先は物件・担当センターごとに異なる</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T21"/>
+  <autoFilter ref="A1:T31"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -2882,46 +3902,56 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId90"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId81"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId91"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2932,7 +3962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:T22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3062,12 +4092,12 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>RE-0001</t>
+          <t>RE-0009</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>三井不動産リアルティ株式会社</t>
+          <t>武蔵コーポレーション株式会社</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -3077,22 +4107,22 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>東京都千代田区</t>
+          <t>埼玉県さいたま市大宮区</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>全国</t>
+          <t>関東中心</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -3102,7 +4132,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・事業用・賃貸管理・資産活用</t>
+          <t>一棟アパート・マンション・ビル・賃貸管理</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -3112,32 +4142,32 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://www.mf-realty.jp/</t>
+          <t>https://www.musashi-corporation.com/</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>https://pro.mf-realty.jp/otherInquiry/input/</t>
+          <t>https://www.musashi-corporation.com/qa/investment_consultation.php</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>https://pro.mf-realty.jp/</t>
+          <t>https://www.musashi-corporation.com/sell-feature/</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>0120-921-582</t>
+          <t>048-788-5636</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>居住用仲介と投資・収益不動産の専門サービスを展開</t>
+          <t>収益不動産の売買・管理・出口戦略に特化</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>https://pro.mf-realty.jp/ | https://pro.mf-realty.jp/otherInquiry/input/</t>
+          <t>https://www.musashi-corporation.com/sell-feature/ | https://www.musashi-corporation.com/qa/investment_consultation.php</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -3157,19 +4187,19 @@
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>投資用戸建てを含む物件種別は個別検索で追加確認可能</t>
+          <t>居住用戸建て仲介は対象外として整理</t>
         </is>
       </c>
     </row>
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>RE-0002</t>
+          <t>RE-0019</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>住友不動産ステップ株式会社</t>
+          <t>みずほ不動産販売株式会社</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -3184,12 +4214,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>東京都新宿区</t>
+          <t>東京都中央区</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>全国</t>
+          <t>首都圏・北海道・東北・中部・関西・中国・九州</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -3204,7 +4234,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・一棟マンション・アパート・ビル</t>
+          <t>マンション・土地・事業用・相続・資産活用</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -3214,32 +4244,32 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://www.stepon.co.jp/</t>
+          <t>https://www.mizuho-re.co.jp/</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>https://www.stepon.co.jp/contact/</t>
+          <t>https://www.mizuho-re.co.jp/contact/</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>https://www.stepon.co.jp/pro/</t>
+          <t>https://www.mizuho-re.co.jp/buy/investment/</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>0120-566-742</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>全国ネットワークで居住用・投資用不動産を仲介</t>
+          <t>全国拠点と金融グループ連携による不動産仲介</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>https://www.stepon.co.jp/pro/area_13/list_13_115/cs_25_06/ | https://www.stepon.co.jp/</t>
+          <t>https://www.mizuho-re.co.jp/</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -3249,29 +4279,29 @@
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>一部確認</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>問い合わせURLは総合窓口。物件ページにも資料請求フォームあり</t>
+          <t>投資用サービスURLは定期リンク確認が必要</t>
         </is>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>RE-0003</t>
+          <t>RE-MLIT-13-00000114</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>東急リバブル株式会社</t>
+          <t>レイモンド不動産 株式会社</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -3286,72 +4316,72 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>東京都渋谷区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>首都圏・札幌・仙台・名古屋・関西・福岡ほか</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・一棟収益・事業用・賃貸</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>https://www.livable.co.jp/</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>https://www.livable.co.jp/branch/toushi-support/</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>https://www.livable.co.jp/fudosan-toushi-baikyaku/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0120-992-151</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>投資サポートセンターと全国店舗網を持つ</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>https://www.livable.co.jp/branch/toushi-support/ | https://www.livable.co.jp/fudosan-toushi-baikyaku/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -3361,19 +4391,19 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>投資用不動産専用窓口あり</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000114号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>RE-0004</t>
+          <t>RE-0001</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>野村不動産ソリューションズ株式会社</t>
+          <t>三井不動産リアルティ株式会社</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -3388,12 +4418,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>東京都新宿区</t>
+          <t>東京都千代田区</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>首都圏・関西・名古屋ほか</t>
+          <t>全国</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3408,7 +4438,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・一棟マンション・アパート・事業用</t>
+          <t>マンション・土地・事業用・賃貸管理・資産活用</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3418,32 +4448,32 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>https://www.nomura-solutions.co.jp/</t>
+          <t>https://www.mf-realty.jp/</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>https://www.nomu.com/pro/contact/</t>
+          <t>https://pro.mf-realty.jp/otherInquiry/input/</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>https://www.nomu.com/pro/house/</t>
+          <t>https://pro.mf-realty.jp/</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>0120-921-582</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ノムコム・プロで投資用戸建て・収益物件を掲載</t>
+          <t>居住用仲介と投資・収益不動産の専門サービスを展開</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>https://www.nomu.com/pro/house/area/1311/ | https://www.nomu.com/pro/contents/knowhow/20240919.html</t>
+          <t>https://pro.mf-realty.jp/ | https://pro.mf-realty.jp/otherInquiry/input/</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3463,19 +4493,19 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>問い合わせ先は物件・担当センターごとに異なる</t>
+          <t>投資用戸建てを含む物件種別は個別検索で追加確認可能</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>RE-0006</t>
+          <t>RE-0018</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>株式会社オープンハウス</t>
+          <t>三菱UFJ不動産販売株式会社</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -3490,12 +4520,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>東京都渋谷区</t>
+          <t>東京都千代田区</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>東京・神奈川・埼玉・千葉・愛知・大阪・兵庫・福岡ほか</t>
+          <t>首都圏・名古屋・関西</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3510,7 +4540,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>新築戸建て・土地・マンション・国内外投資</t>
+          <t>マンション・土地・投資事業用・相続</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3520,32 +4550,32 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://oh.openhouse-group.com/</t>
+          <t>https://www.sumai1.com/</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>https://oh.openhouse-group.com/contact/</t>
+          <t>https://www.sumai1.com/contact/</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>https://oh.openhouse-group.com/s-kodate/</t>
+          <t>https://www.sumai1.com/buyers/investment/</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>03-6213-0775</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>都市部の戸建て供給とグループの不動産投資事業</t>
+          <t>金融グループ系の仲介・資産承継・投資用不動産対応</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>https://oh.openhouse-group.com/company/about/ | https://oh.openhouse-group.com/s-kodate/saitama/ | https://wm.openhouse-group.com/</t>
+          <t>https://www.sumai1.com/</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3560,24 +4590,24 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>国内収益物件の一般顧客向け窓口はグループ各社も確認</t>
+          <t>サービスURLと問い合わせURLの定期リンク確認が必要</t>
         </is>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>RE-0007</t>
+          <t>RE-0002</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>株式会社オープンハウス・リアルエステート</t>
+          <t>住友不動産ステップ株式会社</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -3592,17 +4622,17 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>東京都千代田区</t>
+          <t>東京都新宿区</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>首都圏・関西・名古屋</t>
+          <t>全国</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -3612,7 +4642,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>一棟マンション・アパート・ビル・土地</t>
+          <t>マンション・土地・一棟マンション・アパート・ビル</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3622,32 +4652,32 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://ohre.openhouse-group.com/</t>
+          <t>https://www.stepon.co.jp/</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>https://ohre.openhouse-group.com/</t>
+          <t>https://www.stepon.co.jp/contact/</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>https://shueki.ohd.openhouse-group.com/</t>
+          <t>https://www.stepon.co.jp/pro/</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>03-6854-7452</t>
+          <t>0120-566-742</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>収益不動産の仕入れ・再生・売買に対応</t>
+          <t>全国ネットワークで居住用・投資用不動産を仲介</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>https://ohre.openhouse-group.com/ | https://shueki.ohd.openhouse-group.com/</t>
+          <t>https://www.stepon.co.jp/pro/area_13/list_13_115/cs_25_06/ | https://www.stepon.co.jp/</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3667,19 +4697,19 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>戸建ての直接取扱は追加確認</t>
+          <t>問い合わせURLは総合窓口。物件ページにも資料請求フォームあり</t>
         </is>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RE-0008</t>
+          <t>RE-MLIT-13-00000212</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>株式会社ランドネット</t>
+          <t>日本不動産 株式会社</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -3694,72 +4724,72 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>東京都豊島区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>東京・横浜・大阪・福岡ほか</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>中古マンション・賃貸管理・買取・リフォーム</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>https://landnet.co.jp/</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>https://landnet.co.jp/contact/</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>https://landnet.co.jp/housing-search/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0120-012-461</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>投資用中古マンションと居住用不動産をワンストップで扱う</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>https://landnet.co.jp/ | https://landnet.co.jp/contact/ | https://landnet.co.jp/housing-search/kanagawa/yamato-shi</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -3769,19 +4799,19 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>戸建て掲載状況はエリアにより異なる</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000212号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>RE-0009</t>
+          <t>RE-MLIT-13-00000170</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>武蔵コーポレーション株式会社</t>
+          <t>有限会社 マルミ商事</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -3791,77 +4821,77 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>埼玉県さいたま市大宮区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>関東中心</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>一棟アパート・マンション・ビル・賃貸管理</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.musashi-corporation.com/</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.musashi-corporation.com/qa/investment_consultation.php</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.musashi-corporation.com/sell-feature/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>048-788-5636</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>収益不動産の売買・管理・出口戦略に特化</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>https://www.musashi-corporation.com/sell-feature/ | https://www.musashi-corporation.com/qa/investment_consultation.php</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -3871,19 +4901,19 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>居住用戸建て仲介は対象外として整理</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000170号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>RE-0018</t>
+          <t>RE-0003</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>三菱UFJ不動産販売株式会社</t>
+          <t>東急リバブル株式会社</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -3898,12 +4928,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>東京都千代田区</t>
+          <t>東京都渋谷区</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>首都圏・名古屋・関西</t>
+          <t>首都圏・札幌・仙台・名古屋・関西・福岡ほか</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3918,7 +4948,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・投資事業用・相続</t>
+          <t>マンション・土地・一棟収益・事業用・賃貸</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3928,32 +4958,32 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://www.sumai1.com/</t>
+          <t>https://www.livable.co.jp/</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>https://www.sumai1.com/contact/</t>
+          <t>https://www.livable.co.jp/branch/toushi-support/</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>https://www.sumai1.com/buyers/investment/</t>
+          <t>https://www.livable.co.jp/fudosan-toushi-baikyaku/</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>0120-992-151</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>金融グループ系の仲介・資産承継・投資用不動産対応</t>
+          <t>投資サポートセンターと全国店舗網を持つ</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>https://www.sumai1.com/</t>
+          <t>https://www.livable.co.jp/branch/toushi-support/ | https://www.livable.co.jp/fudosan-toushi-baikyaku/</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3963,29 +4993,29 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>確認済み</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>サービスURLと問い合わせURLの定期リンク確認が必要</t>
+          <t>投資用不動産専用窓口あり</t>
         </is>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>RE-0019</t>
+          <t>RE-MLIT-13-00000044</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>みずほ不動産販売株式会社</t>
+          <t>栗城建設興業 株式会社</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -4000,47 +5030,47 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>東京都中央区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>首都圏・北海道・東北・中部・関西・中国・九州</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・事業用・相続・資産活用</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mizuho-re.co.jp/</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mizuho-re.co.jp/contact/</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mizuho-re.co.jp/buy/investment/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4050,139 +5080,1159 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>全国拠点と金融グループ連携による不動産仲介</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>https://www.mizuho-re.co.jp/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>投資用サービスURLは定期リンク確認が必要</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000044号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>RE-MLIT-13-00000164</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>株式会社 なかやま不動産</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 東京都; 免許番号: 第000164号; 自動追加日: 2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-13-00000098</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>株式会社 三和不動産鑑定事務所</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 東京都; 免許番号: 第000098号; 自動追加日: 2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-13-00000001</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>株式会社 三富不動産</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 東京都; 免許番号: 第000001号; 自動追加日: 2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-13-00000093</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>株式会社 伊藤商会</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 東京都; 免許番号: 第000093号; 自動追加日: 2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-13-00000060</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>株式会社 長岡建設</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 東京都; 免許番号: 第000060号; 自動追加日: 2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>RE-0020</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>株式会社GA technologies（RENOSY）</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>関東</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>東京都</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>東京都港区</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>全国オンライン中心</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>投資用マンション・賃貸管理・売却</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>https://www.renosy.com/</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>https://www.renosy.com/contact</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t>https://www.renosy.com/asset</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>オンラインを中心とした不動産投資サービス</t>
         </is>
       </c>
-      <c r="P12" s="3" t="inlineStr">
+      <c r="P17" s="3" t="inlineStr">
         <is>
           <t>https://www.renosy.com/</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="R12" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>一部確認</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="T12" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
         <is>
           <t>戸建て仲介ではなく区分マンション投資中心</t>
         </is>
       </c>
     </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>RE-0006</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>株式会社オープンハウス</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>東京都渋谷区</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>東京・神奈川・埼玉・千葉・愛知・大阪・兵庫・福岡ほか</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>新築戸建て・土地・マンション・国内外投資</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>https://oh.openhouse-group.com/</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>https://oh.openhouse-group.com/contact/</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>https://oh.openhouse-group.com/s-kodate/</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>03-6213-0775</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>都市部の戸建て供給とグループの不動産投資事業</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>https://oh.openhouse-group.com/company/about/ | https://oh.openhouse-group.com/s-kodate/saitama/ | https://wm.openhouse-group.com/</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>国内収益物件の一般顧客向け窓口はグループ各社も確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>RE-0007</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>株式会社オープンハウス・リアルエステート</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>東京都千代田区</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>首都圏・関西・名古屋</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>一棟マンション・アパート・ビル・土地</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>https://ohre.openhouse-group.com/</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>https://ohre.openhouse-group.com/</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>https://shueki.ohd.openhouse-group.com/</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>03-6854-7452</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>収益不動産の仕入れ・再生・売買に対応</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>https://ohre.openhouse-group.com/ | https://shueki.ohd.openhouse-group.com/</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>確認済み</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>戸建ての直接取扱は追加確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>RE-0008</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ランドネット</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>東京都豊島区</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>東京・横浜・大阪・福岡ほか</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>中古マンション・賃貸管理・買取・リフォーム</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>https://landnet.co.jp/</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>https://landnet.co.jp/contact/</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>https://landnet.co.jp/housing-search/</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0120-012-461</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>投資用中古マンションと居住用不動産をワンストップで扱う</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>https://landnet.co.jp/ | https://landnet.co.jp/contact/ | https://landnet.co.jp/housing-search/kanagawa/yamato-shi</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>確認済み</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>戸建て掲載状況はエリアにより異なる</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-13-00000218</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>西武建設 株式会社</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 東京都; 免許番号: 第000218号; 自動追加日: 2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>RE-0004</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>野村不動産ソリューションズ株式会社</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>東京都新宿区</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>首都圏・関西・名古屋ほか</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>マンション・土地・一棟マンション・アパート・事業用</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nomura-solutions.co.jp/</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nomu.com/pro/contact/</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nomu.com/pro/house/</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>ノムコム・プロで投資用戸建て・収益物件を掲載</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nomu.com/pro/house/area/1311/ | https://www.nomu.com/pro/contents/knowhow/20240919.html</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>確認済み</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>問い合わせ先は物件・担当センターごとに異なる</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T12"/>
+  <autoFilter ref="A1:T22"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -4192,46 +6242,56 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId54"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId45"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId55"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4372,12 +6432,12 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>RE-0011</t>
+          <t>RE-0012</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>株式会社永大ハウス工業</t>
+          <t>株式会社常口アトム</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -4387,17 +6447,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>宮城県</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>宮城県仙台市若林区</t>
+          <t>北海道札幌市中央区</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>仙台市・宮城県全域</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -4412,7 +6472,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>中古マンション・土地・法人向け不動産</t>
+          <t>マンション・土地・賃貸管理・リフォーム</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -4422,32 +6482,32 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://eidaihouse.com/</t>
+          <t>https://www.jogjog.com/</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>https://eidaihouse.com/baikyaku</t>
+          <t>https://www.jogjog.com/inquiry/</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>https://eidaihouse.com/search?bk_sbt_kbn%5B0%5D=14</t>
+          <t>https://www.jogjog.com/kikaku/investment/</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>0120-18-4646</t>
+          <t>011-272-0059</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>宮城県に密着し戸建てから投資物件まで対応</t>
+          <t>北海道の総合不動産会社で投資相談窓口を持つ</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>https://eidaihouse.com/ | https://eidaihouse.com/search?bk_sbt_kbn%5B0%5D=14 | https://eidaihouse.com/baikyaku-business</t>
+          <t>https://www.jogjog.com/kikaku/investment/ | https://www.jogjog.com/inquiry/</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -4457,7 +6517,7 @@
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>一部確認</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
@@ -4467,19 +6527,19 @@
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>宮城県の地域密着候補として優先</t>
+          <t>売買戸建ての具体的掲載URLは追加確認</t>
         </is>
       </c>
     </row>
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>RE-0012</t>
+          <t>RE-0011</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>株式会社常口アトム</t>
+          <t>株式会社永大ハウス工業</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -4489,17 +6549,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>宮城県</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>北海道札幌市中央区</t>
+          <t>宮城県仙台市若林区</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>仙台市・宮城県全域</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -4514,7 +6574,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・賃貸管理・リフォーム</t>
+          <t>中古マンション・土地・法人向け不動産</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -4524,32 +6584,32 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://www.jogjog.com/</t>
+          <t>https://eidaihouse.com/</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>https://www.jogjog.com/inquiry/</t>
+          <t>https://eidaihouse.com/baikyaku</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>https://www.jogjog.com/kikaku/investment/</t>
+          <t>https://eidaihouse.com/search?bk_sbt_kbn%5B0%5D=14</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>011-272-0059</t>
+          <t>0120-18-4646</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>北海道の総合不動産会社で投資相談窓口を持つ</t>
+          <t>宮城県に密着し戸建てから投資物件まで対応</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>https://www.jogjog.com/kikaku/investment/ | https://www.jogjog.com/inquiry/</t>
+          <t>https://eidaihouse.com/ | https://eidaihouse.com/search?bk_sbt_kbn%5B0%5D=14 | https://eidaihouse.com/baikyaku-business</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -4559,7 +6619,7 @@
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>確認済み</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
@@ -4569,7 +6629,7 @@
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>売買戸建ての具体的掲載URLは追加確認</t>
+          <t>宮城県の地域密着候補として優先</t>
         </is>
       </c>
     </row>
@@ -5228,12 +7288,12 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>RE-0015</t>
+          <t>RE-0016</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>株式会社三好不動産</t>
+          <t>GLC株式会社</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -5248,17 +7308,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>福岡県福岡市中央区</t>
+          <t>福岡県福岡市博多区</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>福岡中心・首都圏</t>
+          <t>東京・福岡・熊本・沖縄</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -5268,7 +7328,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>一棟賃貸・分譲マンション・土地・賃貸管理・相続</t>
+          <t>一棟賃貸マンション・土地活用・賃貸管理</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -5278,32 +7338,32 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://www.miyoshi.co.jp/</t>
+          <t>https://goodlife-c.jp/</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>https://www.miyoshi.co.jp/contact/</t>
+          <t>https://www.goodlife-c.jp/contact/investment/</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>https://www.miyoshi.co.jp/company/bases/</t>
+          <t>https://goodlife-c.jp/sales/category/fukuoka/</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>0120-78-1000</t>
+          <t>092-471-4123</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>福岡で一棟・分譲マンション・戸建ての資産管理窓口を展開</t>
+          <t>一棟賃貸マンションの開発・運用・売却を一体支援</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>https://www.miyoshi.co.jp/company/bases/ | https://www.miyoshi.co.jp/enterprises/management/rental/rent_house/</t>
+          <t>https://goodlife-c.jp/index.php | https://www.goodlife-c.jp/contact/investment/ | https://goodlife-c.jp/sales/category/fukuoka/</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -5323,19 +7383,19 @@
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>投資物件の売買メニューは部署別に追加調査</t>
+          <t>戸建て仲介ではなく収益マンション特化として分類</t>
         </is>
       </c>
     </row>
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>RE-0016</t>
+          <t>RE-0015</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>GLC株式会社</t>
+          <t>株式会社三好不動産</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -5350,17 +7410,17 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>福岡県福岡市博多区</t>
+          <t>福岡県福岡市中央区</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>東京・福岡・熊本・沖縄</t>
+          <t>福岡中心・首都圏</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -5370,7 +7430,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>一棟賃貸マンション・土地活用・賃貸管理</t>
+          <t>一棟賃貸・分譲マンション・土地・賃貸管理・相続</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -5380,32 +7440,32 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://goodlife-c.jp/</t>
+          <t>https://www.miyoshi.co.jp/</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>https://www.goodlife-c.jp/contact/investment/</t>
+          <t>https://www.miyoshi.co.jp/contact/</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>https://goodlife-c.jp/sales/category/fukuoka/</t>
+          <t>https://www.miyoshi.co.jp/company/bases/</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>092-471-4123</t>
+          <t>0120-78-1000</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>一棟賃貸マンションの開発・運用・売却を一体支援</t>
+          <t>福岡で一棟・分譲マンション・戸建ての資産管理窓口を展開</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>https://goodlife-c.jp/index.php | https://www.goodlife-c.jp/contact/investment/ | https://goodlife-c.jp/sales/category/fukuoka/</t>
+          <t>https://www.miyoshi.co.jp/company/bases/ | https://www.miyoshi.co.jp/enterprises/management/rental/rent_house/</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -5425,7 +7485,7 @@
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>戸建て仲介ではなく収益マンション特化として分類</t>
+          <t>投資物件の売買メニューは部署別に追加調査</t>
         </is>
       </c>
     </row>
@@ -5584,12 +7644,12 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>RE-0005</t>
+          <t>RE-0017</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>株式会社センチュリー21・ジャパン</t>
+          <t>株式会社ハウスドゥ・ジャパン</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -5599,17 +7659,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>京都府</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>東京都港区</t>
+          <t>京都府京都市中京区</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>全国の加盟店</t>
+          <t>全国</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -5619,12 +7679,12 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・事業用・賃貸</t>
+          <t>マンション・土地・事業用・買取・リースバック</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -5634,17 +7694,17 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://www.century21.jp/</t>
+          <t>https://www.housedo.com/</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>https://www.century21.jp/contact</t>
+          <t>https://www.housedo.com/contact/</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>https://www.century21.jp/biz/</t>
+          <t>https://www.housedo.com/house/</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -5654,12 +7714,12 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>全国の独立加盟店ネットワーク。戸建て・事業投資用物件を検索可能</t>
+          <t>全国店舗網と戸建て売買・買取サービス</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>https://www.century21.jp/biz/kanagawa/14205/detail/159701-46167 | https://www.century21.jp/biz/chiba/12225/detail/161601-8706</t>
+          <t>https://www.housedo.com/</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -5669,29 +7729,29 @@
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>一部確認</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>実際の取扱範囲・免許・連絡先は加盟店単位で確認</t>
+          <t>収益不動産の取扱は店舗単位で追加確認</t>
         </is>
       </c>
     </row>
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>RE-0014</t>
+          <t>RE-0005</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>株式会社大京穴吹不動産</t>
+          <t>株式会社センチュリー21・ジャパン</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -5706,12 +7766,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>東京都渋谷区</t>
+          <t>東京都港区</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>全国主要都市</t>
+          <t>全国の加盟店</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -5726,7 +7786,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・一棟レジデンス・事業用・賃貸管理</t>
+          <t>マンション・土地・事業用・賃貸</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -5736,32 +7796,32 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://www.daikyo-anabuki.co.jp/</t>
+          <t>https://www.century21.jp/</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>https://www.daikyo-anabuki.co.jp/contact/</t>
+          <t>https://www.century21.jp/contact</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>https://www.daikyo-anabuki.co.jp/sumai/invesment/</t>
+          <t>https://www.century21.jp/biz/</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>0120-988-264</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>全国店舗網と売買・賃貸・投資事業用窓口を持つ</t>
+          <t>全国の独立加盟店ネットワーク。戸建て・事業投資用物件を検索可能</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>https://www.daikyo-anabuki.co.jp/contact/ | https://www.daikyo-anabuki.co.jp/company/</t>
+          <t>https://www.century21.jp/biz/kanagawa/14205/detail/159701-46167 | https://www.century21.jp/biz/chiba/12225/detail/161601-8706</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -5781,19 +7841,19 @@
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>法人向け投資・事業用窓口は専用問い合わせ先</t>
+          <t>実際の取扱範囲・免許・連絡先は加盟店単位で確認</t>
         </is>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>RE-0017</t>
+          <t>RE-0014</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>株式会社ハウスドゥ・ジャパン</t>
+          <t>株式会社大京穴吹不動産</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -5803,17 +7863,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>京都府</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>京都府京都市中京区</t>
+          <t>東京都渋谷区</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>全国</t>
+          <t>全国主要都市</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5823,12 +7883,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・事業用・買取・リースバック</t>
+          <t>マンション・土地・一棟レジデンス・事業用・賃貸管理</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5838,32 +7898,32 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://www.housedo.com/</t>
+          <t>https://www.daikyo-anabuki.co.jp/</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>https://www.housedo.com/contact/</t>
+          <t>https://www.daikyo-anabuki.co.jp/contact/</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>https://www.housedo.com/house/</t>
+          <t>https://www.daikyo-anabuki.co.jp/sumai/invesment/</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>0120-988-264</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>全国店舗網と戸建て売買・買取サービス</t>
+          <t>全国店舗網と売買・賃貸・投資事業用窓口を持つ</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>https://www.housedo.com/</t>
+          <t>https://www.daikyo-anabuki.co.jp/contact/ | https://www.daikyo-anabuki.co.jp/company/</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5873,17 +7933,17 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>確認済み</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>収益不動産の取扱は店舗単位で追加確認</t>
+          <t>法人向け投資・事業用窓口は専用問い合わせ先</t>
         </is>
       </c>
     </row>

--- a/database/real_estate_brokers.xlsx
+++ b/database/real_estate_brokers.xlsx
@@ -17,8 +17,8 @@
     <sheet name="データ辞書" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全社一覧'!$A$1:$T$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'関東'!$A$1:$T$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全社一覧'!$A$1:$T$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'関東'!$A$1:$T$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'北海道・東北'!$A$1:$T$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'近畿'!$A$1:$T$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'中国・四国'!$A$1:$T$2</definedName>
@@ -177,8 +177,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_9e7587520fcb" displayName="T_9e7587520fcb" ref="A1:T31" headerRowCount="1">
-  <autoFilter ref="A1:T31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_9e7587520fcb" displayName="T_9e7587520fcb" ref="A1:T41" headerRowCount="1">
+  <autoFilter ref="A1:T41"/>
   <tableColumns count="20">
     <tableColumn id="1" name="会社ID"/>
     <tableColumn id="2" name="会社名"/>
@@ -206,8 +206,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_92ae89f64a96" displayName="T_92ae89f64a96" ref="A1:T22" headerRowCount="1">
-  <autoFilter ref="A1:T22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_92ae89f64a96" displayName="T_92ae89f64a96" ref="A1:T32" headerRowCount="1">
+  <autoFilter ref="A1:T32"/>
   <tableColumns count="20">
     <tableColumn id="1" name="会社ID"/>
     <tableColumn id="2" name="会社名"/>
@@ -668,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T31"/>
+  <dimension ref="A1:T41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3855,8 +3855,1028 @@
         </is>
       </c>
     </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000181</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>大栄興業 株式会社</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000181号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000260</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>有限会社 協和商事</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000260号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000365</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>有限会社 小沢建設商事</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000365号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000162</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>有限会社 濱屋</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000162号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000071</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>東栄商事 株式会社</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000071号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="42" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000060</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>東横不動産 株式会社</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="42" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000013</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>株式会社 大谷商事</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000013号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="42" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000024</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>浅間建設 株式会社</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000024号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="42" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000066</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>相澤土地 株式会社</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000066号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="42" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000198</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>親和商事 有限会社</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000198号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T31"/>
+  <autoFilter ref="A1:T41"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -3948,10 +4968,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId100"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId91"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId101"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3962,7 +4992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T22"/>
+  <dimension ref="A1:T32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6231,8 +7261,1028 @@
         </is>
       </c>
     </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000181</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>大栄興業 株式会社</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000181号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000260</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>有限会社 協和商事</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000260号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000365</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>有限会社 小沢建設商事</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000365号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000162</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>有限会社 濱屋</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000162号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000071</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>東栄商事 株式会社</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000071号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000060</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>東横不動産 株式会社</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000013</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>株式会社 大谷商事</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000013号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000024</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>浅間建設 株式会社</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000024号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000066</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>相澤土地 株式会社</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000066号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000198</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>親和商事 有限会社</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000198号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T22"/>
+  <autoFilter ref="A1:T32"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -6288,10 +8338,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId64"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId55"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId65"/>
   </tableParts>
 </worksheet>
 </file>

--- a/database/real_estate_brokers.xlsx
+++ b/database/real_estate_brokers.xlsx
@@ -17,8 +17,8 @@
     <sheet name="データ辞書" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全社一覧'!$A$1:$T$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'関東'!$A$1:$T$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全社一覧'!$A$1:$T$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'関東'!$A$1:$T$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'北海道・東北'!$A$1:$T$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'近畿'!$A$1:$T$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'中国・四国'!$A$1:$T$2</definedName>
@@ -177,8 +177,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_9e7587520fcb" displayName="T_9e7587520fcb" ref="A1:T41" headerRowCount="1">
-  <autoFilter ref="A1:T41"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_9e7587520fcb" displayName="T_9e7587520fcb" ref="A1:T51" headerRowCount="1">
+  <autoFilter ref="A1:T51"/>
   <tableColumns count="20">
     <tableColumn id="1" name="会社ID"/>
     <tableColumn id="2" name="会社名"/>
@@ -206,8 +206,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_92ae89f64a96" displayName="T_92ae89f64a96" ref="A1:T32" headerRowCount="1">
-  <autoFilter ref="A1:T32"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_92ae89f64a96" displayName="T_92ae89f64a96" ref="A1:T42" headerRowCount="1">
+  <autoFilter ref="A1:T42"/>
   <tableColumns count="20">
     <tableColumn id="1" name="会社ID"/>
     <tableColumn id="2" name="会社名"/>
@@ -668,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T41"/>
+  <dimension ref="A1:T51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1716,12 +1716,12 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>RE-0009</t>
+          <t>RE-MLIT-11-00000122</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>武蔵コーポレーション株式会社</t>
+          <t>三幸土地建物株式会社</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1736,72 +1736,72 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>埼玉県さいたま市大宮区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>関東中心</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>一棟アパート・マンション・ビル・賃貸管理</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>https://www.musashi-corporation.com/</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>https://www.musashi-corporation.com/qa/investment_consultation.php</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>https://www.musashi-corporation.com/sell-feature/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>048-788-5636</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>収益不動産の売買・管理・出口戦略に特化</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>https://www.musashi-corporation.com/sell-feature/ | https://www.musashi-corporation.com/qa/investment_consultation.php</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1811,19 +1811,19 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>居住用戸建て仲介は対象外として整理</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000122号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>RE-0019</t>
+          <t>RE-MLIT-11-00000152</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>みずほ不動産販売株式会社</t>
+          <t>大和屋株式会社</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1833,52 +1833,52 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>東京都中央区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>首都圏・北海道・東北・中部・関西・中国・九州</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・事業用・相続・資産活用</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mizuho-re.co.jp/</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mizuho-re.co.jp/contact/</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mizuho-re.co.jp/buy/investment/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1888,44 +1888,44 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>全国拠点と金融グループ連携による不動産仲介</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>https://www.mizuho-re.co.jp/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>投資用サービスURLは定期リンク確認が必要</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000152号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000114</t>
+          <t>RE-MLIT-11-00000101</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>レイモンド不動産 株式会社</t>
+          <t>有限会社旭商事</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
@@ -2015,19 +2015,19 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000114号; 自動追加日: 2026-07-16</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000101号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>RE-0001</t>
+          <t>RE-MLIT-11-00000079</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>三井不動産リアルティ株式会社</t>
+          <t>株式会社三井商事</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2037,77 +2037,77 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>東京都千代田区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>全国</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・事業用・賃貸管理・資産活用</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mf-realty.jp/</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>https://pro.mf-realty.jp/otherInquiry/input/</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>https://pro.mf-realty.jp/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0120-921-582</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>居住用仲介と投資・収益不動産の専門サービスを展開</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>https://pro.mf-realty.jp/ | https://pro.mf-realty.jp/otherInquiry/input/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -2117,19 +2117,19 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>投資用戸建てを含む物件種別は個別検索で追加確認可能</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000079号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>RE-0018</t>
+          <t>RE-MLIT-11-00000126</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>三菱UFJ不動産販売株式会社</t>
+          <t>株式会社日和商事</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2139,52 +2139,52 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>東京都千代田区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>首都圏・名古屋・関西</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・投資事業用・相続</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sumai1.com/</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sumai1.com/contact/</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sumai1.com/buyers/investment/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2194,44 +2194,44 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>金融グループ系の仲介・資産承継・投資用不動産対応</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>https://www.sumai1.com/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>サービスURLと問い合わせURLの定期リンク確認が必要</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000126号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>RE-0002</t>
+          <t>RE-MLIT-11-00000047</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>住友不動産ステップ株式会社</t>
+          <t>株式会社石井不動産</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2241,77 +2241,77 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>東京都新宿区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>全国</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・一棟マンション・アパート・ビル</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>https://www.stepon.co.jp/</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>https://www.stepon.co.jp/contact/</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>https://www.stepon.co.jp/pro/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0120-566-742</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>全国ネットワークで居住用・投資用不動産を仲介</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>https://www.stepon.co.jp/pro/area_13/list_13_115/cs_25_06/ | https://www.stepon.co.jp/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2321,19 +2321,19 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>問い合わせURLは総合窓口。物件ページにも資料請求フォームあり</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000047号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000212</t>
+          <t>RE-0009</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>日本不動産 株式会社</t>
+          <t>武蔵コーポレーション株式会社</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2343,77 +2343,77 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>埼玉県さいたま市大宮区</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>関東中心</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>一棟アパート・マンション・ビル・賃貸管理</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.musashi-corporation.com/</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.musashi-corporation.com/qa/investment_consultation.php</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.musashi-corporation.com/sell-feature/</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>048-788-5636</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>収益不動産の売買・管理・出口戦略に特化</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://www.musashi-corporation.com/sell-feature/ | https://www.musashi-corporation.com/qa/investment_consultation.php</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>確認済み</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2423,19 +2423,19 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000212号; 自動追加日: 2026-07-16</t>
+          <t>居住用戸建て仲介は対象外として整理</t>
         </is>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000170</t>
+          <t>RE-MLIT-11-00000001</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>有限会社 マルミ商事</t>
+          <t>武藏野土地株式会社</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
@@ -2525,19 +2525,19 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000170号; 自動追加日: 2026-07-16</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000001号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>RE-0003</t>
+          <t>RE-MLIT-11-00000003</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>東急リバブル株式会社</t>
+          <t>福岡土地有限会社</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -2547,77 +2547,77 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>東京都渋谷区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>首都圏・札幌・仙台・名古屋・関西・福岡ほか</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・一棟収益・事業用・賃貸</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>https://www.livable.co.jp/</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>https://www.livable.co.jp/branch/toushi-support/</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>https://www.livable.co.jp/fudosan-toushi-baikyaku/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0120-992-151</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>投資サポートセンターと全国店舗網を持つ</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>https://www.livable.co.jp/branch/toushi-support/ | https://www.livable.co.jp/fudosan-toushi-baikyaku/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2627,19 +2627,19 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>投資用不動産専用窓口あり</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000003号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000044</t>
+          <t>RE-MLIT-11-00000030</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>栗城建設興業 株式会社</t>
+          <t>近藤不動産株式会社</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
@@ -2729,19 +2729,19 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000044号; 自動追加日: 2026-07-16</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000030号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000164</t>
+          <t>RE-MLIT-11-00000060</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>株式会社 なかやま不動産</t>
+          <t>ＫＭ不動産株式会社</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
@@ -2831,19 +2831,19 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000164号; 自動追加日: 2026-07-16</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000098</t>
+          <t>RE-0019</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>株式会社 三和不動産鑑定事務所</t>
+          <t>みずほ不動産販売株式会社</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2858,47 +2858,47 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>東京都中央区</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>首都圏・北海道・東北・中部・関西・中国・九州</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>マンション・土地・事業用・相続・資産活用</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mizuho-re.co.jp/</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mizuho-re.co.jp/contact/</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mizuho-re.co.jp/buy/investment/</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2908,44 +2908,44 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>全国拠点と金融グループ連携による不動産仲介</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://www.mizuho-re.co.jp/</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>一部確認</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000098号; 自動追加日: 2026-07-16</t>
+          <t>投資用サービスURLは定期リンク確認が必要</t>
         </is>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000001</t>
+          <t>RE-MLIT-13-00000114</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>株式会社 三富不動産</t>
+          <t>レイモンド不動産 株式会社</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -3035,19 +3035,19 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000001号; 自動追加日: 2026-07-16</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000114号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000093</t>
+          <t>RE-0001</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>株式会社 伊藤商会</t>
+          <t>三井不動産リアルティ株式会社</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -3062,72 +3062,72 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>東京都千代田区</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>全国</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>マンション・土地・事業用・賃貸管理・資産活用</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mf-realty.jp/</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>https://pro.mf-realty.jp/otherInquiry/input/</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>https://pro.mf-realty.jp/</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>0120-921-582</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>居住用仲介と投資・収益不動産の専門サービスを展開</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://pro.mf-realty.jp/ | https://pro.mf-realty.jp/otherInquiry/input/</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>確認済み</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -3137,19 +3137,19 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000093号; 自動追加日: 2026-07-16</t>
+          <t>投資用戸建てを含む物件種別は個別検索で追加確認可能</t>
         </is>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000060</t>
+          <t>RE-0018</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>株式会社 長岡建設</t>
+          <t>三菱UFJ不動産販売株式会社</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -3164,47 +3164,47 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>東京都千代田区</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>首都圏・名古屋・関西</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>マンション・土地・投資事業用・相続</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sumai1.com/</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sumai1.com/contact/</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sumai1.com/buyers/investment/</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3214,44 +3214,44 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>金融グループ系の仲介・資産承継・投資用不動産対応</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://www.sumai1.com/</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>一部確認</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000060号; 自動追加日: 2026-07-16</t>
+          <t>サービスURLと問い合わせURLの定期リンク確認が必要</t>
         </is>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>RE-0020</t>
+          <t>RE-0002</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>株式会社GA technologies（RENOSY）</t>
+          <t>住友不動産ステップ株式会社</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3266,17 +3266,17 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>東京都港区</t>
+          <t>東京都新宿区</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>全国オンライン中心</t>
+          <t>全国</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>投資用マンション・賃貸管理・売却</t>
+          <t>マンション・土地・一棟マンション・アパート・ビル</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>https://www.renosy.com/</t>
+          <t>https://www.stepon.co.jp/</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>https://www.renosy.com/contact</t>
+          <t>https://www.stepon.co.jp/contact/</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>https://www.renosy.com/asset</t>
+          <t>https://www.stepon.co.jp/pro/</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>0120-566-742</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>オンラインを中心とした不動産投資サービス</t>
+          <t>全国ネットワークで居住用・投資用不動産を仲介</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>https://www.renosy.com/</t>
+          <t>https://www.stepon.co.jp/pro/area_13/list_13_115/cs_25_06/ | https://www.stepon.co.jp/</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3331,29 +3331,29 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>確認済み</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>戸建て仲介ではなく区分マンション投資中心</t>
+          <t>問い合わせURLは総合窓口。物件ページにも資料請求フォームあり</t>
         </is>
       </c>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>RE-0006</t>
+          <t>RE-MLIT-13-00000212</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>株式会社オープンハウス</t>
+          <t>日本不動産 株式会社</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -3368,72 +3368,72 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>東京都渋谷区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>東京・神奈川・埼玉・千葉・愛知・大阪・兵庫・福岡ほか</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>新築戸建て・土地・マンション・国内外投資</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>https://oh.openhouse-group.com/</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>https://oh.openhouse-group.com/contact/</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t>https://oh.openhouse-group.com/s-kodate/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>03-6213-0775</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>都市部の戸建て供給とグループの不動産投資事業</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>https://oh.openhouse-group.com/company/about/ | https://oh.openhouse-group.com/s-kodate/saitama/ | https://wm.openhouse-group.com/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
@@ -3443,19 +3443,19 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>国内収益物件の一般顧客向け窓口はグループ各社も確認</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000212号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>RE-0007</t>
+          <t>RE-MLIT-13-00000170</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>株式会社オープンハウス・リアルエステート</t>
+          <t>有限会社 マルミ商事</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>東京都千代田区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>首都圏・関西・名古屋</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3485,57 +3485,57 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>一棟マンション・アパート・ビル・土地</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>https://ohre.openhouse-group.com/</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>https://ohre.openhouse-group.com/</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>https://shueki.ohd.openhouse-group.com/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>03-6854-7452</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>収益不動産の仕入れ・再生・売買に対応</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>https://ohre.openhouse-group.com/ | https://shueki.ohd.openhouse-group.com/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -3545,19 +3545,19 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>戸建ての直接取扱は追加確認</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000170号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="29" ht="42" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>RE-0008</t>
+          <t>RE-0003</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>株式会社ランドネット</t>
+          <t>東急リバブル株式会社</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>東京都豊島区</t>
+          <t>東京都渋谷区</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>東京・横浜・大阪・福岡ほか</t>
+          <t>首都圏・札幌・仙台・名古屋・関西・福岡ほか</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>中古マンション・賃貸管理・買取・リフォーム</t>
+          <t>マンション・土地・一棟収益・事業用・賃貸</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,32 +3602,32 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>https://landnet.co.jp/</t>
+          <t>https://www.livable.co.jp/</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>https://landnet.co.jp/contact/</t>
+          <t>https://www.livable.co.jp/branch/toushi-support/</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>https://landnet.co.jp/housing-search/</t>
+          <t>https://www.livable.co.jp/fudosan-toushi-baikyaku/</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0120-012-461</t>
+          <t>0120-992-151</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>投資用中古マンションと居住用不動産をワンストップで扱う</t>
+          <t>投資サポートセンターと全国店舗網を持つ</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>https://landnet.co.jp/ | https://landnet.co.jp/contact/ | https://landnet.co.jp/housing-search/kanagawa/yamato-shi</t>
+          <t>https://www.livable.co.jp/branch/toushi-support/ | https://www.livable.co.jp/fudosan-toushi-baikyaku/</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3647,19 +3647,19 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>戸建て掲載状況はエリアにより異なる</t>
+          <t>投資用不動産専用窓口あり</t>
         </is>
       </c>
     </row>
     <row r="30" ht="42" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000218</t>
+          <t>RE-MLIT-13-00000044</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>西武建設 株式会社</t>
+          <t>栗城建設興業 株式会社</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -3749,19 +3749,19 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000218号; 自動追加日: 2026-07-16</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000044号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="31" ht="42" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>RE-0004</t>
+          <t>RE-MLIT-13-00000164</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>野村不動産ソリューションズ株式会社</t>
+          <t>株式会社 なかやま不動産</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -3776,47 +3776,47 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>東京都新宿区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>首都圏・関西・名古屋ほか</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・一棟マンション・アパート・事業用</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nomura-solutions.co.jp/</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nomu.com/pro/contact/</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nomu.com/pro/house/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3826,22 +3826,22 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ノムコム・プロで投資用戸建て・収益物件を掲載</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>https://www.nomu.com/pro/house/area/1311/ | https://www.nomu.com/pro/contents/knowhow/20240919.html</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3851,19 +3851,19 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>問い合わせ先は物件・担当センターごとに異なる</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000164号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000181</t>
+          <t>RE-MLIT-13-00000098</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>大栄興業 株式会社</t>
+          <t>株式会社 三和不動産鑑定事務所</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
@@ -3953,19 +3953,19 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000181号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000098号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="33" ht="42" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000260</t>
+          <t>RE-MLIT-13-00000001</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>有限会社 協和商事</t>
+          <t>株式会社 三富不動産</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4035,12 +4035,12 @@
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
@@ -4055,19 +4055,19 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000260号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000001号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="34" ht="42" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000365</t>
+          <t>RE-MLIT-13-00000093</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>有限会社 小沢建設商事</t>
+          <t>株式会社 伊藤商会</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
@@ -4157,19 +4157,19 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000365号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000093号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="35" ht="42" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000162</t>
+          <t>RE-MLIT-13-00000060</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>有限会社 濱屋</t>
+          <t>株式会社 長岡建設</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
@@ -4259,19 +4259,19 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000162号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000060号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="36" ht="42" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000071</t>
+          <t>RE-0020</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>東栄商事 株式会社</t>
+          <t>株式会社GA technologies（RENOSY）</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -4281,52 +4281,52 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>東京都港区</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>全国オンライン中心</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>投資用マンション・賃貸管理・売却</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>https://www.renosy.com/</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>https://www.renosy.com/contact</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>https://www.renosy.com/asset</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4336,44 +4336,44 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>オンラインを中心とした不動産投資サービス</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://www.renosy.com/</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>一部確認</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000071号; 自動追加日: 2026-07-21</t>
+          <t>戸建て仲介ではなく区分マンション投資中心</t>
         </is>
       </c>
     </row>
     <row r="37" ht="42" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000060</t>
+          <t>RE-0006</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>東横不動産 株式会社</t>
+          <t>株式会社オープンハウス</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -4383,77 +4383,77 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>東京都渋谷区</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京・神奈川・埼玉・千葉・愛知・大阪・兵庫・福岡ほか</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>新築戸建て・土地・マンション・国内外投資</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>https://oh.openhouse-group.com/</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>https://oh.openhouse-group.com/contact/</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>https://oh.openhouse-group.com/s-kodate/</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>03-6213-0775</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>都市部の戸建て供給とグループの不動産投資事業</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://oh.openhouse-group.com/company/about/ | https://oh.openhouse-group.com/s-kodate/saitama/ | https://wm.openhouse-group.com/</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>一部確認</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
@@ -4463,19 +4463,19 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
+          <t>国内収益物件の一般顧客向け窓口はグループ各社も確認</t>
         </is>
       </c>
     </row>
     <row r="38" ht="42" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000013</t>
+          <t>RE-0007</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>株式会社 大谷商事</t>
+          <t>株式会社オープンハウス・リアルエステート</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -4485,17 +4485,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>東京都千代田区</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>首都圏・関西・名古屋</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4505,57 +4505,57 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>一棟マンション・アパート・ビル・土地</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>https://ohre.openhouse-group.com/</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>https://ohre.openhouse-group.com/</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>https://shueki.ohd.openhouse-group.com/</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>03-6854-7452</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>収益不動産の仕入れ・再生・売買に対応</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://ohre.openhouse-group.com/ | https://shueki.ohd.openhouse-group.com/</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>確認済み</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
@@ -4565,19 +4565,19 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000013号; 自動追加日: 2026-07-21</t>
+          <t>戸建ての直接取扱は追加確認</t>
         </is>
       </c>
     </row>
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000024</t>
+          <t>RE-0008</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>浅間建設 株式会社</t>
+          <t>株式会社ランドネット</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -4587,77 +4587,77 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>東京都豊島区</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京・横浜・大阪・福岡ほか</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>中古マンション・賃貸管理・買取・リフォーム</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>https://landnet.co.jp/</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>https://landnet.co.jp/contact/</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>https://landnet.co.jp/housing-search/</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>0120-012-461</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>投資用中古マンションと居住用不動産をワンストップで扱う</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://landnet.co.jp/ | https://landnet.co.jp/contact/ | https://landnet.co.jp/housing-search/kanagawa/yamato-shi</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>確認済み</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
@@ -4667,19 +4667,19 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000024号; 自動追加日: 2026-07-21</t>
+          <t>戸建て掲載状況はエリアにより異なる</t>
         </is>
       </c>
     </row>
     <row r="40" ht="42" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000066</t>
+          <t>RE-MLIT-13-00000218</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>相澤土地 株式会社</t>
+          <t>西武建設 株式会社</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
@@ -4769,114 +4769,1134 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000066号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000218号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="41" ht="42" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>RE-0004</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>野村不動産ソリューションズ株式会社</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>東京都新宿区</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>首都圏・関西・名古屋ほか</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>マンション・土地・一棟マンション・アパート・事業用</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nomura-solutions.co.jp/</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nomu.com/pro/contact/</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nomu.com/pro/house/</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>ノムコム・プロで投資用戸建て・収益物件を掲載</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nomu.com/pro/house/area/1311/ | https://www.nomu.com/pro/contents/knowhow/20240919.html</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>確認済み</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>問い合わせ先は物件・担当センターごとに異なる</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="42" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000181</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>大栄興業 株式会社</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000181号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="42" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000260</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>有限会社 協和商事</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000260号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="42" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000365</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>有限会社 小沢建設商事</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000365号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000162</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>有限会社 濱屋</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000162号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="42" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000071</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>東栄商事 株式会社</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000071号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="42" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000060</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>東横不動産 株式会社</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="42" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000013</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>株式会社 大谷商事</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000013号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="42" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000024</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>浅間建設 株式会社</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000024号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="42" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000066</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>相澤土地 株式会社</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000066号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="42" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
           <t>RE-MLIT-14-00000198</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>親和商事 有限会社</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>関東</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>神奈川県</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>神奈川県</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
         <is>
           <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
-      <c r="P41" s="3" t="inlineStr">
+      <c r="P51" s="3" t="inlineStr">
         <is>
           <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
-      <c r="Q41" s="2" t="inlineStr">
+      <c r="Q51" s="2" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="R41" s="2" t="inlineStr">
+      <c r="R51" s="2" t="inlineStr">
         <is>
           <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
-      <c r="S41" s="2" t="inlineStr">
+      <c r="S51" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="T41" s="2" t="inlineStr">
+      <c r="T51" s="2" t="inlineStr">
         <is>
           <t>免許行政庁: 神奈川県; 免許番号: 第000198号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T41"/>
+  <autoFilter ref="A1:T51"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -4914,74 +5934,84 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P45" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P50" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId110"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId101"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId111"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4992,7 +6022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T32"/>
+  <dimension ref="A1:T42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5122,12 +6152,12 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>RE-0009</t>
+          <t>RE-MLIT-11-00000122</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>武蔵コーポレーション株式会社</t>
+          <t>三幸土地建物株式会社</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -5142,72 +6172,72 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>埼玉県さいたま市大宮区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>関東中心</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>一棟アパート・マンション・ビル・賃貸管理</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>https://www.musashi-corporation.com/</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>https://www.musashi-corporation.com/qa/investment_consultation.php</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>https://www.musashi-corporation.com/sell-feature/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>048-788-5636</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>収益不動産の売買・管理・出口戦略に特化</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>https://www.musashi-corporation.com/sell-feature/ | https://www.musashi-corporation.com/qa/investment_consultation.php</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
@@ -5217,19 +6247,19 @@
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>居住用戸建て仲介は対象外として整理</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000122号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>RE-0019</t>
+          <t>RE-MLIT-11-00000152</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>みずほ不動産販売株式会社</t>
+          <t>大和屋株式会社</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -5239,52 +6269,52 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>東京都中央区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>首都圏・北海道・東北・中部・関西・中国・九州</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・事業用・相続・資産活用</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mizuho-re.co.jp/</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mizuho-re.co.jp/contact/</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mizuho-re.co.jp/buy/investment/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -5294,44 +6324,44 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>全国拠点と金融グループ連携による不動産仲介</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>https://www.mizuho-re.co.jp/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>投資用サービスURLは定期リンク確認が必要</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000152号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000114</t>
+          <t>RE-MLIT-11-00000101</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>レイモンド不動産 株式会社</t>
+          <t>有限会社旭商事</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -5341,7 +6371,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -5351,7 +6381,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5401,12 +6431,12 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -5421,19 +6451,19 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000114号; 自動追加日: 2026-07-16</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000101号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>RE-0001</t>
+          <t>RE-MLIT-11-00000079</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>三井不動産リアルティ株式会社</t>
+          <t>株式会社三井商事</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -5443,77 +6473,77 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>東京都千代田区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>全国</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・事業用・賃貸管理・資産活用</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mf-realty.jp/</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>https://pro.mf-realty.jp/otherInquiry/input/</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>https://pro.mf-realty.jp/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0120-921-582</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>居住用仲介と投資・収益不動産の専門サービスを展開</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>https://pro.mf-realty.jp/ | https://pro.mf-realty.jp/otherInquiry/input/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -5523,19 +6553,19 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>投資用戸建てを含む物件種別は個別検索で追加確認可能</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000079号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>RE-0018</t>
+          <t>RE-MLIT-11-00000126</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>三菱UFJ不動産販売株式会社</t>
+          <t>株式会社日和商事</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -5545,52 +6575,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>東京都千代田区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>首都圏・名古屋・関西</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・投資事業用・相続</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sumai1.com/</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sumai1.com/contact/</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sumai1.com/buyers/investment/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5600,44 +6630,44 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>金融グループ系の仲介・資産承継・投資用不動産対応</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>https://www.sumai1.com/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>サービスURLと問い合わせURLの定期リンク確認が必要</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000126号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>RE-0002</t>
+          <t>RE-MLIT-11-00000047</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>住友不動産ステップ株式会社</t>
+          <t>株式会社石井不動産</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -5647,77 +6677,77 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>東京都新宿区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>全国</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・一棟マンション・アパート・ビル</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>https://www.stepon.co.jp/</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>https://www.stepon.co.jp/contact/</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>https://www.stepon.co.jp/pro/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0120-566-742</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>全国ネットワークで居住用・投資用不動産を仲介</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>https://www.stepon.co.jp/pro/area_13/list_13_115/cs_25_06/ | https://www.stepon.co.jp/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -5727,19 +6757,19 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>問い合わせURLは総合窓口。物件ページにも資料請求フォームあり</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000047号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000212</t>
+          <t>RE-0009</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>日本不動産 株式会社</t>
+          <t>武蔵コーポレーション株式会社</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -5749,77 +6779,77 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>埼玉県さいたま市大宮区</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>関東中心</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>一棟アパート・マンション・ビル・賃貸管理</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.musashi-corporation.com/</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.musashi-corporation.com/qa/investment_consultation.php</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.musashi-corporation.com/sell-feature/</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>048-788-5636</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>収益不動産の売買・管理・出口戦略に特化</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://www.musashi-corporation.com/sell-feature/ | https://www.musashi-corporation.com/qa/investment_consultation.php</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>確認済み</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -5829,19 +6859,19 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000212号; 自動追加日: 2026-07-16</t>
+          <t>居住用戸建て仲介は対象外として整理</t>
         </is>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000170</t>
+          <t>RE-MLIT-11-00000001</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>有限会社 マルミ商事</t>
+          <t>武藏野土地株式会社</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -5851,7 +6881,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -5861,7 +6891,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5911,12 +6941,12 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
@@ -5931,19 +6961,19 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000170号; 自動追加日: 2026-07-16</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000001号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>RE-0003</t>
+          <t>RE-MLIT-11-00000003</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>東急リバブル株式会社</t>
+          <t>福岡土地有限会社</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -5953,77 +6983,77 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>東京都渋谷区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>首都圏・札幌・仙台・名古屋・関西・福岡ほか</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・一棟収益・事業用・賃貸</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>https://www.livable.co.jp/</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>https://www.livable.co.jp/branch/toushi-support/</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>https://www.livable.co.jp/fudosan-toushi-baikyaku/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0120-992-151</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>投資サポートセンターと全国店舗網を持つ</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>https://www.livable.co.jp/branch/toushi-support/ | https://www.livable.co.jp/fudosan-toushi-baikyaku/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -6033,19 +7063,19 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>投資用不動産専用窓口あり</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000003号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000044</t>
+          <t>RE-MLIT-11-00000030</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>栗城建設興業 株式会社</t>
+          <t>近藤不動産株式会社</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -6055,7 +7085,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -6065,7 +7095,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6115,12 +7145,12 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
@@ -6135,19 +7165,19 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000044号; 自動追加日: 2026-07-16</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000030号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000164</t>
+          <t>RE-MLIT-11-00000060</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>株式会社 なかやま不動産</t>
+          <t>ＫＭ不動産株式会社</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -6157,7 +7187,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -6167,7 +7197,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6217,12 +7247,12 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
@@ -6237,19 +7267,19 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000164号; 自動追加日: 2026-07-16</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000098</t>
+          <t>RE-0019</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>株式会社 三和不動産鑑定事務所</t>
+          <t>みずほ不動産販売株式会社</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -6264,47 +7294,47 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>東京都中央区</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>首都圏・北海道・東北・中部・関西・中国・九州</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>マンション・土地・事業用・相続・資産活用</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mizuho-re.co.jp/</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mizuho-re.co.jp/contact/</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mizuho-re.co.jp/buy/investment/</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6314,44 +7344,44 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>全国拠点と金融グループ連携による不動産仲介</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://www.mizuho-re.co.jp/</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>一部確認</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000098号; 自動追加日: 2026-07-16</t>
+          <t>投資用サービスURLは定期リンク確認が必要</t>
         </is>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000001</t>
+          <t>RE-MLIT-13-00000114</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>株式会社 三富不動産</t>
+          <t>レイモンド不動産 株式会社</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -6441,19 +7471,19 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000001号; 自動追加日: 2026-07-16</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000114号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000093</t>
+          <t>RE-0001</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>株式会社 伊藤商会</t>
+          <t>三井不動産リアルティ株式会社</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -6468,72 +7498,72 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>東京都千代田区</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>全国</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>マンション・土地・事業用・賃貸管理・資産活用</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mf-realty.jp/</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>https://pro.mf-realty.jp/otherInquiry/input/</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>https://pro.mf-realty.jp/</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>0120-921-582</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>居住用仲介と投資・収益不動産の専門サービスを展開</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://pro.mf-realty.jp/ | https://pro.mf-realty.jp/otherInquiry/input/</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>確認済み</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -6543,19 +7573,19 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000093号; 自動追加日: 2026-07-16</t>
+          <t>投資用戸建てを含む物件種別は個別検索で追加確認可能</t>
         </is>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000060</t>
+          <t>RE-0018</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>株式会社 長岡建設</t>
+          <t>三菱UFJ不動産販売株式会社</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -6570,47 +7600,47 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>東京都千代田区</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>首都圏・名古屋・関西</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>マンション・土地・投資事業用・相続</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sumai1.com/</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sumai1.com/contact/</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sumai1.com/buyers/investment/</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6620,44 +7650,44 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>金融グループ系の仲介・資産承継・投資用不動産対応</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://www.sumai1.com/</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>一部確認</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000060号; 自動追加日: 2026-07-16</t>
+          <t>サービスURLと問い合わせURLの定期リンク確認が必要</t>
         </is>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>RE-0020</t>
+          <t>RE-0002</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>株式会社GA technologies（RENOSY）</t>
+          <t>住友不動産ステップ株式会社</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -6672,17 +7702,17 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>東京都港区</t>
+          <t>東京都新宿区</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>全国オンライン中心</t>
+          <t>全国</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -6692,7 +7722,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>投資用マンション・賃貸管理・売却</t>
+          <t>マンション・土地・一棟マンション・アパート・ビル</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6702,32 +7732,32 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>https://www.renosy.com/</t>
+          <t>https://www.stepon.co.jp/</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>https://www.renosy.com/contact</t>
+          <t>https://www.stepon.co.jp/contact/</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>https://www.renosy.com/asset</t>
+          <t>https://www.stepon.co.jp/pro/</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>0120-566-742</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>オンラインを中心とした不動産投資サービス</t>
+          <t>全国ネットワークで居住用・投資用不動産を仲介</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>https://www.renosy.com/</t>
+          <t>https://www.stepon.co.jp/pro/area_13/list_13_115/cs_25_06/ | https://www.stepon.co.jp/</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6737,29 +7767,29 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>確認済み</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>戸建て仲介ではなく区分マンション投資中心</t>
+          <t>問い合わせURLは総合窓口。物件ページにも資料請求フォームあり</t>
         </is>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>RE-0006</t>
+          <t>RE-MLIT-13-00000212</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>株式会社オープンハウス</t>
+          <t>日本不動産 株式会社</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -6774,72 +7804,72 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>東京都渋谷区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>東京・神奈川・埼玉・千葉・愛知・大阪・兵庫・福岡ほか</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>新築戸建て・土地・マンション・国内外投資</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>https://oh.openhouse-group.com/</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>https://oh.openhouse-group.com/contact/</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>https://oh.openhouse-group.com/s-kodate/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>03-6213-0775</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>都市部の戸建て供給とグループの不動産投資事業</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>https://oh.openhouse-group.com/company/about/ | https://oh.openhouse-group.com/s-kodate/saitama/ | https://wm.openhouse-group.com/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -6849,19 +7879,19 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>国内収益物件の一般顧客向け窓口はグループ各社も確認</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000212号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>RE-0007</t>
+          <t>RE-MLIT-13-00000170</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>株式会社オープンハウス・リアルエステート</t>
+          <t>有限会社 マルミ商事</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -6876,12 +7906,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>東京都千代田区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>首都圏・関西・名古屋</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6891,57 +7921,57 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>一棟マンション・アパート・ビル・土地</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>https://ohre.openhouse-group.com/</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>https://ohre.openhouse-group.com/</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>https://shueki.ohd.openhouse-group.com/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>03-6854-7452</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>収益不動産の仕入れ・再生・売買に対応</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>https://ohre.openhouse-group.com/ | https://shueki.ohd.openhouse-group.com/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -6951,19 +7981,19 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>戸建ての直接取扱は追加確認</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000170号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>RE-0008</t>
+          <t>RE-0003</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>株式会社ランドネット</t>
+          <t>東急リバブル株式会社</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -6978,12 +8008,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>東京都豊島区</t>
+          <t>東京都渋谷区</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>東京・横浜・大阪・福岡ほか</t>
+          <t>首都圏・札幌・仙台・名古屋・関西・福岡ほか</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6998,7 +8028,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>中古マンション・賃貸管理・買取・リフォーム</t>
+          <t>マンション・土地・一棟収益・事業用・賃貸</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7008,32 +8038,32 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://landnet.co.jp/</t>
+          <t>https://www.livable.co.jp/</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>https://landnet.co.jp/contact/</t>
+          <t>https://www.livable.co.jp/branch/toushi-support/</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>https://landnet.co.jp/housing-search/</t>
+          <t>https://www.livable.co.jp/fudosan-toushi-baikyaku/</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0120-012-461</t>
+          <t>0120-992-151</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>投資用中古マンションと居住用不動産をワンストップで扱う</t>
+          <t>投資サポートセンターと全国店舗網を持つ</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>https://landnet.co.jp/ | https://landnet.co.jp/contact/ | https://landnet.co.jp/housing-search/kanagawa/yamato-shi</t>
+          <t>https://www.livable.co.jp/branch/toushi-support/ | https://www.livable.co.jp/fudosan-toushi-baikyaku/</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7053,19 +8083,19 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>戸建て掲載状況はエリアにより異なる</t>
+          <t>投資用不動産専用窓口あり</t>
         </is>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000218</t>
+          <t>RE-MLIT-13-00000044</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>西武建設 株式会社</t>
+          <t>栗城建設興業 株式会社</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -7155,19 +8185,19 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000218号; 自動追加日: 2026-07-16</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000044号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>RE-0004</t>
+          <t>RE-MLIT-13-00000164</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>野村不動産ソリューションズ株式会社</t>
+          <t>株式会社 なかやま不動産</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -7182,47 +8212,47 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>東京都新宿区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>首都圏・関西・名古屋ほか</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・一棟マンション・アパート・事業用</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nomura-solutions.co.jp/</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nomu.com/pro/contact/</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nomu.com/pro/house/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7232,22 +8262,22 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ノムコム・プロで投資用戸建て・収益物件を掲載</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>https://www.nomu.com/pro/house/area/1311/ | https://www.nomu.com/pro/contents/knowhow/20240919.html</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -7257,19 +8287,19 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>問い合わせ先は物件・担当センターごとに異なる</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000164号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000181</t>
+          <t>RE-MLIT-13-00000098</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>大栄興業 株式会社</t>
+          <t>株式会社 三和不動産鑑定事務所</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -7279,7 +8309,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -7289,7 +8319,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7339,12 +8369,12 @@
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
@@ -7359,19 +8389,19 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000181号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000098号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000260</t>
+          <t>RE-MLIT-13-00000001</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>有限会社 協和商事</t>
+          <t>株式会社 三富不動産</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -7381,7 +8411,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -7391,7 +8421,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7441,12 +8471,12 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
@@ -7461,19 +8491,19 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000260号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000001号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000365</t>
+          <t>RE-MLIT-13-00000093</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>有限会社 小沢建設商事</t>
+          <t>株式会社 伊藤商会</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -7483,7 +8513,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -7493,7 +8523,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7543,12 +8573,12 @@
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
@@ -7563,19 +8593,19 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000365号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000093号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000162</t>
+          <t>RE-MLIT-13-00000060</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>有限会社 濱屋</t>
+          <t>株式会社 長岡建設</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -7585,7 +8615,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -7595,7 +8625,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7645,12 +8675,12 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
@@ -7665,19 +8695,19 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000162号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000060号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000071</t>
+          <t>RE-0020</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>東栄商事 株式会社</t>
+          <t>株式会社GA technologies（RENOSY）</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -7687,52 +8717,52 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>東京都港区</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>全国オンライン中心</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>投資用マンション・賃貸管理・売却</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.renosy.com/</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.renosy.com/contact</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.renosy.com/asset</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7742,44 +8772,44 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>オンラインを中心とした不動産投資サービス</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://www.renosy.com/</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>一部確認</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000071号; 自動追加日: 2026-07-21</t>
+          <t>戸建て仲介ではなく区分マンション投資中心</t>
         </is>
       </c>
     </row>
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000060</t>
+          <t>RE-0006</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>東横不動産 株式会社</t>
+          <t>株式会社オープンハウス</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -7789,77 +8819,77 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>東京都渋谷区</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京・神奈川・埼玉・千葉・愛知・大阪・兵庫・福岡ほか</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>新築戸建て・土地・マンション・国内外投資</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>https://oh.openhouse-group.com/</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>https://oh.openhouse-group.com/contact/</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>https://oh.openhouse-group.com/s-kodate/</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>03-6213-0775</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>都市部の戸建て供給とグループの不動産投資事業</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://oh.openhouse-group.com/company/about/ | https://oh.openhouse-group.com/s-kodate/saitama/ | https://wm.openhouse-group.com/</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>一部確認</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -7869,19 +8899,19 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
+          <t>国内収益物件の一般顧客向け窓口はグループ各社も確認</t>
         </is>
       </c>
     </row>
     <row r="29" ht="42" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000013</t>
+          <t>RE-0007</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>株式会社 大谷商事</t>
+          <t>株式会社オープンハウス・リアルエステート</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -7891,17 +8921,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>東京都千代田区</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>首都圏・関西・名古屋</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7911,57 +8941,57 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>一棟マンション・アパート・ビル・土地</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>https://ohre.openhouse-group.com/</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>https://ohre.openhouse-group.com/</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>https://shueki.ohd.openhouse-group.com/</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>03-6854-7452</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>収益不動産の仕入れ・再生・売買に対応</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://ohre.openhouse-group.com/ | https://shueki.ohd.openhouse-group.com/</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>確認済み</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -7971,19 +9001,19 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000013号; 自動追加日: 2026-07-21</t>
+          <t>戸建ての直接取扱は追加確認</t>
         </is>
       </c>
     </row>
     <row r="30" ht="42" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000024</t>
+          <t>RE-0008</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>浅間建設 株式会社</t>
+          <t>株式会社ランドネット</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -7993,77 +9023,77 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>東京都豊島区</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京・横浜・大阪・福岡ほか</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>中古マンション・賃貸管理・買取・リフォーム</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>https://landnet.co.jp/</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>https://landnet.co.jp/contact/</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>https://landnet.co.jp/housing-search/</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>0120-012-461</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>投資用中古マンションと居住用不動産をワンストップで扱う</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://landnet.co.jp/ | https://landnet.co.jp/contact/ | https://landnet.co.jp/housing-search/kanagawa/yamato-shi</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>確認済み</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -8073,19 +9103,19 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000024号; 自動追加日: 2026-07-21</t>
+          <t>戸建て掲載状況はエリアにより異なる</t>
         </is>
       </c>
     </row>
     <row r="31" ht="42" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000066</t>
+          <t>RE-MLIT-13-00000218</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>相澤土地 株式会社</t>
+          <t>西武建設 株式会社</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -8095,7 +9125,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -8105,7 +9135,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8155,12 +9185,12 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
@@ -8175,183 +9205,1213 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000066号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000218号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>RE-0004</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>野村不動産ソリューションズ株式会社</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>東京都新宿区</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>首都圏・関西・名古屋ほか</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>マンション・土地・一棟マンション・アパート・事業用</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nomura-solutions.co.jp/</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nomu.com/pro/contact/</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nomu.com/pro/house/</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>ノムコム・プロで投資用戸建て・収益物件を掲載</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nomu.com/pro/house/area/1311/ | https://www.nomu.com/pro/contents/knowhow/20240919.html</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>確認済み</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>問い合わせ先は物件・担当センターごとに異なる</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000181</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>大栄興業 株式会社</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000181号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000260</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>有限会社 協和商事</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000260号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000365</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>有限会社 小沢建設商事</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000365号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000162</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>有限会社 濱屋</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000162号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="42" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000071</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>東栄商事 株式会社</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000071号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="42" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000060</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>東横不動産 株式会社</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="42" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000013</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>株式会社 大谷商事</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000013号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="42" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000024</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>浅間建設 株式会社</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000024号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="42" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000066</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>相澤土地 株式会社</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000066号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="42" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
           <t>RE-MLIT-14-00000198</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>親和商事 有限会社</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>関東</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>神奈川県</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>神奈川県</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
-      <c r="P32" s="3" t="inlineStr">
+      <c r="P42" s="3" t="inlineStr">
         <is>
           <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
-      <c r="Q32" s="2" t="inlineStr">
+      <c r="Q42" s="2" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="R32" s="2" t="inlineStr">
+      <c r="R42" s="2" t="inlineStr">
         <is>
           <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
-      <c r="S32" s="2" t="inlineStr">
+      <c r="S42" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="T32" s="2" t="inlineStr">
+      <c r="T42" s="2" t="inlineStr">
         <is>
           <t>免許行政庁: 神奈川県; 免許番号: 第000198号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T32"/>
+  <autoFilter ref="A1:T42"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId74"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId65"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId75"/>
   </tableParts>
 </worksheet>
 </file>

--- a/database/real_estate_brokers.xlsx
+++ b/database/real_estate_brokers.xlsx
@@ -17,8 +17,8 @@
     <sheet name="データ辞書" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全社一覧'!$A$1:$T$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'関東'!$A$1:$T$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全社一覧'!$A$1:$T$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'関東'!$A$1:$T$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'北海道・東北'!$A$1:$T$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'近畿'!$A$1:$T$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'中国・四国'!$A$1:$T$2</definedName>
@@ -177,8 +177,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_9e7587520fcb" displayName="T_9e7587520fcb" ref="A1:T51" headerRowCount="1">
-  <autoFilter ref="A1:T51"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_9e7587520fcb" displayName="T_9e7587520fcb" ref="A1:T61" headerRowCount="1">
+  <autoFilter ref="A1:T61"/>
   <tableColumns count="20">
     <tableColumn id="1" name="会社ID"/>
     <tableColumn id="2" name="会社名"/>
@@ -206,8 +206,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_92ae89f64a96" displayName="T_92ae89f64a96" ref="A1:T42" headerRowCount="1">
-  <autoFilter ref="A1:T42"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_92ae89f64a96" displayName="T_92ae89f64a96" ref="A1:T52" headerRowCount="1">
+  <autoFilter ref="A1:T52"/>
   <tableColumns count="20">
     <tableColumn id="1" name="会社ID"/>
     <tableColumn id="2" name="会社名"/>
@@ -668,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T51"/>
+  <dimension ref="A1:T61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1716,12 +1716,12 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-11-00000122</t>
+          <t>RE-MLIT-12-00000283</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>三幸土地建物株式会社</t>
+          <t>ミドリ不動産株式会社</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
@@ -1811,19 +1811,19 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 埼玉県; 免許番号: 第000122号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 千葉県; 免許番号: 第000283号; 自動追加日: 2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-11-00000152</t>
+          <t>RE-MLIT-12-00000271</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>大和屋株式会社</t>
+          <t>丸正商事株式会社</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1893,12 +1893,12 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
@@ -1913,19 +1913,19 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 埼玉県; 免許番号: 第000152号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 千葉県; 免許番号: 第000271号; 自動追加日: 2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-11-00000101</t>
+          <t>RE-MLIT-12-00000119</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>有限会社旭商事</t>
+          <t>北葉開発株式会社</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
@@ -2015,19 +2015,19 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 埼玉県; 免許番号: 第000101号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 千葉県; 免許番号: 第000119号; 自動追加日: 2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-11-00000079</t>
+          <t>RE-MLIT-12-00000001</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>株式会社三井商事</t>
+          <t>千葉復興株式会社</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2097,12 +2097,12 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
@@ -2117,19 +2117,19 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 埼玉県; 免許番号: 第000079号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 千葉県; 免許番号: 第000001号; 自動追加日: 2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-11-00000126</t>
+          <t>RE-MLIT-12-00000120</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>株式会社日和商事</t>
+          <t>小湊鉄道株式会社</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2199,12 +2199,12 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
@@ -2219,19 +2219,19 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 埼玉県; 免許番号: 第000126号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 千葉県; 免許番号: 第000120号; 自動追加日: 2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-11-00000047</t>
+          <t>RE-MLIT-12-00000292</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>株式会社石井不動産</t>
+          <t>常南土地株式会社</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
@@ -2321,19 +2321,19 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 埼玉県; 免許番号: 第000047号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 千葉県; 免許番号: 第000292号; 自動追加日: 2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>RE-0009</t>
+          <t>RE-MLIT-12-00000298</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>武蔵コーポレーション株式会社</t>
+          <t>日東不動産株式会社</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2343,77 +2343,77 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>埼玉県さいたま市大宮区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>関東中心</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>一棟アパート・マンション・ビル・賃貸管理</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>https://www.musashi-corporation.com/</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>https://www.musashi-corporation.com/qa/investment_consultation.php</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>https://www.musashi-corporation.com/sell-feature/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>048-788-5636</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>収益不動産の売買・管理・出口戦略に特化</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>https://www.musashi-corporation.com/sell-feature/ | https://www.musashi-corporation.com/qa/investment_consultation.php</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2423,19 +2423,19 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>居住用戸建て仲介は対象外として整理</t>
+          <t>免許行政庁: 千葉県; 免許番号: 第000298号; 自動追加日: 2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-11-00000001</t>
+          <t>RE-MLIT-12-00000184</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>武藏野土地株式会社</t>
+          <t>有限会社京葉ビル</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
@@ -2525,19 +2525,19 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 埼玉県; 免許番号: 第000001号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 千葉県; 免許番号: 第000184号; 自動追加日: 2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-11-00000003</t>
+          <t>RE-MLIT-12-00000234</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>福岡土地有限会社</t>
+          <t>有限会社川崎不動産</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
@@ -2627,19 +2627,19 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 埼玉県; 免許番号: 第000003号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 千葉県; 免許番号: 第000234号; 自動追加日: 2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-11-00000030</t>
+          <t>RE-MLIT-12-00000286</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>近藤不動産株式会社</t>
+          <t>株式会社富士見地所</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
@@ -2729,19 +2729,19 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 埼玉県; 免許番号: 第000030号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 千葉県; 免許番号: 第000286号; 自動追加日: 2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-11-00000060</t>
+          <t>RE-MLIT-11-00000122</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>ＫＭ不動産株式会社</t>
+          <t>三幸土地建物株式会社</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2831,19 +2831,19 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 埼玉県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000122号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>RE-0019</t>
+          <t>RE-MLIT-11-00000152</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>みずほ不動産販売株式会社</t>
+          <t>大和屋株式会社</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2853,99 +2853,99 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>東京都中央区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>首都圏・北海道・東北・中部・関西・中国・九州</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・事業用・相続・資産活用</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>https://www.mizuho-re.co.jp/</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mizuho-re.co.jp/contact/</t>
+          <t>https://www.yamatoya-kk.co.jp/saiyou/</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>https://www.mizuho-re.co.jp/buy/investment/</t>
+          <t>https://www.yamatoya-kk.co.jp/saiyou/</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>048-522-8611</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>全国拠点と金融グループ連携による不動産仲介</t>
+          <t>公式サイトを自動確認</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>https://www.mizuho-re.co.jp/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1 | https://www.yamatoya-kk.co.jp/saiyou/</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>一部自動確認</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>投資用サービスURLは定期リンク確認が必要</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000152号; 自動追加日: 2026-07-21; 公式サイト自動確認日: 2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000114</t>
+          <t>RE-MLIT-11-00000101</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>レイモンド不動産 株式会社</t>
+          <t>有限会社旭商事</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3015,12 +3015,12 @@
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
@@ -3035,19 +3035,19 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000114号; 自動追加日: 2026-07-16</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000101号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>RE-0001</t>
+          <t>RE-MLIT-11-00000079</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>三井不動産リアルティ株式会社</t>
+          <t>株式会社三井商事</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -3057,77 +3057,77 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>東京都千代田区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>全国</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・事業用・賃貸管理・資産活用</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mf-realty.jp/</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>https://pro.mf-realty.jp/otherInquiry/input/</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>https://pro.mf-realty.jp/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0120-921-582</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>居住用仲介と投資・収益不動産の専門サービスを展開</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>https://pro.mf-realty.jp/ | https://pro.mf-realty.jp/otherInquiry/input/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -3137,19 +3137,19 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>投資用戸建てを含む物件種別は個別検索で追加確認可能</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000079号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>RE-0018</t>
+          <t>RE-MLIT-11-00000126</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>三菱UFJ不動産販売株式会社</t>
+          <t>株式会社日和商事</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -3159,52 +3159,52 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>東京都千代田区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>首都圏・名古屋・関西</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・投資事業用・相続</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sumai1.com/</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sumai1.com/contact/</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sumai1.com/buyers/investment/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3214,44 +3214,44 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>金融グループ系の仲介・資産承継・投資用不動産対応</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>https://www.sumai1.com/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>サービスURLと問い合わせURLの定期リンク確認が必要</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000126号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>RE-0002</t>
+          <t>RE-MLIT-11-00000047</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>住友不動産ステップ株式会社</t>
+          <t>株式会社石井不動産</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3261,77 +3261,77 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>東京都新宿区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>全国</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・一棟マンション・アパート・ビル</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>https://www.stepon.co.jp/</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>https://www.stepon.co.jp/contact/</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>https://www.stepon.co.jp/pro/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0120-566-742</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>全国ネットワークで居住用・投資用不動産を仲介</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>https://www.stepon.co.jp/pro/area_13/list_13_115/cs_25_06/ | https://www.stepon.co.jp/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -3341,19 +3341,19 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>問い合わせURLは総合窓口。物件ページにも資料請求フォームあり</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000047号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000212</t>
+          <t>RE-0009</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>日本不動産 株式会社</t>
+          <t>武蔵コーポレーション株式会社</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -3363,77 +3363,77 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>埼玉県さいたま市大宮区</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>関東中心</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>一棟アパート・マンション・ビル・賃貸管理</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.musashi-corporation.com/</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.musashi-corporation.com/qa/investment_consultation.php</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.musashi-corporation.com/sell-feature/</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>048-788-5636</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>収益不動産の売買・管理・出口戦略に特化</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://www.musashi-corporation.com/sell-feature/ | https://www.musashi-corporation.com/qa/investment_consultation.php</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>確認済み</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
@@ -3443,19 +3443,19 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000212号; 自動追加日: 2026-07-16</t>
+          <t>居住用戸建て仲介は対象外として整理</t>
         </is>
       </c>
     </row>
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000170</t>
+          <t>RE-MLIT-11-00000001</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>有限会社 マルミ商事</t>
+          <t>武藏野土地株式会社</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
@@ -3545,19 +3545,19 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000170号; 自動追加日: 2026-07-16</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000001号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="29" ht="42" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>RE-0003</t>
+          <t>RE-MLIT-11-00000003</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>東急リバブル株式会社</t>
+          <t>福岡土地有限会社</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -3567,77 +3567,77 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>東京都渋谷区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>首都圏・札幌・仙台・名古屋・関西・福岡ほか</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・一棟収益・事業用・賃貸</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>https://www.livable.co.jp/</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>https://www.livable.co.jp/branch/toushi-support/</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>https://www.livable.co.jp/fudosan-toushi-baikyaku/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0120-992-151</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>投資サポートセンターと全国店舗網を持つ</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>https://www.livable.co.jp/branch/toushi-support/ | https://www.livable.co.jp/fudosan-toushi-baikyaku/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3647,19 +3647,19 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>投資用不動産専用窓口あり</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000003号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="30" ht="42" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000044</t>
+          <t>RE-MLIT-11-00000030</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>栗城建設興業 株式会社</t>
+          <t>近藤不動産株式会社</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
@@ -3749,19 +3749,19 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000044号; 自動追加日: 2026-07-16</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000030号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="31" ht="42" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000164</t>
+          <t>RE-MLIT-11-00000060</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>株式会社 なかやま不動産</t>
+          <t>ＫＭ不動産株式会社</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
@@ -3851,19 +3851,19 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000164号; 自動追加日: 2026-07-16</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000098</t>
+          <t>RE-0019</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>株式会社 三和不動産鑑定事務所</t>
+          <t>みずほ不動産販売株式会社</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3878,47 +3878,47 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>東京都中央区</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>首都圏・北海道・東北・中部・関西・中国・九州</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>マンション・土地・事業用・相続・資産活用</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mizuho-re.co.jp/</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mizuho-re.co.jp/contact/</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mizuho-re.co.jp/buy/investment/</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3928,44 +3928,44 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>全国拠点と金融グループ連携による不動産仲介</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://www.mizuho-re.co.jp/</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>一部確認</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000098号; 自動追加日: 2026-07-16</t>
+          <t>投資用サービスURLは定期リンク確認が必要</t>
         </is>
       </c>
     </row>
     <row r="33" ht="42" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000001</t>
+          <t>RE-MLIT-13-00000114</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>株式会社 三富不動産</t>
+          <t>レイモンド不動産 株式会社</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -4055,19 +4055,19 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000001号; 自動追加日: 2026-07-16</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000114号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="34" ht="42" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000093</t>
+          <t>RE-0001</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>株式会社 伊藤商会</t>
+          <t>三井不動産リアルティ株式会社</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -4082,72 +4082,72 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>東京都千代田区</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>全国</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>マンション・土地・事業用・賃貸管理・資産活用</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mf-realty.jp/</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>https://pro.mf-realty.jp/otherInquiry/input/</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>https://pro.mf-realty.jp/</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>0120-921-582</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>居住用仲介と投資・収益不動産の専門サービスを展開</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://pro.mf-realty.jp/ | https://pro.mf-realty.jp/otherInquiry/input/</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>確認済み</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -4157,19 +4157,19 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000093号; 自動追加日: 2026-07-16</t>
+          <t>投資用戸建てを含む物件種別は個別検索で追加確認可能</t>
         </is>
       </c>
     </row>
     <row r="35" ht="42" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000060</t>
+          <t>RE-0018</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>株式会社 長岡建設</t>
+          <t>三菱UFJ不動産販売株式会社</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -4184,47 +4184,47 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>東京都千代田区</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>首都圏・名古屋・関西</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>マンション・土地・投資事業用・相続</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sumai1.com/</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sumai1.com/contact/</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sumai1.com/buyers/investment/</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4234,44 +4234,44 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>金融グループ系の仲介・資産承継・投資用不動産対応</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://www.sumai1.com/</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>一部確認</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000060号; 自動追加日: 2026-07-16</t>
+          <t>サービスURLと問い合わせURLの定期リンク確認が必要</t>
         </is>
       </c>
     </row>
     <row r="36" ht="42" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>RE-0020</t>
+          <t>RE-0002</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>株式会社GA technologies（RENOSY）</t>
+          <t>住友不動産ステップ株式会社</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -4286,17 +4286,17 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>東京都港区</t>
+          <t>東京都新宿区</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>全国オンライン中心</t>
+          <t>全国</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>投資用マンション・賃貸管理・売却</t>
+          <t>マンション・土地・一棟マンション・アパート・ビル</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4316,32 +4316,32 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>https://www.renosy.com/</t>
+          <t>https://www.stepon.co.jp/</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>https://www.renosy.com/contact</t>
+          <t>https://www.stepon.co.jp/contact/</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>https://www.renosy.com/asset</t>
+          <t>https://www.stepon.co.jp/pro/</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>0120-566-742</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>オンラインを中心とした不動産投資サービス</t>
+          <t>全国ネットワークで居住用・投資用不動産を仲介</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>https://www.renosy.com/</t>
+          <t>https://www.stepon.co.jp/pro/area_13/list_13_115/cs_25_06/ | https://www.stepon.co.jp/</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4351,29 +4351,29 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>確認済み</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>戸建て仲介ではなく区分マンション投資中心</t>
+          <t>問い合わせURLは総合窓口。物件ページにも資料請求フォームあり</t>
         </is>
       </c>
     </row>
     <row r="37" ht="42" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>RE-0006</t>
+          <t>RE-MLIT-13-00000212</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>株式会社オープンハウス</t>
+          <t>日本不動産 株式会社</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -4388,72 +4388,72 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>東京都渋谷区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>東京・神奈川・埼玉・千葉・愛知・大阪・兵庫・福岡ほか</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>新築戸建て・土地・マンション・国内外投資</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>https://oh.openhouse-group.com/</t>
-        </is>
-      </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t>https://oh.openhouse-group.com/contact/</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t>https://oh.openhouse-group.com/s-kodate/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>03-6213-0775</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>都市部の戸建て供給とグループの不動産投資事業</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>https://oh.openhouse-group.com/company/about/ | https://oh.openhouse-group.com/s-kodate/saitama/ | https://wm.openhouse-group.com/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
@@ -4463,19 +4463,19 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>国内収益物件の一般顧客向け窓口はグループ各社も確認</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000212号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="38" ht="42" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>RE-0007</t>
+          <t>RE-MLIT-13-00000170</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>株式会社オープンハウス・リアルエステート</t>
+          <t>有限会社 マルミ商事</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>東京都千代田区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>首都圏・関西・名古屋</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4505,57 +4505,57 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>一棟マンション・アパート・ビル・土地</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>https://ohre.openhouse-group.com/</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>https://ohre.openhouse-group.com/</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>https://shueki.ohd.openhouse-group.com/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>03-6854-7452</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>収益不動産の仕入れ・再生・売買に対応</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>https://ohre.openhouse-group.com/ | https://shueki.ohd.openhouse-group.com/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
@@ -4565,19 +4565,19 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>戸建ての直接取扱は追加確認</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000170号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>RE-0008</t>
+          <t>RE-0003</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>株式会社ランドネット</t>
+          <t>東急リバブル株式会社</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>東京都豊島区</t>
+          <t>東京都渋谷区</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>東京・横浜・大阪・福岡ほか</t>
+          <t>首都圏・札幌・仙台・名古屋・関西・福岡ほか</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>中古マンション・賃貸管理・買取・リフォーム</t>
+          <t>マンション・土地・一棟収益・事業用・賃貸</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>https://landnet.co.jp/</t>
+          <t>https://www.livable.co.jp/</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>https://landnet.co.jp/contact/</t>
+          <t>https://www.livable.co.jp/branch/toushi-support/</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>https://landnet.co.jp/housing-search/</t>
+          <t>https://www.livable.co.jp/fudosan-toushi-baikyaku/</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>0120-012-461</t>
+          <t>0120-992-151</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>投資用中古マンションと居住用不動産をワンストップで扱う</t>
+          <t>投資サポートセンターと全国店舗網を持つ</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>https://landnet.co.jp/ | https://landnet.co.jp/contact/ | https://landnet.co.jp/housing-search/kanagawa/yamato-shi</t>
+          <t>https://www.livable.co.jp/branch/toushi-support/ | https://www.livable.co.jp/fudosan-toushi-baikyaku/</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4667,19 +4667,19 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>戸建て掲載状況はエリアにより異なる</t>
+          <t>投資用不動産専用窓口あり</t>
         </is>
       </c>
     </row>
     <row r="40" ht="42" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000218</t>
+          <t>RE-MLIT-13-00000044</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>西武建設 株式会社</t>
+          <t>栗城建設興業 株式会社</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -4769,19 +4769,19 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000218号; 自動追加日: 2026-07-16</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000044号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="41" ht="42" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>RE-0004</t>
+          <t>RE-MLIT-13-00000164</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>野村不動産ソリューションズ株式会社</t>
+          <t>株式会社 なかやま不動産</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -4796,47 +4796,47 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>東京都新宿区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>首都圏・関西・名古屋ほか</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・一棟マンション・アパート・事業用</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nomura-solutions.co.jp/</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nomu.com/pro/contact/</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nomu.com/pro/house/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4846,22 +4846,22 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ノムコム・プロで投資用戸建て・収益物件を掲載</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>https://www.nomu.com/pro/house/area/1311/ | https://www.nomu.com/pro/contents/knowhow/20240919.html</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
@@ -4871,19 +4871,19 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>問い合わせ先は物件・担当センターごとに異なる</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000164号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="42" ht="42" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000181</t>
+          <t>RE-MLIT-13-00000098</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>大栄興業 株式会社</t>
+          <t>株式会社 三和不動産鑑定事務所</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -4953,12 +4953,12 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
@@ -4973,19 +4973,19 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000181号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000098号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="43" ht="42" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000260</t>
+          <t>RE-MLIT-13-00000001</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>有限会社 協和商事</t>
+          <t>株式会社 三富不動産</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
@@ -5075,19 +5075,19 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000260号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000001号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="44" ht="42" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000365</t>
+          <t>RE-MLIT-13-00000093</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>有限会社 小沢建設商事</t>
+          <t>株式会社 伊藤商会</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
@@ -5177,19 +5177,19 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000365号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000093号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="45" ht="42" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000162</t>
+          <t>RE-MLIT-13-00000060</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>有限会社 濱屋</t>
+          <t>株式会社 長岡建設</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
@@ -5279,19 +5279,19 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000162号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000060号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="46" ht="42" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000071</t>
+          <t>RE-0020</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>東栄商事 株式会社</t>
+          <t>株式会社GA technologies（RENOSY）</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -5301,52 +5301,52 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>東京都港区</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>全国オンライン中心</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>投資用マンション・賃貸管理・売却</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>https://www.renosy.com/</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>https://www.renosy.com/contact</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>https://www.renosy.com/asset</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5356,44 +5356,44 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>オンラインを中心とした不動産投資サービス</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://www.renosy.com/</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>一部確認</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000071号; 自動追加日: 2026-07-21</t>
+          <t>戸建て仲介ではなく区分マンション投資中心</t>
         </is>
       </c>
     </row>
     <row r="47" ht="42" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000060</t>
+          <t>RE-0006</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>東横不動産 株式会社</t>
+          <t>株式会社オープンハウス</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -5403,77 +5403,77 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>東京都渋谷区</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京・神奈川・埼玉・千葉・愛知・大阪・兵庫・福岡ほか</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>新築戸建て・土地・マンション・国内外投資</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>https://oh.openhouse-group.com/</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>https://oh.openhouse-group.com/contact/</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>https://oh.openhouse-group.com/s-kodate/</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>03-6213-0775</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>都市部の戸建て供給とグループの不動産投資事業</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://oh.openhouse-group.com/company/about/ | https://oh.openhouse-group.com/s-kodate/saitama/ | https://wm.openhouse-group.com/</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>一部確認</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
@@ -5483,19 +5483,19 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
+          <t>国内収益物件の一般顧客向け窓口はグループ各社も確認</t>
         </is>
       </c>
     </row>
     <row r="48" ht="42" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000013</t>
+          <t>RE-0007</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>株式会社 大谷商事</t>
+          <t>株式会社オープンハウス・リアルエステート</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -5505,17 +5505,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>東京都千代田区</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>首都圏・関西・名古屋</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5525,57 +5525,57 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>一棟マンション・アパート・ビル・土地</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>https://ohre.openhouse-group.com/</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>https://ohre.openhouse-group.com/</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>https://shueki.ohd.openhouse-group.com/</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>03-6854-7452</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>収益不動産の仕入れ・再生・売買に対応</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://ohre.openhouse-group.com/ | https://shueki.ohd.openhouse-group.com/</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>確認済み</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
@@ -5585,19 +5585,19 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000013号; 自動追加日: 2026-07-21</t>
+          <t>戸建ての直接取扱は追加確認</t>
         </is>
       </c>
     </row>
     <row r="49" ht="42" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000024</t>
+          <t>RE-0008</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>浅間建設 株式会社</t>
+          <t>株式会社ランドネット</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -5607,77 +5607,77 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>東京都豊島区</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京・横浜・大阪・福岡ほか</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>中古マンション・賃貸管理・買取・リフォーム</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>https://landnet.co.jp/</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>https://landnet.co.jp/contact/</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>https://landnet.co.jp/housing-search/</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>0120-012-461</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>投資用中古マンションと居住用不動産をワンストップで扱う</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://landnet.co.jp/ | https://landnet.co.jp/contact/ | https://landnet.co.jp/housing-search/kanagawa/yamato-shi</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>確認済み</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
@@ -5687,19 +5687,19 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000024号; 自動追加日: 2026-07-21</t>
+          <t>戸建て掲載状況はエリアにより異なる</t>
         </is>
       </c>
     </row>
     <row r="50" ht="42" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000066</t>
+          <t>RE-MLIT-13-00000218</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>相澤土地 株式会社</t>
+          <t>西武建設 株式会社</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr">
@@ -5789,114 +5789,1134 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000066号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000218号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="51" ht="42" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>RE-0004</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>野村不動産ソリューションズ株式会社</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>東京都新宿区</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>首都圏・関西・名古屋ほか</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>マンション・土地・一棟マンション・アパート・事業用</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nomura-solutions.co.jp/</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nomu.com/pro/contact/</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nomu.com/pro/house/</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>ノムコム・プロで投資用戸建て・収益物件を掲載</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nomu.com/pro/house/area/1311/ | https://www.nomu.com/pro/contents/knowhow/20240919.html</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>確認済み</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>問い合わせ先は物件・担当センターごとに異なる</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="42" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000181</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>大栄興業 株式会社</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000181号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="42" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000260</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>有限会社 協和商事</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000260号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="42" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000365</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>有限会社 小沢建設商事</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000365号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="42" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000162</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>有限会社 濱屋</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000162号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="42" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000071</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>東栄商事 株式会社</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000071号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="42" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000060</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>東横不動産 株式会社</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="42" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000013</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>株式会社 大谷商事</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000013号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="42" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000024</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>浅間建設 株式会社</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000024号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="42" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000066</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>相澤土地 株式会社</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000066号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="42" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
           <t>RE-MLIT-14-00000198</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>親和商事 有限会社</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>関東</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>神奈川県</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>神奈川県</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
         <is>
           <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
-      <c r="P51" s="3" t="inlineStr">
+      <c r="P61" s="3" t="inlineStr">
         <is>
           <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
-      <c r="Q51" s="2" t="inlineStr">
+      <c r="Q61" s="2" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="R51" s="2" t="inlineStr">
+      <c r="R61" s="2" t="inlineStr">
         <is>
           <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
-      <c r="S51" s="2" t="inlineStr">
+      <c r="S61" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="T51" s="2" t="inlineStr">
+      <c r="T61" s="2" t="inlineStr">
         <is>
           <t>免許行政庁: 神奈川県; 免許番号: 第000198号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T51"/>
+  <autoFilter ref="A1:T61"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -5940,78 +6960,90 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P45" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P50" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P45" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P50" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P52" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P53" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P54" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P55" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P56" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P57" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P58" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P59" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P60" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P61" r:id="rId122"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId111"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId123"/>
   </tableParts>
 </worksheet>
 </file>
@@ -6022,7 +7054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T42"/>
+  <dimension ref="A1:T52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6152,12 +7184,12 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-11-00000122</t>
+          <t>RE-MLIT-12-00000283</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>三幸土地建物株式会社</t>
+          <t>ミドリ不動産株式会社</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -6167,7 +7199,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -6177,7 +7209,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -6227,12 +7259,12 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -6247,19 +7279,19 @@
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 埼玉県; 免許番号: 第000122号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 千葉県; 免許番号: 第000283号; 自動追加日: 2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-11-00000152</t>
+          <t>RE-MLIT-12-00000271</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>大和屋株式会社</t>
+          <t>丸正商事株式会社</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -6269,7 +7301,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -6279,7 +7311,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -6329,12 +7361,12 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -6349,19 +7381,19 @@
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 埼玉県; 免許番号: 第000152号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 千葉県; 免許番号: 第000271号; 自動追加日: 2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-11-00000101</t>
+          <t>RE-MLIT-12-00000119</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>有限会社旭商事</t>
+          <t>北葉開発株式会社</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -6371,7 +7403,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -6381,7 +7413,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6431,12 +7463,12 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -6451,19 +7483,19 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 埼玉県; 免許番号: 第000101号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 千葉県; 免許番号: 第000119号; 自動追加日: 2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-11-00000079</t>
+          <t>RE-MLIT-12-00000001</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>株式会社三井商事</t>
+          <t>千葉復興株式会社</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -6473,7 +7505,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -6483,7 +7515,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6533,12 +7565,12 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
@@ -6553,19 +7585,19 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 埼玉県; 免許番号: 第000079号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 千葉県; 免許番号: 第000001号; 自動追加日: 2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-11-00000126</t>
+          <t>RE-MLIT-12-00000120</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>株式会社日和商事</t>
+          <t>小湊鉄道株式会社</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -6575,7 +7607,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -6585,7 +7617,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6635,12 +7667,12 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
@@ -6655,19 +7687,19 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 埼玉県; 免許番号: 第000126号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 千葉県; 免許番号: 第000120号; 自動追加日: 2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-11-00000047</t>
+          <t>RE-MLIT-12-00000292</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>株式会社石井不動産</t>
+          <t>常南土地株式会社</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -6677,7 +7709,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -6687,7 +7719,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6737,12 +7769,12 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
@@ -6757,19 +7789,19 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 埼玉県; 免許番号: 第000047号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 千葉県; 免許番号: 第000292号; 自動追加日: 2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RE-0009</t>
+          <t>RE-MLIT-12-00000298</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>武蔵コーポレーション株式会社</t>
+          <t>日東不動産株式会社</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -6779,77 +7811,77 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>埼玉県さいたま市大宮区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>関東中心</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>一棟アパート・マンション・ビル・賃貸管理</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>https://www.musashi-corporation.com/</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>https://www.musashi-corporation.com/qa/investment_consultation.php</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>https://www.musashi-corporation.com/sell-feature/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>048-788-5636</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>収益不動産の売買・管理・出口戦略に特化</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>https://www.musashi-corporation.com/sell-feature/ | https://www.musashi-corporation.com/qa/investment_consultation.php</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -6859,19 +7891,19 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>居住用戸建て仲介は対象外として整理</t>
+          <t>免許行政庁: 千葉県; 免許番号: 第000298号; 自動追加日: 2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-11-00000001</t>
+          <t>RE-MLIT-12-00000184</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>武藏野土地株式会社</t>
+          <t>有限会社京葉ビル</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -6881,7 +7913,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -6891,7 +7923,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6941,12 +7973,12 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
@@ -6961,19 +7993,19 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 埼玉県; 免許番号: 第000001号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 千葉県; 免許番号: 第000184号; 自動追加日: 2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-11-00000003</t>
+          <t>RE-MLIT-12-00000234</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>福岡土地有限会社</t>
+          <t>有限会社川崎不動産</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -6983,7 +8015,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -6993,7 +8025,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7043,12 +8075,12 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
@@ -7063,19 +8095,19 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 埼玉県; 免許番号: 第000003号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 千葉県; 免許番号: 第000234号; 自動追加日: 2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-11-00000030</t>
+          <t>RE-MLIT-12-00000286</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>近藤不動産株式会社</t>
+          <t>株式会社富士見地所</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -7085,7 +8117,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -7095,7 +8127,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7145,12 +8177,12 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
@@ -7165,19 +8197,19 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 埼玉県; 免許番号: 第000030号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 千葉県; 免許番号: 第000286号; 自動追加日: 2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-11-00000060</t>
+          <t>RE-MLIT-11-00000122</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ＫＭ不動産株式会社</t>
+          <t>三幸土地建物株式会社</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -7267,19 +8299,19 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 埼玉県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000122号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>RE-0019</t>
+          <t>RE-MLIT-11-00000152</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>みずほ不動産販売株式会社</t>
+          <t>大和屋株式会社</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -7289,99 +8321,99 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>東京都中央区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>首都圏・北海道・東北・中部・関西・中国・九州</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・事業用・相続・資産活用</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://www.mizuho-re.co.jp/</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mizuho-re.co.jp/contact/</t>
+          <t>https://www.yamatoya-kk.co.jp/saiyou/</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>https://www.mizuho-re.co.jp/buy/investment/</t>
+          <t>https://www.yamatoya-kk.co.jp/saiyou/</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>048-522-8611</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>全国拠点と金融グループ連携による不動産仲介</t>
+          <t>公式サイトを自動確認</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>https://www.mizuho-re.co.jp/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1 | https://www.yamatoya-kk.co.jp/saiyou/</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>一部自動確認</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>投資用サービスURLは定期リンク確認が必要</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000152号; 自動追加日: 2026-07-21; 公式サイト自動確認日: 2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000114</t>
+          <t>RE-MLIT-11-00000101</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>レイモンド不動産 株式会社</t>
+          <t>有限会社旭商事</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -7391,7 +8423,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -7401,7 +8433,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7451,12 +8483,12 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
@@ -7471,19 +8503,19 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000114号; 自動追加日: 2026-07-16</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000101号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>RE-0001</t>
+          <t>RE-MLIT-11-00000079</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>三井不動産リアルティ株式会社</t>
+          <t>株式会社三井商事</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -7493,77 +8525,77 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>東京都千代田区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>全国</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・事業用・賃貸管理・資産活用</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mf-realty.jp/</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>https://pro.mf-realty.jp/otherInquiry/input/</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>https://pro.mf-realty.jp/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0120-921-582</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>居住用仲介と投資・収益不動産の専門サービスを展開</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>https://pro.mf-realty.jp/ | https://pro.mf-realty.jp/otherInquiry/input/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -7573,19 +8605,19 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>投資用戸建てを含む物件種別は個別検索で追加確認可能</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000079号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>RE-0018</t>
+          <t>RE-MLIT-11-00000126</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>三菱UFJ不動産販売株式会社</t>
+          <t>株式会社日和商事</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -7595,52 +8627,52 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>東京都千代田区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>首都圏・名古屋・関西</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・投資事業用・相続</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sumai1.com/</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sumai1.com/contact/</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sumai1.com/buyers/investment/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7650,44 +8682,44 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>金融グループ系の仲介・資産承継・投資用不動産対応</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>https://www.sumai1.com/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>サービスURLと問い合わせURLの定期リンク確認が必要</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000126号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>RE-0002</t>
+          <t>RE-MLIT-11-00000047</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>住友不動産ステップ株式会社</t>
+          <t>株式会社石井不動産</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -7697,77 +8729,77 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>東京都新宿区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>全国</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・一棟マンション・アパート・ビル</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>https://www.stepon.co.jp/</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>https://www.stepon.co.jp/contact/</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>https://www.stepon.co.jp/pro/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0120-566-742</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>全国ネットワークで居住用・投資用不動産を仲介</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>https://www.stepon.co.jp/pro/area_13/list_13_115/cs_25_06/ | https://www.stepon.co.jp/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -7777,19 +8809,19 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>問い合わせURLは総合窓口。物件ページにも資料請求フォームあり</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000047号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000212</t>
+          <t>RE-0009</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>日本不動産 株式会社</t>
+          <t>武蔵コーポレーション株式会社</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -7799,77 +8831,77 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>埼玉県さいたま市大宮区</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>関東中心</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>一棟アパート・マンション・ビル・賃貸管理</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.musashi-corporation.com/</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.musashi-corporation.com/qa/investment_consultation.php</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.musashi-corporation.com/sell-feature/</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>048-788-5636</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>収益不動産の売買・管理・出口戦略に特化</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://www.musashi-corporation.com/sell-feature/ | https://www.musashi-corporation.com/qa/investment_consultation.php</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>確認済み</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -7879,19 +8911,19 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000212号; 自動追加日: 2026-07-16</t>
+          <t>居住用戸建て仲介は対象外として整理</t>
         </is>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000170</t>
+          <t>RE-MLIT-11-00000001</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>有限会社 マルミ商事</t>
+          <t>武藏野土地株式会社</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -7901,7 +8933,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -7911,7 +8943,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7961,12 +8993,12 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
@@ -7981,19 +9013,19 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000170号; 自動追加日: 2026-07-16</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000001号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>RE-0003</t>
+          <t>RE-MLIT-11-00000003</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>東急リバブル株式会社</t>
+          <t>福岡土地有限会社</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -8003,77 +9035,77 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>東京都渋谷区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>首都圏・札幌・仙台・名古屋・関西・福岡ほか</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・一棟収益・事業用・賃貸</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>https://www.livable.co.jp/</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>https://www.livable.co.jp/branch/toushi-support/</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>https://www.livable.co.jp/fudosan-toushi-baikyaku/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0120-992-151</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>投資サポートセンターと全国店舗網を持つ</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>https://www.livable.co.jp/branch/toushi-support/ | https://www.livable.co.jp/fudosan-toushi-baikyaku/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -8083,19 +9115,19 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>投資用不動産専用窓口あり</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000003号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000044</t>
+          <t>RE-MLIT-11-00000030</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>栗城建設興業 株式会社</t>
+          <t>近藤不動産株式会社</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -8105,7 +9137,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -8115,7 +9147,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8165,12 +9197,12 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
@@ -8185,19 +9217,19 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000044号; 自動追加日: 2026-07-16</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000030号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000164</t>
+          <t>RE-MLIT-11-00000060</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>株式会社 なかやま不動産</t>
+          <t>ＫＭ不動産株式会社</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -8207,7 +9239,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -8217,7 +9249,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8267,12 +9299,12 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
@@ -8287,19 +9319,19 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000164号; 自動追加日: 2026-07-16</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000098</t>
+          <t>RE-0019</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>株式会社 三和不動産鑑定事務所</t>
+          <t>みずほ不動産販売株式会社</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -8314,47 +9346,47 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>東京都中央区</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>首都圏・北海道・東北・中部・関西・中国・九州</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>マンション・土地・事業用・相続・資産活用</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mizuho-re.co.jp/</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mizuho-re.co.jp/contact/</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mizuho-re.co.jp/buy/investment/</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8364,44 +9396,44 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>全国拠点と金融グループ連携による不動産仲介</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://www.mizuho-re.co.jp/</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>一部確認</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000098号; 自動追加日: 2026-07-16</t>
+          <t>投資用サービスURLは定期リンク確認が必要</t>
         </is>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000001</t>
+          <t>RE-MLIT-13-00000114</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>株式会社 三富不動産</t>
+          <t>レイモンド不動産 株式会社</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -8491,19 +9523,19 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000001号; 自動追加日: 2026-07-16</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000114号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000093</t>
+          <t>RE-0001</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>株式会社 伊藤商会</t>
+          <t>三井不動産リアルティ株式会社</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -8518,72 +9550,72 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>東京都千代田区</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>全国</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>マンション・土地・事業用・賃貸管理・資産活用</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mf-realty.jp/</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>https://pro.mf-realty.jp/otherInquiry/input/</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>https://pro.mf-realty.jp/</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>0120-921-582</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>居住用仲介と投資・収益不動産の専門サービスを展開</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://pro.mf-realty.jp/ | https://pro.mf-realty.jp/otherInquiry/input/</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>確認済み</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -8593,19 +9625,19 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000093号; 自動追加日: 2026-07-16</t>
+          <t>投資用戸建てを含む物件種別は個別検索で追加確認可能</t>
         </is>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000060</t>
+          <t>RE-0018</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>株式会社 長岡建設</t>
+          <t>三菱UFJ不動産販売株式会社</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -8620,47 +9652,47 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>東京都千代田区</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>首都圏・名古屋・関西</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>マンション・土地・投資事業用・相続</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sumai1.com/</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sumai1.com/contact/</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sumai1.com/buyers/investment/</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8670,44 +9702,44 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>金融グループ系の仲介・資産承継・投資用不動産対応</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://www.sumai1.com/</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>一部確認</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000060号; 自動追加日: 2026-07-16</t>
+          <t>サービスURLと問い合わせURLの定期リンク確認が必要</t>
         </is>
       </c>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>RE-0020</t>
+          <t>RE-0002</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>株式会社GA technologies（RENOSY）</t>
+          <t>住友不動産ステップ株式会社</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -8722,17 +9754,17 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>東京都港区</t>
+          <t>東京都新宿区</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>全国オンライン中心</t>
+          <t>全国</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -8742,7 +9774,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>投資用マンション・賃貸管理・売却</t>
+          <t>マンション・土地・一棟マンション・アパート・ビル</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8752,32 +9784,32 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>https://www.renosy.com/</t>
+          <t>https://www.stepon.co.jp/</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>https://www.renosy.com/contact</t>
+          <t>https://www.stepon.co.jp/contact/</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>https://www.renosy.com/asset</t>
+          <t>https://www.stepon.co.jp/pro/</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>0120-566-742</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>オンラインを中心とした不動産投資サービス</t>
+          <t>全国ネットワークで居住用・投資用不動産を仲介</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>https://www.renosy.com/</t>
+          <t>https://www.stepon.co.jp/pro/area_13/list_13_115/cs_25_06/ | https://www.stepon.co.jp/</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8787,29 +9819,29 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>確認済み</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>戸建て仲介ではなく区分マンション投資中心</t>
+          <t>問い合わせURLは総合窓口。物件ページにも資料請求フォームあり</t>
         </is>
       </c>
     </row>
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>RE-0006</t>
+          <t>RE-MLIT-13-00000212</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>株式会社オープンハウス</t>
+          <t>日本不動産 株式会社</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -8824,72 +9856,72 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>東京都渋谷区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>東京・神奈川・埼玉・千葉・愛知・大阪・兵庫・福岡ほか</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>新築戸建て・土地・マンション・国内外投資</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>https://oh.openhouse-group.com/</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>https://oh.openhouse-group.com/contact/</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>https://oh.openhouse-group.com/s-kodate/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>03-6213-0775</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>都市部の戸建て供給とグループの不動産投資事業</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>https://oh.openhouse-group.com/company/about/ | https://oh.openhouse-group.com/s-kodate/saitama/ | https://wm.openhouse-group.com/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -8899,19 +9931,19 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>国内収益物件の一般顧客向け窓口はグループ各社も確認</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000212号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="29" ht="42" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>RE-0007</t>
+          <t>RE-MLIT-13-00000170</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>株式会社オープンハウス・リアルエステート</t>
+          <t>有限会社 マルミ商事</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -8926,12 +9958,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>東京都千代田区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>首都圏・関西・名古屋</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8941,57 +9973,57 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>一棟マンション・アパート・ビル・土地</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>https://ohre.openhouse-group.com/</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>https://ohre.openhouse-group.com/</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>https://shueki.ohd.openhouse-group.com/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>03-6854-7452</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>収益不動産の仕入れ・再生・売買に対応</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>https://ohre.openhouse-group.com/ | https://shueki.ohd.openhouse-group.com/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -9001,19 +10033,19 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>戸建ての直接取扱は追加確認</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000170号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="30" ht="42" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>RE-0008</t>
+          <t>RE-0003</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>株式会社ランドネット</t>
+          <t>東急リバブル株式会社</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -9028,12 +10060,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>東京都豊島区</t>
+          <t>東京都渋谷区</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>東京・横浜・大阪・福岡ほか</t>
+          <t>首都圏・札幌・仙台・名古屋・関西・福岡ほか</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9048,7 +10080,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>中古マンション・賃貸管理・買取・リフォーム</t>
+          <t>マンション・土地・一棟収益・事業用・賃貸</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9058,32 +10090,32 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>https://landnet.co.jp/</t>
+          <t>https://www.livable.co.jp/</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>https://landnet.co.jp/contact/</t>
+          <t>https://www.livable.co.jp/branch/toushi-support/</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>https://landnet.co.jp/housing-search/</t>
+          <t>https://www.livable.co.jp/fudosan-toushi-baikyaku/</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0120-012-461</t>
+          <t>0120-992-151</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>投資用中古マンションと居住用不動産をワンストップで扱う</t>
+          <t>投資サポートセンターと全国店舗網を持つ</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>https://landnet.co.jp/ | https://landnet.co.jp/contact/ | https://landnet.co.jp/housing-search/kanagawa/yamato-shi</t>
+          <t>https://www.livable.co.jp/branch/toushi-support/ | https://www.livable.co.jp/fudosan-toushi-baikyaku/</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9103,19 +10135,19 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>戸建て掲載状況はエリアにより異なる</t>
+          <t>投資用不動産専用窓口あり</t>
         </is>
       </c>
     </row>
     <row r="31" ht="42" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-13-00000218</t>
+          <t>RE-MLIT-13-00000044</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>西武建設 株式会社</t>
+          <t>栗城建設興業 株式会社</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -9205,19 +10237,19 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 東京都; 免許番号: 第000218号; 自動追加日: 2026-07-16</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000044号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>RE-0004</t>
+          <t>RE-MLIT-13-00000164</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>野村不動産ソリューションズ株式会社</t>
+          <t>株式会社 なかやま不動産</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -9232,47 +10264,47 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>東京都新宿区</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>首都圏・関西・名古屋ほか</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・一棟マンション・アパート・事業用</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nomura-solutions.co.jp/</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nomu.com/pro/contact/</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nomu.com/pro/house/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9282,22 +10314,22 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ノムコム・プロで投資用戸建て・収益物件を掲載</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>https://www.nomu.com/pro/house/area/1311/ | https://www.nomu.com/pro/contents/knowhow/20240919.html</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -9307,19 +10339,19 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>問い合わせ先は物件・担当センターごとに異なる</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000164号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="33" ht="42" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000181</t>
+          <t>RE-MLIT-13-00000098</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>大栄興業 株式会社</t>
+          <t>株式会社 三和不動産鑑定事務所</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -9329,7 +10361,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -9339,7 +10371,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -9389,12 +10421,12 @@
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
@@ -9409,19 +10441,19 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000181号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000098号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="34" ht="42" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000260</t>
+          <t>RE-MLIT-13-00000001</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>有限会社 協和商事</t>
+          <t>株式会社 三富不動産</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -9431,7 +10463,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -9441,7 +10473,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9491,12 +10523,12 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
@@ -9511,19 +10543,19 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000260号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000001号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="35" ht="42" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000365</t>
+          <t>RE-MLIT-13-00000093</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>有限会社 小沢建設商事</t>
+          <t>株式会社 伊藤商会</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -9533,7 +10565,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -9543,7 +10575,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9593,12 +10625,12 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
@@ -9613,19 +10645,19 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000365号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000093号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="36" ht="42" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000162</t>
+          <t>RE-MLIT-13-00000060</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>有限会社 濱屋</t>
+          <t>株式会社 長岡建設</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -9635,7 +10667,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -9645,7 +10677,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9695,12 +10727,12 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
@@ -9715,19 +10747,19 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000162号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000060号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="37" ht="42" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000071</t>
+          <t>RE-0020</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>東栄商事 株式会社</t>
+          <t>株式会社GA technologies（RENOSY）</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -9737,52 +10769,52 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>東京都港区</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>全国オンライン中心</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>投資用マンション・賃貸管理・売却</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>https://www.renosy.com/</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>https://www.renosy.com/contact</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>https://www.renosy.com/asset</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9792,44 +10824,44 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>オンラインを中心とした不動産投資サービス</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://www.renosy.com/</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>一部確認</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000071号; 自動追加日: 2026-07-21</t>
+          <t>戸建て仲介ではなく区分マンション投資中心</t>
         </is>
       </c>
     </row>
     <row r="38" ht="42" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000060</t>
+          <t>RE-0006</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>東横不動産 株式会社</t>
+          <t>株式会社オープンハウス</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -9839,77 +10871,77 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>東京都渋谷区</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京・神奈川・埼玉・千葉・愛知・大阪・兵庫・福岡ほか</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>新築戸建て・土地・マンション・国内外投資</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>https://oh.openhouse-group.com/</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>https://oh.openhouse-group.com/contact/</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>https://oh.openhouse-group.com/s-kodate/</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>03-6213-0775</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>都市部の戸建て供給とグループの不動産投資事業</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://oh.openhouse-group.com/company/about/ | https://oh.openhouse-group.com/s-kodate/saitama/ | https://wm.openhouse-group.com/</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>一部確認</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
@@ -9919,19 +10951,19 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
+          <t>国内収益物件の一般顧客向け窓口はグループ各社も確認</t>
         </is>
       </c>
     </row>
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000013</t>
+          <t>RE-0007</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>株式会社 大谷商事</t>
+          <t>株式会社オープンハウス・リアルエステート</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -9941,17 +10973,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>東京都千代田区</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>首都圏・関西・名古屋</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9961,57 +10993,57 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>一棟マンション・アパート・ビル・土地</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>https://ohre.openhouse-group.com/</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>https://ohre.openhouse-group.com/</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>https://shueki.ohd.openhouse-group.com/</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>03-6854-7452</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>収益不動産の仕入れ・再生・売買に対応</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://ohre.openhouse-group.com/ | https://shueki.ohd.openhouse-group.com/</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>確認済み</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
@@ -10021,19 +11053,19 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000013号; 自動追加日: 2026-07-21</t>
+          <t>戸建ての直接取扱は追加確認</t>
         </is>
       </c>
     </row>
     <row r="40" ht="42" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000024</t>
+          <t>RE-0008</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>浅間建設 株式会社</t>
+          <t>株式会社ランドネット</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -10043,77 +11075,77 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>東京都豊島区</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京・横浜・大阪・福岡ほか</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>中古マンション・賃貸管理・買取・リフォーム</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>https://landnet.co.jp/</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>https://landnet.co.jp/contact/</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>https://landnet.co.jp/housing-search/</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>0120-012-461</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>投資用中古マンションと居住用不動産をワンストップで扱う</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://landnet.co.jp/ | https://landnet.co.jp/contact/ | https://landnet.co.jp/housing-search/kanagawa/yamato-shi</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>確認済み</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
@@ -10123,19 +11155,19 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000024号; 自動追加日: 2026-07-21</t>
+          <t>戸建て掲載状況はエリアにより異なる</t>
         </is>
       </c>
     </row>
     <row r="41" ht="42" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000066</t>
+          <t>RE-MLIT-13-00000218</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>相澤土地 株式会社</t>
+          <t>西武建設 株式会社</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -10145,7 +11177,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -10155,7 +11187,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10205,12 +11237,12 @@
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=13&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
@@ -10225,114 +11257,1134 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000066号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 東京都; 免許番号: 第000218号; 自動追加日: 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="42" ht="42" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>RE-0004</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>野村不動産ソリューションズ株式会社</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>東京都新宿区</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>首都圏・関西・名古屋ほか</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>マンション・土地・一棟マンション・アパート・事業用</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nomura-solutions.co.jp/</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nomu.com/pro/contact/</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nomu.com/pro/house/</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>ノムコム・プロで投資用戸建て・収益物件を掲載</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nomu.com/pro/house/area/1311/ | https://www.nomu.com/pro/contents/knowhow/20240919.html</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>確認済み</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>問い合わせ先は物件・担当センターごとに異なる</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="42" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000181</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>大栄興業 株式会社</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000181号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="42" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000260</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>有限会社 協和商事</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000260号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000365</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>有限会社 小沢建設商事</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000365号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="42" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000162</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>有限会社 濱屋</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000162号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="42" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000071</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>東栄商事 株式会社</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000071号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="42" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000060</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>東横不動産 株式会社</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="42" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000013</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>株式会社 大谷商事</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000013号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="42" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000024</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>浅間建設 株式会社</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000024号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="42" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-14-00000066</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>相澤土地 株式会社</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000066号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="42" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
           <t>RE-MLIT-14-00000198</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>親和商事 有限会社</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>関東</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>神奈川県</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>神奈川県</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
         <is>
           <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
-      <c r="P42" s="3" t="inlineStr">
+      <c r="P52" s="3" t="inlineStr">
         <is>
           <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
-      <c r="Q42" s="2" t="inlineStr">
+      <c r="Q52" s="2" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="R42" s="2" t="inlineStr">
+      <c r="R52" s="2" t="inlineStr">
         <is>
           <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
-      <c r="S42" s="2" t="inlineStr">
+      <c r="S52" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="T42" s="2" t="inlineStr">
+      <c r="T52" s="2" t="inlineStr">
         <is>
           <t>免許行政庁: 神奈川県; 免許番号: 第000198号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T42"/>
+  <autoFilter ref="A1:T52"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId2"/>
@@ -10340,78 +12392,90 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P45" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P50" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P52" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId75"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId87"/>
   </tableParts>
 </worksheet>
 </file>

--- a/database/real_estate_brokers.xlsx
+++ b/database/real_estate_brokers.xlsx
@@ -17,8 +17,8 @@
     <sheet name="データ辞書" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全社一覧'!$A$1:$T$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'関東'!$A$1:$T$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全社一覧'!$A$1:$T$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'関東'!$A$1:$T$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'北海道・東北'!$A$1:$T$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'近畿'!$A$1:$T$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'中国・四国'!$A$1:$T$2</definedName>
@@ -177,8 +177,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_9e7587520fcb" displayName="T_9e7587520fcb" ref="A1:T61" headerRowCount="1">
-  <autoFilter ref="A1:T61"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_9e7587520fcb" displayName="T_9e7587520fcb" ref="A1:T71" headerRowCount="1">
+  <autoFilter ref="A1:T71"/>
   <tableColumns count="20">
     <tableColumn id="1" name="会社ID"/>
     <tableColumn id="2" name="会社名"/>
@@ -206,8 +206,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_92ae89f64a96" displayName="T_92ae89f64a96" ref="A1:T52" headerRowCount="1">
-  <autoFilter ref="A1:T52"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_92ae89f64a96" displayName="T_92ae89f64a96" ref="A1:T62" headerRowCount="1">
+  <autoFilter ref="A1:T62"/>
   <tableColumns count="20">
     <tableColumn id="1" name="会社ID"/>
     <tableColumn id="2" name="会社名"/>
@@ -668,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T61"/>
+  <dimension ref="A1:T71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2164,52 +2164,52 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>土地・事業用</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>https://ja.wikipedia.org/wiki/%E5%B0%8F%E6%B9%8A%E9%89%84%E9%81%93</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>https://ja.wikipedia.org/wiki/Wikipedia:%E9%80%A3%E7%B5%A1%E5%85%88</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>https://ja.wikipedia.org/wiki/%E5%B0%8F%E6%B9%8A%E9%89%84%E9%81%93</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>04000105392</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>公式サイトを自動確認。問い合わせ導線あり</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1 | https://ja.wikipedia.org/wiki/%E5%B0%8F%E6%B9%8A%E9%89%84%E9%81%93 | https://ja.wikipedia.org/wiki/Wikipedia:%E9%80%A3%E7%B5%A1%E5%85%88</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>自動確認済み</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 千葉県; 免許番号: 第000120号; 自動追加日: 2026-07-22</t>
+          <t>免許行政庁: 千葉県; 免許番号: 第000120号; 自動追加日: 2026-07-22; 公式サイト自動確認日: 2026-07-23</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>事業用</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2478,9 +2478,9 @@
           <t>要確認</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>https://estate.sesh.jp/corp/detail/108313</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2488,9 +2488,9 @@
           <t>要確認</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>https://estate.sesh.jp/corp/detail/108313</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2500,22 +2500,22 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>公式サイトを自動確認</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1 | https://estate.sesh.jp/corp/detail/108313</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>一部自動確認</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 千葉県; 免許番号: 第000184号; 自動追加日: 2026-07-22</t>
+          <t>免許行政庁: 千葉県; 免許番号: 第000184号; 自動追加日: 2026-07-22; 公式サイト自動確認日: 2026-07-23</t>
         </is>
       </c>
     </row>
@@ -6915,8 +6915,1028 @@
         </is>
       </c>
     </row>
+    <row r="62" ht="42" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000204</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>一般財団法人笠間市開発公社</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000204号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="42" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000014</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>下館土地株式会社</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000014号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="42" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000167</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>公益財団法人茨城県開発公社</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000167号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="42" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000036</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>平和不動産株式会社</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000036号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="42" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000106</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>有限会社岩田不動産</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P66" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000106号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="42" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000058</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>有限会社栄進</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S67" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T67" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000058号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="42" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000021</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>有限会社高橋商事</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T68" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000021号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="42" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000110</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>株式会社野口物産</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T69" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000110号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="42" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000109</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>関友商事株式会社</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P70" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000109号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="42" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000203</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>関東鉄道株式会社</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000203号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T61"/>
+  <autoFilter ref="A1:T71"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -6958,92 +7978,107 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P45" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P50" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P52" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P53" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P54" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P55" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P56" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P57" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P58" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P59" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P60" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P61" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P45" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P50" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P52" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P53" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P54" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P55" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P56" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P57" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P58" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P59" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P60" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P61" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P62" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P63" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P64" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P65" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P66" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P67" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P70" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P71" r:id="rId137"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId123"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId138"/>
   </tableParts>
 </worksheet>
 </file>
@@ -7054,7 +8089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T52"/>
+  <dimension ref="A1:T62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7632,52 +8667,52 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>土地・事業用</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>https://ja.wikipedia.org/wiki/%E5%B0%8F%E6%B9%8A%E9%89%84%E9%81%93</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>https://ja.wikipedia.org/wiki/Wikipedia:%E9%80%A3%E7%B5%A1%E5%85%88</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>https://ja.wikipedia.org/wiki/%E5%B0%8F%E6%B9%8A%E9%89%84%E9%81%93</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>04000105392</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>公式サイトを自動確認。問い合わせ導線あり</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1 | https://ja.wikipedia.org/wiki/%E5%B0%8F%E6%B9%8A%E9%89%84%E9%81%93 | https://ja.wikipedia.org/wiki/Wikipedia:%E9%80%A3%E7%B5%A1%E5%85%88</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>自動確認済み</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -7687,7 +8722,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 千葉県; 免許番号: 第000120号; 自動追加日: 2026-07-22</t>
+          <t>免許行政庁: 千葉県; 免許番号: 第000120号; 自動追加日: 2026-07-22; 公式サイト自動確認日: 2026-07-23</t>
         </is>
       </c>
     </row>
@@ -7938,7 +8973,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>事業用</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7946,9 +8981,9 @@
           <t>要確認</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>https://estate.sesh.jp/corp/detail/108313</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -7956,9 +8991,9 @@
           <t>要確認</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>https://estate.sesh.jp/corp/detail/108313</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7968,22 +9003,22 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>公式サイトを自動確認</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1 | https://estate.sesh.jp/corp/detail/108313</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>一部自動確認</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -7993,7 +9028,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 千葉県; 免許番号: 第000184号; 自動追加日: 2026-07-22</t>
+          <t>免許行政庁: 千葉県; 免許番号: 第000184号; 自動追加日: 2026-07-22; 公式サイト自動確認日: 2026-07-23</t>
         </is>
       </c>
     </row>
@@ -12383,99 +13418,1134 @@
         </is>
       </c>
     </row>
+    <row r="53" ht="42" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000204</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>一般財団法人笠間市開発公社</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000204号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="42" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000014</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>下館土地株式会社</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000014号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="42" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000167</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>公益財団法人茨城県開発公社</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000167号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="42" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000036</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>平和不動産株式会社</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000036号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="42" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000106</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>有限会社岩田不動産</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000106号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="42" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000058</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>有限会社栄進</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000058号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="42" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000021</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>有限会社高橋商事</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000021号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="42" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000110</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>株式会社野口物産</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000110号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="42" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000109</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>関友商事株式会社</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000109号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="42" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000203</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>関東鉄道株式会社</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000203号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T52"/>
+  <autoFilter ref="A1:T62"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P45" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P50" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P52" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P45" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P50" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P52" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P53" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P54" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P55" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P56" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P57" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P58" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P59" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P60" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P61" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P62" r:id="rId101"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId87"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId102"/>
   </tableParts>
 </worksheet>
 </file>

--- a/database/real_estate_brokers.xlsx
+++ b/database/real_estate_brokers.xlsx
@@ -17,8 +17,8 @@
     <sheet name="データ辞書" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全社一覧'!$A$1:$T$71</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'関東'!$A$1:$T$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全社一覧'!$A$1:$T$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'関東'!$A$1:$T$72</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'北海道・東北'!$A$1:$T$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'近畿'!$A$1:$T$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'中国・四国'!$A$1:$T$2</definedName>
@@ -177,8 +177,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_9e7587520fcb" displayName="T_9e7587520fcb" ref="A1:T71" headerRowCount="1">
-  <autoFilter ref="A1:T71"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_9e7587520fcb" displayName="T_9e7587520fcb" ref="A1:T81" headerRowCount="1">
+  <autoFilter ref="A1:T81"/>
   <tableColumns count="20">
     <tableColumn id="1" name="会社ID"/>
     <tableColumn id="2" name="会社名"/>
@@ -206,8 +206,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_92ae89f64a96" displayName="T_92ae89f64a96" ref="A1:T62" headerRowCount="1">
-  <autoFilter ref="A1:T62"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_92ae89f64a96" displayName="T_92ae89f64a96" ref="A1:T72" headerRowCount="1">
+  <autoFilter ref="A1:T72"/>
   <tableColumns count="20">
     <tableColumn id="1" name="会社ID"/>
     <tableColumn id="2" name="会社名"/>
@@ -668,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T71"/>
+  <dimension ref="A1:T81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5898,12 +5898,12 @@
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000181</t>
+          <t>RE-MLIT-09-00000002</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>大栄興業 株式会社</t>
+          <t>丸栃不動産倉庫 株式会社</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr">
@@ -5993,19 +5993,19 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000181号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000002号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="53" ht="42" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000260</t>
+          <t>RE-MLIT-09-00000064</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>有限会社 協和商事</t>
+          <t>前田不動産 株式会社</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6075,12 +6075,12 @@
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R53" s="2" t="inlineStr">
@@ -6095,19 +6095,19 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000260号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000064号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="54" ht="42" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000365</t>
+          <t>RE-MLIT-09-00000108</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>有限会社 小沢建設商事</t>
+          <t>協立不動産 株式会社</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6177,12 +6177,12 @@
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr">
@@ -6197,19 +6197,19 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000365号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000108号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="55" ht="42" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000162</t>
+          <t>RE-MLIT-09-00000159</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>有限会社 濱屋</t>
+          <t>大国不動産 株式会社</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R55" s="2" t="inlineStr">
@@ -6299,19 +6299,19 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000162号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000159号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="56" ht="42" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000071</t>
+          <t>RE-MLIT-09-00000168</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>東栄商事 株式会社</t>
+          <t>小山土地建物 株式会社</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R56" s="2" t="inlineStr">
@@ -6401,19 +6401,19 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000071号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000168号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="57" ht="42" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000060</t>
+          <t>RE-MLIT-09-00000062</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>東横不動産 株式会社</t>
+          <t>小金井不動産 株式会社</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R57" s="2" t="inlineStr">
@@ -6503,19 +6503,19 @@
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000062号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="58" ht="42" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000013</t>
+          <t>RE-MLIT-09-00000054</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>株式会社 大谷商事</t>
+          <t>昭和商事 株式会社</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R58" s="2" t="inlineStr">
@@ -6605,19 +6605,19 @@
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000013号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000054号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="59" ht="42" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000024</t>
+          <t>RE-MLIT-09-00000022</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>浅間建設 株式会社</t>
+          <t>有限会社 カワシマ不動産</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6687,12 +6687,12 @@
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R59" s="2" t="inlineStr">
@@ -6707,19 +6707,19 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000024号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000022号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="60" ht="42" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000066</t>
+          <t>RE-MLIT-09-00000182</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>相澤土地 株式会社</t>
+          <t>有限会社 東栄不動産</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -6789,12 +6789,12 @@
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R60" s="2" t="inlineStr">
@@ -6809,19 +6809,19 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000066号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000182号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000198</t>
+          <t>RE-MLIT-09-00000117</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>親和商事 有限会社</t>
+          <t>株式会社 万建設興業</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R61" s="2" t="inlineStr">
@@ -6911,19 +6911,19 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000198号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000117号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="62" ht="42" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000204</t>
+          <t>RE-MLIT-14-00000181</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>一般財団法人笠間市開発公社</t>
+          <t>大栄興業 株式会社</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -6993,12 +6993,12 @@
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R62" s="2" t="inlineStr">
@@ -7013,19 +7013,19 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000204号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000181号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000014</t>
+          <t>RE-MLIT-14-00000260</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>下館土地株式会社</t>
+          <t>有限会社 協和商事</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R63" s="2" t="inlineStr">
@@ -7115,19 +7115,19 @@
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000014号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000260号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000167</t>
+          <t>RE-MLIT-14-00000365</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>公益財団法人茨城県開発公社</t>
+          <t>有限会社 小沢建設商事</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr">
@@ -7217,19 +7217,19 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000167号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000365号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="65" ht="42" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000036</t>
+          <t>RE-MLIT-14-00000162</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>平和不動産株式会社</t>
+          <t>有限会社 濱屋</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -7249,7 +7249,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R65" s="2" t="inlineStr">
@@ -7319,19 +7319,19 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000036号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000162号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="66" ht="42" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000106</t>
+          <t>RE-MLIT-14-00000071</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>有限会社岩田不動産</t>
+          <t>東栄商事 株式会社</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R66" s="2" t="inlineStr">
@@ -7421,19 +7421,19 @@
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000106号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000071号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="67" ht="42" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000058</t>
+          <t>RE-MLIT-14-00000060</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>有限会社栄進</t>
+          <t>東横不動産 株式会社</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="P67" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R67" s="2" t="inlineStr">
@@ -7523,19 +7523,19 @@
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000058号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="68" ht="42" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000021</t>
+          <t>RE-MLIT-14-00000013</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>有限会社高橋商事</t>
+          <t>株式会社 大谷商事</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R68" s="2" t="inlineStr">
@@ -7625,19 +7625,19 @@
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000021号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000013号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="69" ht="42" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000110</t>
+          <t>RE-MLIT-14-00000024</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>株式会社野口物産</t>
+          <t>浅間建設 株式会社</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R69" s="2" t="inlineStr">
@@ -7727,19 +7727,19 @@
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000110号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000024号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="70" ht="42" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000109</t>
+          <t>RE-MLIT-14-00000066</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>関友商事株式会社</t>
+          <t>相澤土地 株式会社</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -7749,7 +7749,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -7809,12 +7809,12 @@
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R70" s="2" t="inlineStr">
@@ -7829,114 +7829,1134 @@
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000109号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000066号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="71" ht="42" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>RE-MLIT-14-00000198</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>親和商事 有限会社</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000198号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="42" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000204</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>一般財団法人笠間市開発公社</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P72" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000204号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="42" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000014</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>下館土地株式会社</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000014号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="42" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000167</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>公益財団法人茨城県開発公社</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P74" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T74" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000167号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="42" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000036</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>平和不動産株式会社</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P75" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S75" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T75" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000036号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="42" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000106</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>有限会社岩田不動産</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P76" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000106号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="42" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000058</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>有限会社栄進</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P77" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S77" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T77" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000058号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="42" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000021</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>有限会社高橋商事</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P78" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S78" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T78" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000021号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="42" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000110</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>株式会社野口物産</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P79" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S79" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T79" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000110号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="42" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000109</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>関友商事株式会社</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P80" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S80" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T80" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000109号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="42" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
           <t>RE-MLIT-08-00000203</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>関東鉄道株式会社</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>関東</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="O71" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
         <is>
           <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
-      <c r="P71" s="3" t="inlineStr">
+      <c r="P81" s="3" t="inlineStr">
         <is>
           <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
-      <c r="Q71" s="2" t="inlineStr">
+      <c r="Q81" s="2" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="R71" s="2" t="inlineStr">
+      <c r="R81" s="2" t="inlineStr">
         <is>
           <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
-      <c r="S71" s="2" t="inlineStr">
+      <c r="S81" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="T71" s="2" t="inlineStr">
+      <c r="T81" s="2" t="inlineStr">
         <is>
           <t>免許行政庁: 茨城県; 免許番号: 第000203号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T71"/>
+  <autoFilter ref="A1:T81"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -8075,10 +9095,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P69" r:id="rId135"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P70" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P71" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P72" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P73" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P74" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P75" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P76" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P77" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P78" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P79" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P80" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P81" r:id="rId147"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId138"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId148"/>
   </tableParts>
 </worksheet>
 </file>
@@ -8089,7 +9119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T62"/>
+  <dimension ref="A1:T72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12401,12 +13431,12 @@
     <row r="43" ht="42" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000181</t>
+          <t>RE-MLIT-09-00000002</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>大栄興業 株式会社</t>
+          <t>丸栃不動産倉庫 株式会社</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -12416,7 +13446,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -12426,7 +13456,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -12476,12 +13506,12 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
@@ -12496,19 +13526,19 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000181号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000002号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="44" ht="42" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000260</t>
+          <t>RE-MLIT-09-00000064</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>有限会社 協和商事</t>
+          <t>前田不動産 株式会社</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -12518,7 +13548,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -12528,7 +13558,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -12578,12 +13608,12 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
@@ -12598,19 +13628,19 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000260号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000064号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="45" ht="42" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000365</t>
+          <t>RE-MLIT-09-00000108</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>有限会社 小沢建設商事</t>
+          <t>協立不動産 株式会社</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -12620,7 +13650,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -12630,7 +13660,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -12680,12 +13710,12 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
@@ -12700,19 +13730,19 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000365号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000108号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="46" ht="42" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000162</t>
+          <t>RE-MLIT-09-00000159</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>有限会社 濱屋</t>
+          <t>大国不動産 株式会社</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -12722,7 +13752,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -12732,7 +13762,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12782,12 +13812,12 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
@@ -12802,19 +13832,19 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000162号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000159号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="47" ht="42" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000071</t>
+          <t>RE-MLIT-09-00000168</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>東栄商事 株式会社</t>
+          <t>小山土地建物 株式会社</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -12824,7 +13854,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -12834,7 +13864,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12884,12 +13914,12 @@
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R47" s="2" t="inlineStr">
@@ -12904,19 +13934,19 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000071号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000168号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="48" ht="42" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000060</t>
+          <t>RE-MLIT-09-00000062</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>東横不動産 株式会社</t>
+          <t>小金井不動産 株式会社</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -12926,7 +13956,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -12936,7 +13966,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12986,12 +14016,12 @@
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
@@ -13006,19 +14036,19 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000062号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="49" ht="42" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000013</t>
+          <t>RE-MLIT-09-00000054</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>株式会社 大谷商事</t>
+          <t>昭和商事 株式会社</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -13028,7 +14058,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -13038,7 +14068,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -13088,12 +14118,12 @@
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
@@ -13108,19 +14138,19 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000013号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000054号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="50" ht="42" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000024</t>
+          <t>RE-MLIT-09-00000022</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>浅間建設 株式会社</t>
+          <t>有限会社 カワシマ不動産</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -13130,7 +14160,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -13140,7 +14170,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -13190,12 +14220,12 @@
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr">
@@ -13210,19 +14240,19 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000024号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000022号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="51" ht="42" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000066</t>
+          <t>RE-MLIT-09-00000182</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>相澤土地 株式会社</t>
+          <t>有限会社 東栄不動産</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -13232,7 +14262,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -13242,7 +14272,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -13292,12 +14322,12 @@
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R51" s="2" t="inlineStr">
@@ -13312,19 +14342,19 @@
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000066号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000182号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000198</t>
+          <t>RE-MLIT-09-00000117</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>親和商事 有限会社</t>
+          <t>株式会社 万建設興業</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -13334,7 +14364,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -13344,7 +14374,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -13394,12 +14424,12 @@
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr">
@@ -13414,19 +14444,19 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000198号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000117号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="53" ht="42" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000204</t>
+          <t>RE-MLIT-14-00000181</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>一般財団法人笠間市開発公社</t>
+          <t>大栄興業 株式会社</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -13436,7 +14466,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -13446,7 +14476,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -13496,12 +14526,12 @@
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R53" s="2" t="inlineStr">
@@ -13516,19 +14546,19 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000204号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000181号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="54" ht="42" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000014</t>
+          <t>RE-MLIT-14-00000260</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>下館土地株式会社</t>
+          <t>有限会社 協和商事</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -13538,7 +14568,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -13548,7 +14578,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -13598,12 +14628,12 @@
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr">
@@ -13618,19 +14648,19 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000014号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000260号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="55" ht="42" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000167</t>
+          <t>RE-MLIT-14-00000365</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>公益財団法人茨城県開発公社</t>
+          <t>有限会社 小沢建設商事</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -13640,7 +14670,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -13650,7 +14680,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -13700,12 +14730,12 @@
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R55" s="2" t="inlineStr">
@@ -13720,19 +14750,19 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000167号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000365号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="56" ht="42" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000036</t>
+          <t>RE-MLIT-14-00000162</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>平和不動産株式会社</t>
+          <t>有限会社 濱屋</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -13742,7 +14772,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -13752,7 +14782,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13802,12 +14832,12 @@
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R56" s="2" t="inlineStr">
@@ -13822,19 +14852,19 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000036号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000162号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="57" ht="42" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000106</t>
+          <t>RE-MLIT-14-00000071</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>有限会社岩田不動産</t>
+          <t>東栄商事 株式会社</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -13844,7 +14874,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -13854,7 +14884,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13904,12 +14934,12 @@
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R57" s="2" t="inlineStr">
@@ -13924,19 +14954,19 @@
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000106号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000071号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="58" ht="42" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000058</t>
+          <t>RE-MLIT-14-00000060</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>有限会社栄進</t>
+          <t>東横不動産 株式会社</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -13946,7 +14976,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -13956,7 +14986,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -14006,12 +15036,12 @@
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R58" s="2" t="inlineStr">
@@ -14026,19 +15056,19 @@
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000058号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="59" ht="42" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000021</t>
+          <t>RE-MLIT-14-00000013</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>有限会社高橋商事</t>
+          <t>株式会社 大谷商事</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -14048,7 +15078,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -14058,7 +15088,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -14108,12 +15138,12 @@
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R59" s="2" t="inlineStr">
@@ -14128,19 +15158,19 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000021号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000013号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="60" ht="42" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000110</t>
+          <t>RE-MLIT-14-00000024</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>株式会社野口物産</t>
+          <t>浅間建設 株式会社</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -14150,7 +15180,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -14160,7 +15190,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -14210,12 +15240,12 @@
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R60" s="2" t="inlineStr">
@@ -14230,19 +15260,19 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000110号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000024号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000109</t>
+          <t>RE-MLIT-14-00000066</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>関友商事株式会社</t>
+          <t>相澤土地 株式会社</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -14252,7 +15282,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -14262,7 +15292,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -14312,12 +15342,12 @@
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R61" s="2" t="inlineStr">
@@ -14332,114 +15362,1134 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000109号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000066号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="62" ht="42" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>RE-MLIT-14-00000198</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>親和商事 有限会社</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000198号; 自動追加日: 2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="42" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000204</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>一般財団法人笠間市開発公社</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000204号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="42" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000014</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>下館土地株式会社</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000014号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="42" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000167</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>公益財団法人茨城県開発公社</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000167号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="42" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000036</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>平和不動産株式会社</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P66" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000036号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="42" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000106</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>有限会社岩田不動産</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S67" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T67" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000106号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="42" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000058</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>有限会社栄進</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T68" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000058号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="42" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000021</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>有限会社高橋商事</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T69" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000021号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="42" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000110</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>株式会社野口物産</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P70" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000110号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="42" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000109</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>関友商事株式会社</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000109号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="42" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
           <t>RE-MLIT-08-00000203</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>関東鉄道株式会社</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>関東</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="O62" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
         <is>
           <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
-      <c r="P62" s="3" t="inlineStr">
+      <c r="P72" s="3" t="inlineStr">
         <is>
           <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
-      <c r="Q62" s="2" t="inlineStr">
+      <c r="Q72" s="2" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="R62" s="2" t="inlineStr">
+      <c r="R72" s="2" t="inlineStr">
         <is>
           <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
-      <c r="S62" s="2" t="inlineStr">
+      <c r="S72" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="T62" s="2" t="inlineStr">
+      <c r="T72" s="2" t="inlineStr">
         <is>
           <t>免許行政庁: 茨城県; 免許番号: 第000203号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T62"/>
+  <autoFilter ref="A1:T72"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId2"/>
@@ -14542,10 +16592,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P60" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P61" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P62" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P63" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P64" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P65" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P66" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P67" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P68" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P69" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P70" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P71" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P72" r:id="rId111"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId102"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId112"/>
   </tableParts>
 </worksheet>
 </file>

--- a/database/real_estate_brokers.xlsx
+++ b/database/real_estate_brokers.xlsx
@@ -17,8 +17,8 @@
     <sheet name="データ辞書" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全社一覧'!$A$1:$T$81</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'関東'!$A$1:$T$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全社一覧'!$A$1:$T$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'関東'!$A$1:$T$82</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'北海道・東北'!$A$1:$T$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'近畿'!$A$1:$T$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'中国・四国'!$A$1:$T$2</definedName>
@@ -177,8 +177,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_9e7587520fcb" displayName="T_9e7587520fcb" ref="A1:T81" headerRowCount="1">
-  <autoFilter ref="A1:T81"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_9e7587520fcb" displayName="T_9e7587520fcb" ref="A1:T91" headerRowCount="1">
+  <autoFilter ref="A1:T91"/>
   <tableColumns count="20">
     <tableColumn id="1" name="会社ID"/>
     <tableColumn id="2" name="会社名"/>
@@ -206,8 +206,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_92ae89f64a96" displayName="T_92ae89f64a96" ref="A1:T72" headerRowCount="1">
-  <autoFilter ref="A1:T72"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_92ae89f64a96" displayName="T_92ae89f64a96" ref="A1:T82" headerRowCount="1">
+  <autoFilter ref="A1:T82"/>
   <tableColumns count="20">
     <tableColumn id="1" name="会社ID"/>
     <tableColumn id="2" name="会社名"/>
@@ -668,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T81"/>
+  <dimension ref="A1:T91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7938,12 +7938,12 @@
     <row r="72" ht="42" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000204</t>
+          <t>RE-MLIT-10-00000114</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>一般財団法人笠間市開発公社</t>
+          <t>上信電鉄株式会社</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8013,12 +8013,12 @@
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R72" s="2" t="inlineStr">
@@ -8033,19 +8033,19 @@
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000204号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000114号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="73" ht="42" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000014</t>
+          <t>RE-MLIT-10-00000292</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>下館土地株式会社</t>
+          <t>小林工業株式会社</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="P73" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R73" s="2" t="inlineStr">
@@ -8135,19 +8135,19 @@
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000014号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000292号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="74" ht="42" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000167</t>
+          <t>RE-MLIT-10-00000146</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>公益財団法人茨城県開発公社</t>
+          <t>有限会社前橋不動産</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8217,12 +8217,12 @@
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R74" s="2" t="inlineStr">
@@ -8237,19 +8237,19 @@
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000167号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000146号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="75" ht="42" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000036</t>
+          <t>RE-MLIT-10-00000098</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>平和不動産株式会社</t>
+          <t>有限会社田口不動産</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R75" s="2" t="inlineStr">
@@ -8339,19 +8339,19 @@
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000036号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000098号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="76" ht="42" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000106</t>
+          <t>RE-MLIT-10-00000302</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>有限会社岩田不動産</t>
+          <t>朝日開発興業株式会社</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R76" s="2" t="inlineStr">
@@ -8441,19 +8441,19 @@
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000106号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000302号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="77" ht="42" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000058</t>
+          <t>RE-MLIT-10-00000257</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>有限会社栄進</t>
+          <t>東神不動産株式会社</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -8523,12 +8523,12 @@
       </c>
       <c r="P77" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R77" s="2" t="inlineStr">
@@ -8543,19 +8543,19 @@
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000058号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000257号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="78" ht="42" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000021</t>
+          <t>RE-MLIT-10-00000038</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>有限会社高橋商事</t>
+          <t>株式会社ティーエムエフ</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="P78" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R78" s="2" t="inlineStr">
@@ -8645,19 +8645,19 @@
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000021号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000038号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="79" ht="42" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000110</t>
+          <t>RE-MLIT-10-00000230</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>株式会社野口物産</t>
+          <t>石橋建設工業株式会社 ※</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -8727,12 +8727,12 @@
       </c>
       <c r="P79" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R79" s="2" t="inlineStr">
@@ -8747,19 +8747,19 @@
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000110号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000230号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="80" ht="42" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000109</t>
+          <t>RE-MLIT-10-00000227</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>関友商事株式会社</t>
+          <t>群馬不動産株式会社 ※</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -8829,12 +8829,12 @@
       </c>
       <c r="P80" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R80" s="2" t="inlineStr">
@@ -8849,114 +8849,1134 @@
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000109号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000227号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="81" ht="42" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>RE-MLIT-10-00000075</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>鵜川興業株式会社</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>群馬県</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>群馬県</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P81" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S81" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T81" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 群馬県; 免許番号: 第000075号; 自動追加日: 2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="42" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000204</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>一般財団法人笠間市開発公社</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P82" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S82" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T82" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000204号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="42" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000014</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>下館土地株式会社</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P83" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S83" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T83" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000014号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="42" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000167</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>公益財団法人茨城県開発公社</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P84" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S84" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T84" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000167号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="42" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000036</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>平和不動産株式会社</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P85" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S85" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T85" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000036号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="42" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000106</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>有限会社岩田不動産</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P86" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S86" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T86" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000106号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="42" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000058</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>有限会社栄進</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P87" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S87" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T87" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000058号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="42" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000021</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>有限会社高橋商事</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P88" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S88" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T88" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000021号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="42" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000110</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>株式会社野口物産</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P89" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S89" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T89" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000110号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="42" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000109</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>関友商事株式会社</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P90" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S90" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T90" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000109号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="42" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
           <t>RE-MLIT-08-00000203</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>関東鉄道株式会社</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
         <is>
           <t>関東</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="O81" s="2" t="inlineStr">
-        <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
-        </is>
-      </c>
-      <c r="P81" s="3" t="inlineStr">
-        <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
-        </is>
-      </c>
-      <c r="Q81" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="R81" s="2" t="inlineStr">
-        <is>
-          <t>公的登録確認・公式サイト要確認</t>
-        </is>
-      </c>
-      <c r="S81" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>土地・事業用</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>https://www.kantetsu.co.jp/realestate/</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>https://www.kantetsu.co.jp/contact</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>https://www.kantetsu.co.jp/realestate/</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>公式サイトを自動確認。問い合わせ導線あり</t>
+        </is>
+      </c>
+      <c r="P91" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1 | https://www.kantetsu.co.jp/realestate/ | https://www.kantetsu.co.jp/contact</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr">
+        <is>
+          <t>自動確認済み</t>
+        </is>
+      </c>
+      <c r="S91" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="T81" s="2" t="inlineStr">
-        <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000203号; 自動追加日: 2026-07-23</t>
+      <c r="T91" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000203号; 自動追加日: 2026-07-23; 公式サイト自動確認日: 2026-07-25</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T81"/>
+  <autoFilter ref="A1:T91"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -9105,10 +10125,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P79" r:id="rId145"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P80" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P81" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P82" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P83" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P84" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P85" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P86" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P87" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P88" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P89" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P90" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K91" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L91" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M91" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P91" r:id="rId160"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId148"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId161"/>
   </tableParts>
 </worksheet>
 </file>
@@ -9119,7 +10152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T72"/>
+  <dimension ref="A1:T82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15471,12 +16504,12 @@
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000204</t>
+          <t>RE-MLIT-10-00000114</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>一般財団法人笠間市開発公社</t>
+          <t>上信電鉄株式会社</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -15486,7 +16519,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -15496,7 +16529,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -15546,12 +16579,12 @@
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R63" s="2" t="inlineStr">
@@ -15566,19 +16599,19 @@
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000204号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000114号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000014</t>
+          <t>RE-MLIT-10-00000292</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>下館土地株式会社</t>
+          <t>小林工業株式会社</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -15588,7 +16621,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -15598,7 +16631,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -15648,12 +16681,12 @@
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr">
@@ -15668,19 +16701,19 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000014号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000292号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="65" ht="42" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000167</t>
+          <t>RE-MLIT-10-00000146</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>公益財団法人茨城県開発公社</t>
+          <t>有限会社前橋不動産</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -15690,7 +16723,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -15700,7 +16733,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -15750,12 +16783,12 @@
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R65" s="2" t="inlineStr">
@@ -15770,19 +16803,19 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000167号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000146号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="66" ht="42" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000036</t>
+          <t>RE-MLIT-10-00000098</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>平和不動産株式会社</t>
+          <t>有限会社田口不動産</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -15792,7 +16825,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -15802,7 +16835,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -15852,12 +16885,12 @@
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R66" s="2" t="inlineStr">
@@ -15872,19 +16905,19 @@
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000036号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000098号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="67" ht="42" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000106</t>
+          <t>RE-MLIT-10-00000302</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>有限会社岩田不動産</t>
+          <t>朝日開発興業株式会社</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -15894,7 +16927,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -15904,7 +16937,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -15954,12 +16987,12 @@
       </c>
       <c r="P67" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R67" s="2" t="inlineStr">
@@ -15974,19 +17007,19 @@
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000106号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000302号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="68" ht="42" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000058</t>
+          <t>RE-MLIT-10-00000257</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>有限会社栄進</t>
+          <t>東神不動産株式会社</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -15996,7 +17029,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -16006,7 +17039,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -16056,12 +17089,12 @@
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R68" s="2" t="inlineStr">
@@ -16076,19 +17109,19 @@
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000058号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000257号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="69" ht="42" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000021</t>
+          <t>RE-MLIT-10-00000038</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>有限会社高橋商事</t>
+          <t>株式会社ティーエムエフ</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -16098,7 +17131,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -16108,7 +17141,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -16158,12 +17191,12 @@
       </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R69" s="2" t="inlineStr">
@@ -16178,19 +17211,19 @@
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000021号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000038号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="70" ht="42" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000110</t>
+          <t>RE-MLIT-10-00000230</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>株式会社野口物産</t>
+          <t>石橋建設工業株式会社 ※</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -16200,7 +17233,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -16210,7 +17243,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -16260,12 +17293,12 @@
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R70" s="2" t="inlineStr">
@@ -16280,19 +17313,19 @@
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000110号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000230号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="71" ht="42" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000109</t>
+          <t>RE-MLIT-10-00000227</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>関友商事株式会社</t>
+          <t>群馬不動産株式会社 ※</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -16302,7 +17335,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -16312,7 +17345,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -16362,12 +17395,12 @@
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R71" s="2" t="inlineStr">
@@ -16382,114 +17415,1134 @@
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000109号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000227号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="72" ht="42" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>RE-MLIT-10-00000075</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>鵜川興業株式会社</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>群馬県</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>群馬県</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P72" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 群馬県; 免許番号: 第000075号; 自動追加日: 2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="42" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000204</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>一般財団法人笠間市開発公社</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000204号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="42" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000014</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>下館土地株式会社</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P74" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T74" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000014号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="42" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000167</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>公益財団法人茨城県開発公社</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P75" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S75" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T75" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000167号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="42" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000036</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>平和不動産株式会社</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P76" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000036号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="42" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000106</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>有限会社岩田不動産</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P77" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S77" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T77" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000106号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="42" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000058</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>有限会社栄進</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P78" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S78" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T78" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000058号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="42" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000021</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>有限会社高橋商事</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P79" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S79" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T79" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000021号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="42" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000110</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>株式会社野口物産</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P80" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S80" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T80" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000110号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="42" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000109</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>関友商事株式会社</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P81" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S81" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T81" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000109号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="42" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
           <t>RE-MLIT-08-00000203</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>関東鉄道株式会社</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>関東</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="O72" s="2" t="inlineStr">
-        <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
-        </is>
-      </c>
-      <c r="P72" s="3" t="inlineStr">
-        <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
-        </is>
-      </c>
-      <c r="Q72" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="R72" s="2" t="inlineStr">
-        <is>
-          <t>公的登録確認・公式サイト要確認</t>
-        </is>
-      </c>
-      <c r="S72" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>土地・事業用</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>https://www.kantetsu.co.jp/realestate/</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>https://www.kantetsu.co.jp/contact</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>https://www.kantetsu.co.jp/realestate/</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>公式サイトを自動確認。問い合わせ導線あり</t>
+        </is>
+      </c>
+      <c r="P82" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1 | https://www.kantetsu.co.jp/realestate/ | https://www.kantetsu.co.jp/contact</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>自動確認済み</t>
+        </is>
+      </c>
+      <c r="S82" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="T72" s="2" t="inlineStr">
-        <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000203号; 自動追加日: 2026-07-23</t>
+      <c r="T82" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000203号; 自動追加日: 2026-07-23; 公式サイト自動確認日: 2026-07-25</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T72"/>
+  <autoFilter ref="A1:T82"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId2"/>
@@ -16602,10 +18655,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P70" r:id="rId109"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P71" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P72" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P73" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P74" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P75" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P76" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P77" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P78" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P79" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P80" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P81" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L82" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M82" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P82" r:id="rId124"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId112"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId125"/>
   </tableParts>
 </worksheet>
 </file>

--- a/database/real_estate_brokers.xlsx
+++ b/database/real_estate_brokers.xlsx
@@ -17,8 +17,8 @@
     <sheet name="データ辞書" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全社一覧'!$A$1:$T$101</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'関東'!$A$1:$T$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全社一覧'!$A$1:$T$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'関東'!$A$1:$T$102</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'北海道・東北'!$A$1:$T$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'近畿'!$A$1:$T$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'中国・四国'!$A$1:$T$2</definedName>
@@ -177,8 +177,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_9e7587520fcb" displayName="T_9e7587520fcb" ref="A1:T101" headerRowCount="1">
-  <autoFilter ref="A1:T101"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_9e7587520fcb" displayName="T_9e7587520fcb" ref="A1:T111" headerRowCount="1">
+  <autoFilter ref="A1:T111"/>
   <tableColumns count="20">
     <tableColumn id="1" name="会社ID"/>
     <tableColumn id="2" name="会社名"/>
@@ -206,8 +206,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_92ae89f64a96" displayName="T_92ae89f64a96" ref="A1:T92" headerRowCount="1">
-  <autoFilter ref="A1:T92"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_92ae89f64a96" displayName="T_92ae89f64a96" ref="A1:T102" headerRowCount="1">
+  <autoFilter ref="A1:T102"/>
   <tableColumns count="20">
     <tableColumn id="1" name="会社ID"/>
     <tableColumn id="2" name="会社名"/>
@@ -668,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T101"/>
+  <dimension ref="A1:T111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7938,12 +7938,12 @@
     <row r="72" ht="42" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000181</t>
+          <t>RE-MLIT-14-00001852</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>大栄興業 株式会社</t>
+          <t>オーナーズ商事 有限会社</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -8013,12 +8013,12 @@
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R72" s="2" t="inlineStr">
@@ -8033,19 +8033,19 @@
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000181号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001852号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="73" ht="42" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000260</t>
+          <t>RE-MLIT-14-00001691</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>有限会社 協和商事</t>
+          <t>一般財団法人 伊勢原市事業公社</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="P73" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R73" s="2" t="inlineStr">
@@ -8135,19 +8135,19 @@
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000260号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001691号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="74" ht="42" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000365</t>
+          <t>RE-MLIT-14-00001737</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>有限会社 小沢建設商事</t>
+          <t>丸万不動産 有限会社</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -8217,12 +8217,12 @@
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R74" s="2" t="inlineStr">
@@ -8237,19 +8237,19 @@
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000365号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001737号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="75" ht="42" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000162</t>
+          <t>RE-MLIT-14-00001740</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>有限会社 濱屋</t>
+          <t>大和商事 株式会社</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R75" s="2" t="inlineStr">
@@ -8339,19 +8339,19 @@
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000162号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001740号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="76" ht="42" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000071</t>
+          <t>RE-MLIT-14-00000181</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>東栄商事 株式会社</t>
+          <t>大栄興業 株式会社</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -8441,19 +8441,19 @@
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000071号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000181号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="77" ht="42" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000060</t>
+          <t>RE-MLIT-14-00001608</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>東横不動産 株式会社</t>
+          <t>川崎北部開発 株式会社</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -8523,12 +8523,12 @@
       </c>
       <c r="P77" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R77" s="2" t="inlineStr">
@@ -8543,19 +8543,19 @@
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001608号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="78" ht="42" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000013</t>
+          <t>RE-MLIT-14-00000260</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>株式会社 大谷商事</t>
+          <t>有限会社 協和商事</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -8645,19 +8645,19 @@
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000013号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000260号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="79" ht="42" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000024</t>
+          <t>RE-MLIT-14-00001851</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>浅間建設 株式会社</t>
+          <t>有限会社 吉浜不動産</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -8727,12 +8727,12 @@
       </c>
       <c r="P79" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R79" s="2" t="inlineStr">
@@ -8747,19 +8747,19 @@
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000024号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001851号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="80" ht="42" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000066</t>
+          <t>RE-MLIT-14-00000365</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>相澤土地 株式会社</t>
+          <t>有限会社 小沢建設商事</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -8849,19 +8849,19 @@
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000066号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000365号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="81" ht="42" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000198</t>
+          <t>RE-MLIT-14-00001610</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>親和商事 有限会社</t>
+          <t>有限会社 柏菱</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="P81" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R81" s="2" t="inlineStr">
@@ -8951,19 +8951,19 @@
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000198号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001610号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000114</t>
+          <t>RE-MLIT-14-00000162</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>上信電鉄株式会社</t>
+          <t>有限会社 濱屋</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -9033,12 +9033,12 @@
       </c>
       <c r="P82" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R82" s="2" t="inlineStr">
@@ -9053,19 +9053,19 @@
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000114号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000162号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000292</t>
+          <t>RE-MLIT-14-00001724</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>小林工業株式会社</t>
+          <t>末広土地建物 株式会社</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -9085,7 +9085,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="P83" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R83" s="2" t="inlineStr">
@@ -9155,19 +9155,19 @@
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000292号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001724号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000146</t>
+          <t>RE-MLIT-14-00000071</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>有限会社前橋不動産</t>
+          <t>東栄商事 株式会社</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="P84" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R84" s="2" t="inlineStr">
@@ -9257,19 +9257,19 @@
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000146号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000071号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000098</t>
+          <t>RE-MLIT-14-00000060</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>有限会社田口不動産</t>
+          <t>東横不動産 株式会社</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="P85" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R85" s="2" t="inlineStr">
@@ -9359,19 +9359,19 @@
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000098号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="86" ht="42" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000302</t>
+          <t>RE-MLIT-14-00000013</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>朝日開発興業株式会社</t>
+          <t>株式会社 大谷商事</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="P86" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R86" s="2" t="inlineStr">
@@ -9461,19 +9461,19 @@
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000302号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000013号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="87" ht="42" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000257</t>
+          <t>RE-MLIT-14-00001771</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>東神不動産株式会社</t>
+          <t>株式会社 日建</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="P87" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R87" s="2" t="inlineStr">
@@ -9563,19 +9563,19 @@
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000257号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001771号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000038</t>
+          <t>RE-MLIT-14-00000024</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>株式会社ティーエムエフ</t>
+          <t>浅間建設 株式会社</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -9595,7 +9595,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="P88" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R88" s="2" t="inlineStr">
@@ -9665,19 +9665,19 @@
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000038号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000024号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="89" ht="42" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000230</t>
+          <t>RE-MLIT-14-00000066</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>石橋建設工業株式会社 ※</t>
+          <t>相澤土地 株式会社</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -9747,12 +9747,12 @@
       </c>
       <c r="P89" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R89" s="2" t="inlineStr">
@@ -9767,19 +9767,19 @@
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000230号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000066号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="90" ht="42" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000227</t>
+          <t>RE-MLIT-14-00001880</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>群馬不動産株式会社 ※</t>
+          <t>第一商事 株式会社</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -9789,7 +9789,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="P90" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R90" s="2" t="inlineStr">
@@ -9869,19 +9869,19 @@
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000227号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001880号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="91" ht="42" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000075</t>
+          <t>RE-MLIT-14-00000198</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>鵜川興業株式会社</t>
+          <t>親和商事 有限会社</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -9901,7 +9901,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -9951,12 +9951,12 @@
       </c>
       <c r="P91" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R91" s="2" t="inlineStr">
@@ -9971,19 +9971,19 @@
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000075号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000198号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="92" ht="42" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000204</t>
+          <t>RE-MLIT-10-00000114</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>一般財団法人笠間市開発公社</t>
+          <t>上信電鉄株式会社</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -10053,12 +10053,12 @@
       </c>
       <c r="P92" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R92" s="2" t="inlineStr">
@@ -10073,19 +10073,19 @@
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000204号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000114号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="93" ht="42" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000014</t>
+          <t>RE-MLIT-10-00000292</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>下館土地株式会社</t>
+          <t>小林工業株式会社</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -10105,7 +10105,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -10155,12 +10155,12 @@
       </c>
       <c r="P93" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R93" s="2" t="inlineStr">
@@ -10175,19 +10175,19 @@
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000014号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000292号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="94" ht="42" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000167</t>
+          <t>RE-MLIT-10-00000146</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>公益財団法人茨城県開発公社</t>
+          <t>有限会社前橋不動産</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="P94" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R94" s="2" t="inlineStr">
@@ -10277,19 +10277,19 @@
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000167号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000146号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="95" ht="42" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000036</t>
+          <t>RE-MLIT-10-00000098</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>平和不動産株式会社</t>
+          <t>有限会社田口不動産</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="P95" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R95" s="2" t="inlineStr">
@@ -10379,19 +10379,19 @@
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000036号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000098号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="96" ht="42" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000106</t>
+          <t>RE-MLIT-10-00000302</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>有限会社岩田不動産</t>
+          <t>朝日開発興業株式会社</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -10461,12 +10461,12 @@
       </c>
       <c r="P96" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R96" s="2" t="inlineStr">
@@ -10481,19 +10481,19 @@
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000106号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000302号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="97" ht="42" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000058</t>
+          <t>RE-MLIT-10-00000257</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>有限会社栄進</t>
+          <t>東神不動産株式会社</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -10503,7 +10503,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="P97" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R97" s="2" t="inlineStr">
@@ -10583,19 +10583,19 @@
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000058号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000257号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="98" ht="42" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000021</t>
+          <t>RE-MLIT-10-00000038</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>有限会社高橋商事</t>
+          <t>株式会社ティーエムエフ</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -10615,7 +10615,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -10665,12 +10665,12 @@
       </c>
       <c r="P98" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R98" s="2" t="inlineStr">
@@ -10685,19 +10685,19 @@
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000021号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000038号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="99" ht="42" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000110</t>
+          <t>RE-MLIT-10-00000230</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>株式会社野口物産</t>
+          <t>石橋建設工業株式会社 ※</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -10767,12 +10767,12 @@
       </c>
       <c r="P99" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R99" s="2" t="inlineStr">
@@ -10787,19 +10787,19 @@
       </c>
       <c r="T99" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000110号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000230号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="100" ht="42" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000109</t>
+          <t>RE-MLIT-10-00000227</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>関友商事株式会社</t>
+          <t>群馬不動産株式会社 ※</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -10819,7 +10819,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="P100" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R100" s="2" t="inlineStr">
@@ -10889,114 +10889,1134 @@
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000109号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000227号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="101" ht="42" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>RE-MLIT-10-00000075</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>鵜川興業株式会社</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>群馬県</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>群馬県</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P101" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S101" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T101" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 群馬県; 免許番号: 第000075号; 自動追加日: 2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="42" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000204</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>一般財団法人笠間市開発公社</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P102" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T102" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000204号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="42" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000014</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>下館土地株式会社</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P103" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S103" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T103" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000014号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="42" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000167</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>公益財団法人茨城県開発公社</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P104" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S104" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T104" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000167号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="42" customHeight="1">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000036</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>平和不動産株式会社</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P105" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R105" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S105" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T105" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000036号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="42" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000106</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>有限会社岩田不動産</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P106" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R106" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S106" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T106" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000106号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="42" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000058</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>有限会社栄進</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P107" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R107" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S107" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T107" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000058号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="42" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000021</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>有限会社高橋商事</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P108" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R108" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S108" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T108" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000021号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="42" customHeight="1">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000110</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>株式会社野口物産</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P109" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R109" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S109" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T109" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000110号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="42" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000109</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>関友商事株式会社</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P110" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q110" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R110" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S110" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T110" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000109号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="42" customHeight="1">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
           <t>RE-MLIT-08-00000203</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>関東鉄道株式会社</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
         <is>
           <t>関東</t>
         </is>
       </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
         <is>
           <t>土地・事業用</t>
         </is>
       </c>
-      <c r="J101" s="2" t="inlineStr">
+      <c r="J111" s="2" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="K101" s="3" t="inlineStr">
+      <c r="K111" s="3" t="inlineStr">
         <is>
           <t>https://www.kantetsu.co.jp/realestate/</t>
         </is>
       </c>
-      <c r="L101" s="3" t="inlineStr">
+      <c r="L111" s="3" t="inlineStr">
         <is>
           <t>https://www.kantetsu.co.jp/contact</t>
         </is>
       </c>
-      <c r="M101" s="3" t="inlineStr">
+      <c r="M111" s="3" t="inlineStr">
         <is>
           <t>https://www.kantetsu.co.jp/realestate/</t>
         </is>
       </c>
-      <c r="N101" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="O101" s="2" t="inlineStr">
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
         <is>
           <t>公式サイトを自動確認。問い合わせ導線あり</t>
         </is>
       </c>
-      <c r="P101" s="3" t="inlineStr">
+      <c r="P111" s="3" t="inlineStr">
         <is>
           <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1 | https://www.kantetsu.co.jp/realestate/ | https://www.kantetsu.co.jp/contact</t>
         </is>
       </c>
-      <c r="Q101" s="2" t="inlineStr">
+      <c r="Q111" s="2" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="R101" s="2" t="inlineStr">
+      <c r="R111" s="2" t="inlineStr">
         <is>
           <t>自動確認済み</t>
         </is>
       </c>
-      <c r="S101" s="2" t="inlineStr">
+      <c r="S111" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="T101" s="2" t="inlineStr">
+      <c r="T111" s="2" t="inlineStr">
         <is>
           <t>免許行政庁: 茨城県; 免許番号: 第000203号; 自動追加日: 2026-07-23; 公式サイト自動確認日: 2026-07-25</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T101"/>
+  <autoFilter ref="A1:T111"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -11164,14 +12184,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P98" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P99" r:id="rId165"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P100" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K101" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M101" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P101" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P101" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P102" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P103" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P104" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P105" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P106" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P107" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P108" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P109" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P110" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L111" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M111" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P111" r:id="rId180"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId171"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId181"/>
   </tableParts>
 </worksheet>
 </file>
@@ -11182,7 +12212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T92"/>
+  <dimension ref="A1:T102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17534,12 +18564,12 @@
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000181</t>
+          <t>RE-MLIT-14-00001852</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>大栄興業 株式会社</t>
+          <t>オーナーズ商事 有限会社</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -17609,12 +18639,12 @@
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R63" s="2" t="inlineStr">
@@ -17629,19 +18659,19 @@
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000181号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001852号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000260</t>
+          <t>RE-MLIT-14-00001691</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>有限会社 協和商事</t>
+          <t>一般財団法人 伊勢原市事業公社</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -17711,12 +18741,12 @@
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr">
@@ -17731,19 +18761,19 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000260号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001691号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="65" ht="42" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000365</t>
+          <t>RE-MLIT-14-00001737</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>有限会社 小沢建設商事</t>
+          <t>丸万不動産 有限会社</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -17813,12 +18843,12 @@
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R65" s="2" t="inlineStr">
@@ -17833,19 +18863,19 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000365号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001737号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="66" ht="42" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000162</t>
+          <t>RE-MLIT-14-00001740</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>有限会社 濱屋</t>
+          <t>大和商事 株式会社</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -17915,12 +18945,12 @@
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R66" s="2" t="inlineStr">
@@ -17935,19 +18965,19 @@
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000162号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001740号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="67" ht="42" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000071</t>
+          <t>RE-MLIT-14-00000181</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>東栄商事 株式会社</t>
+          <t>大栄興業 株式会社</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -18037,19 +19067,19 @@
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000071号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000181号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="68" ht="42" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000060</t>
+          <t>RE-MLIT-14-00001608</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>東横不動産 株式会社</t>
+          <t>川崎北部開発 株式会社</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -18119,12 +19149,12 @@
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R68" s="2" t="inlineStr">
@@ -18139,19 +19169,19 @@
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001608号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="69" ht="42" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000013</t>
+          <t>RE-MLIT-14-00000260</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>株式会社 大谷商事</t>
+          <t>有限会社 協和商事</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -18241,19 +19271,19 @@
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000013号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000260号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="70" ht="42" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000024</t>
+          <t>RE-MLIT-14-00001851</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>浅間建設 株式会社</t>
+          <t>有限会社 吉浜不動産</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -18323,12 +19353,12 @@
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R70" s="2" t="inlineStr">
@@ -18343,19 +19373,19 @@
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000024号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001851号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="71" ht="42" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000066</t>
+          <t>RE-MLIT-14-00000365</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>相澤土地 株式会社</t>
+          <t>有限会社 小沢建設商事</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -18445,19 +19475,19 @@
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000066号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000365号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="72" ht="42" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000198</t>
+          <t>RE-MLIT-14-00001610</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>親和商事 有限会社</t>
+          <t>有限会社 柏菱</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -18527,12 +19557,12 @@
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R72" s="2" t="inlineStr">
@@ -18547,19 +19577,19 @@
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000198号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001610号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="73" ht="42" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000114</t>
+          <t>RE-MLIT-14-00000162</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>上信電鉄株式会社</t>
+          <t>有限会社 濱屋</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -18569,7 +19599,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -18579,7 +19609,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -18629,12 +19659,12 @@
       </c>
       <c r="P73" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R73" s="2" t="inlineStr">
@@ -18649,19 +19679,19 @@
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000114号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000162号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="74" ht="42" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000292</t>
+          <t>RE-MLIT-14-00001724</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>小林工業株式会社</t>
+          <t>末広土地建物 株式会社</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -18671,7 +19701,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -18681,7 +19711,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -18731,12 +19761,12 @@
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R74" s="2" t="inlineStr">
@@ -18751,19 +19781,19 @@
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000292号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001724号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="75" ht="42" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000146</t>
+          <t>RE-MLIT-14-00000071</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>有限会社前橋不動産</t>
+          <t>東栄商事 株式会社</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -18773,7 +19803,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -18783,7 +19813,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -18833,12 +19863,12 @@
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R75" s="2" t="inlineStr">
@@ -18853,19 +19883,19 @@
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000146号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000071号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="76" ht="42" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000098</t>
+          <t>RE-MLIT-14-00000060</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>有限会社田口不動産</t>
+          <t>東横不動産 株式会社</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -18875,7 +19905,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -18885,7 +19915,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -18935,12 +19965,12 @@
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R76" s="2" t="inlineStr">
@@ -18955,19 +19985,19 @@
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000098号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="77" ht="42" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000302</t>
+          <t>RE-MLIT-14-00000013</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>朝日開発興業株式会社</t>
+          <t>株式会社 大谷商事</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -18977,7 +20007,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -18987,7 +20017,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -19037,12 +20067,12 @@
       </c>
       <c r="P77" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R77" s="2" t="inlineStr">
@@ -19057,19 +20087,19 @@
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000302号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000013号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="78" ht="42" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000257</t>
+          <t>RE-MLIT-14-00001771</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>東神不動産株式会社</t>
+          <t>株式会社 日建</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -19079,7 +20109,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -19089,7 +20119,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -19139,12 +20169,12 @@
       </c>
       <c r="P78" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R78" s="2" t="inlineStr">
@@ -19159,19 +20189,19 @@
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000257号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001771号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="79" ht="42" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000038</t>
+          <t>RE-MLIT-14-00000024</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>株式会社ティーエムエフ</t>
+          <t>浅間建設 株式会社</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -19181,7 +20211,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -19191,7 +20221,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -19241,12 +20271,12 @@
       </c>
       <c r="P79" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R79" s="2" t="inlineStr">
@@ -19261,19 +20291,19 @@
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000038号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000024号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="80" ht="42" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000230</t>
+          <t>RE-MLIT-14-00000066</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>石橋建設工業株式会社 ※</t>
+          <t>相澤土地 株式会社</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -19283,7 +20313,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -19293,7 +20323,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -19343,12 +20373,12 @@
       </c>
       <c r="P80" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R80" s="2" t="inlineStr">
@@ -19363,19 +20393,19 @@
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000230号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000066号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="81" ht="42" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000227</t>
+          <t>RE-MLIT-14-00001880</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>群馬不動産株式会社 ※</t>
+          <t>第一商事 株式会社</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -19385,7 +20415,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -19395,7 +20425,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -19445,12 +20475,12 @@
       </c>
       <c r="P81" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R81" s="2" t="inlineStr">
@@ -19465,19 +20495,19 @@
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000227号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001880号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000075</t>
+          <t>RE-MLIT-14-00000198</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>鵜川興業株式会社</t>
+          <t>親和商事 有限会社</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -19487,7 +20517,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -19497,7 +20527,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -19547,12 +20577,12 @@
       </c>
       <c r="P82" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R82" s="2" t="inlineStr">
@@ -19567,19 +20597,19 @@
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000075号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000198号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000204</t>
+          <t>RE-MLIT-10-00000114</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>一般財団法人笠間市開発公社</t>
+          <t>上信電鉄株式会社</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -19589,7 +20619,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -19599,7 +20629,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -19649,12 +20679,12 @@
       </c>
       <c r="P83" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R83" s="2" t="inlineStr">
@@ -19669,19 +20699,19 @@
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000204号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000114号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000014</t>
+          <t>RE-MLIT-10-00000292</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>下館土地株式会社</t>
+          <t>小林工業株式会社</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -19691,7 +20721,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -19701,7 +20731,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -19751,12 +20781,12 @@
       </c>
       <c r="P84" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R84" s="2" t="inlineStr">
@@ -19771,19 +20801,19 @@
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000014号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000292号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000167</t>
+          <t>RE-MLIT-10-00000146</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>公益財団法人茨城県開発公社</t>
+          <t>有限会社前橋不動産</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -19793,7 +20823,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -19803,7 +20833,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -19853,12 +20883,12 @@
       </c>
       <c r="P85" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R85" s="2" t="inlineStr">
@@ -19873,19 +20903,19 @@
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000167号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000146号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="86" ht="42" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000036</t>
+          <t>RE-MLIT-10-00000098</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>平和不動産株式会社</t>
+          <t>有限会社田口不動産</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -19895,7 +20925,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -19905,7 +20935,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -19955,12 +20985,12 @@
       </c>
       <c r="P86" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R86" s="2" t="inlineStr">
@@ -19975,19 +21005,19 @@
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000036号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000098号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="87" ht="42" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000106</t>
+          <t>RE-MLIT-10-00000302</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>有限会社岩田不動産</t>
+          <t>朝日開発興業株式会社</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -19997,7 +21027,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -20007,7 +21037,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -20057,12 +21087,12 @@
       </c>
       <c r="P87" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R87" s="2" t="inlineStr">
@@ -20077,19 +21107,19 @@
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000106号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000302号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000058</t>
+          <t>RE-MLIT-10-00000257</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>有限会社栄進</t>
+          <t>東神不動産株式会社</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -20099,7 +21129,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -20109,7 +21139,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -20159,12 +21189,12 @@
       </c>
       <c r="P88" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R88" s="2" t="inlineStr">
@@ -20179,19 +21209,19 @@
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000058号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000257号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="89" ht="42" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000021</t>
+          <t>RE-MLIT-10-00000038</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>有限会社高橋商事</t>
+          <t>株式会社ティーエムエフ</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -20201,7 +21231,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -20211,7 +21241,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -20261,12 +21291,12 @@
       </c>
       <c r="P89" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R89" s="2" t="inlineStr">
@@ -20281,19 +21311,19 @@
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000021号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000038号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="90" ht="42" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000110</t>
+          <t>RE-MLIT-10-00000230</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>株式会社野口物産</t>
+          <t>石橋建設工業株式会社 ※</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -20303,7 +21333,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -20313,7 +21343,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -20363,12 +21393,12 @@
       </c>
       <c r="P90" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R90" s="2" t="inlineStr">
@@ -20383,19 +21413,19 @@
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000110号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000230号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="91" ht="42" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000109</t>
+          <t>RE-MLIT-10-00000227</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>関友商事株式会社</t>
+          <t>群馬不動産株式会社 ※</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -20405,7 +21435,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -20415,7 +21445,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -20465,12 +21495,12 @@
       </c>
       <c r="P91" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R91" s="2" t="inlineStr">
@@ -20485,114 +21515,1134 @@
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000109号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000227号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="92" ht="42" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>RE-MLIT-10-00000075</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>鵜川興業株式会社</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>群馬県</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>群馬県</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P92" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S92" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T92" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 群馬県; 免許番号: 第000075号; 自動追加日: 2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="42" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000204</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>一般財団法人笠間市開発公社</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P93" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S93" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T93" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000204号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="42" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000014</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>下館土地株式会社</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P94" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S94" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T94" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000014号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="42" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000167</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>公益財団法人茨城県開発公社</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P95" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S95" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T95" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000167号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="42" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000036</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>平和不動産株式会社</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P96" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T96" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000036号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="42" customHeight="1">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000106</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>有限会社岩田不動産</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P97" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S97" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T97" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000106号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="42" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000058</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>有限会社栄進</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P98" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000058号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="42" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000021</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>有限会社高橋商事</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P99" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S99" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T99" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000021号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="42" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000110</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>株式会社野口物産</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P100" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000110号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="42" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000109</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>関友商事株式会社</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P101" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S101" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T101" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000109号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="42" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
           <t>RE-MLIT-08-00000203</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>関東鉄道株式会社</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>関東</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
         <is>
           <t>土地・事業用</t>
         </is>
       </c>
-      <c r="J92" s="2" t="inlineStr">
+      <c r="J102" s="2" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="K92" s="3" t="inlineStr">
+      <c r="K102" s="3" t="inlineStr">
         <is>
           <t>https://www.kantetsu.co.jp/realestate/</t>
         </is>
       </c>
-      <c r="L92" s="3" t="inlineStr">
+      <c r="L102" s="3" t="inlineStr">
         <is>
           <t>https://www.kantetsu.co.jp/contact</t>
         </is>
       </c>
-      <c r="M92" s="3" t="inlineStr">
+      <c r="M102" s="3" t="inlineStr">
         <is>
           <t>https://www.kantetsu.co.jp/realestate/</t>
         </is>
       </c>
-      <c r="N92" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="O92" s="2" t="inlineStr">
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
         <is>
           <t>公式サイトを自動確認。問い合わせ導線あり</t>
         </is>
       </c>
-      <c r="P92" s="3" t="inlineStr">
+      <c r="P102" s="3" t="inlineStr">
         <is>
           <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1 | https://www.kantetsu.co.jp/realestate/ | https://www.kantetsu.co.jp/contact</t>
         </is>
       </c>
-      <c r="Q92" s="2" t="inlineStr">
+      <c r="Q102" s="2" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="R92" s="2" t="inlineStr">
+      <c r="R102" s="2" t="inlineStr">
         <is>
           <t>自動確認済み</t>
         </is>
       </c>
-      <c r="S92" s="2" t="inlineStr">
+      <c r="S102" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="T92" s="2" t="inlineStr">
+      <c r="T102" s="2" t="inlineStr">
         <is>
           <t>免許行政庁: 茨城県; 免許番号: 第000203号; 自動追加日: 2026-07-23; 公式サイト自動確認日: 2026-07-25</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T92"/>
+  <autoFilter ref="A1:T102"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId2"/>
@@ -20724,14 +22774,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P89" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P90" r:id="rId129"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P91" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L92" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M92" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P92" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P92" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P93" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P94" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P95" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P96" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P97" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P98" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P99" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P100" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P101" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L102" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M102" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P102" r:id="rId144"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId135"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId145"/>
   </tableParts>
 </worksheet>
 </file>

--- a/database/real_estate_brokers.xlsx
+++ b/database/real_estate_brokers.xlsx
@@ -17,8 +17,8 @@
     <sheet name="データ辞書" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全社一覧'!$A$1:$T$131</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'関東'!$A$1:$T$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全社一覧'!$A$1:$T$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'関東'!$A$1:$T$132</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'北海道・東北'!$A$1:$T$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'近畿'!$A$1:$T$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'中国・四国'!$A$1:$T$2</definedName>
@@ -177,8 +177,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_9e7587520fcb" displayName="T_9e7587520fcb" ref="A1:T131" headerRowCount="1">
-  <autoFilter ref="A1:T131"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_9e7587520fcb" displayName="T_9e7587520fcb" ref="A1:T141" headerRowCount="1">
+  <autoFilter ref="A1:T141"/>
   <tableColumns count="20">
     <tableColumn id="1" name="会社ID"/>
     <tableColumn id="2" name="会社名"/>
@@ -206,8 +206,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_92ae89f64a96" displayName="T_92ae89f64a96" ref="A1:T122" headerRowCount="1">
-  <autoFilter ref="A1:T122"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_92ae89f64a96" displayName="T_92ae89f64a96" ref="A1:T132" headerRowCount="1">
+  <autoFilter ref="A1:T132"/>
   <tableColumns count="20">
     <tableColumn id="1" name="会社ID"/>
     <tableColumn id="2" name="会社名"/>
@@ -668,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T131"/>
+  <dimension ref="A1:T141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13038,12 +13038,12 @@
     <row r="122" ht="42" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000204</t>
+          <t>RE-MLIT-08-00001443</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>一般財団法人笠間市開発公社</t>
+          <t>マルカン商事有限会社</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -13113,12 +13113,12 @@
       </c>
       <c r="P122" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R122" s="2" t="inlineStr">
@@ -13133,19 +13133,19 @@
       </c>
       <c r="T122" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000204号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第001443号; 自動追加日: 2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="123" ht="42" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000014</t>
+          <t>RE-MLIT-08-00000204</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>下館土地株式会社</t>
+          <t>一般財団法人笠間市開発公社</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -13235,19 +13235,19 @@
       </c>
       <c r="T123" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000014号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000204号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="124" ht="42" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000167</t>
+          <t>RE-MLIT-08-00000014</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>公益財団法人茨城県開発公社</t>
+          <t>下館土地株式会社</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -13337,19 +13337,19 @@
       </c>
       <c r="T124" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000167号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000014号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="125" ht="42" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000036</t>
+          <t>RE-MLIT-08-00000167</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>平和不動産株式会社</t>
+          <t>公益財団法人茨城県開発公社</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -13439,19 +13439,19 @@
       </c>
       <c r="T125" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000036号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000167号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="126" ht="42" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000106</t>
+          <t>RE-MLIT-08-00001278</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>有限会社岩田不動産</t>
+          <t>大みか不動産株式会社</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -13521,12 +13521,12 @@
       </c>
       <c r="P126" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R126" s="2" t="inlineStr">
@@ -13541,19 +13541,19 @@
       </c>
       <c r="T126" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000106号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第001278号; 自動追加日: 2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="127" ht="42" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000058</t>
+          <t>RE-MLIT-08-00000036</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>有限会社栄進</t>
+          <t>平和不動産株式会社</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -13643,19 +13643,19 @@
       </c>
       <c r="T127" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000058号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000036号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="128" ht="42" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000021</t>
+          <t>RE-MLIT-08-00001437</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>有限会社高橋商事</t>
+          <t>斉丸土地</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -13725,12 +13725,12 @@
       </c>
       <c r="P128" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R128" s="2" t="inlineStr">
@@ -13745,19 +13745,19 @@
       </c>
       <c r="T128" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000021号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第001437号; 自動追加日: 2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="129" ht="42" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000110</t>
+          <t>RE-MLIT-08-00000106</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>株式会社野口物産</t>
+          <t>有限会社岩田不動産</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -13847,19 +13847,19 @@
       </c>
       <c r="T129" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000110号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000106号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="130" ht="42" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000109</t>
+          <t>RE-MLIT-08-00001391</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>関友商事株式会社</t>
+          <t>有限会社東栄</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -13929,12 +13929,12 @@
       </c>
       <c r="P130" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R130" s="2" t="inlineStr">
@@ -13949,114 +13949,1134 @@
       </c>
       <c r="T130" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000109号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第001391号; 自動追加日: 2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="131" ht="42" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>RE-MLIT-08-00000058</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>有限会社栄進</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P131" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q131" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R131" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S131" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T131" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000058号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="42" customHeight="1">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000021</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>有限会社高橋商事</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P132" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q132" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R132" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S132" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T132" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000021号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="42" customHeight="1">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001345</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>株式会社中野商事</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P133" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q133" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R133" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S133" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T133" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001345号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="42" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001306</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>株式会社新栄土地</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P134" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q134" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R134" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S134" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T134" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001306号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="42" customHeight="1">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001321</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>株式会社水戸地産</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P135" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q135" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R135" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S135" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T135" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001321号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="42" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001262</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>株式会社赤尾杉</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P136" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q136" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R136" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S136" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T136" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001262号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="42" customHeight="1">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000110</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>株式会社野口物産</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P137" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q137" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R137" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S137" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T137" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000110号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="42" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001434</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>池田林業株式会社</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P138" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q138" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R138" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S138" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T138" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001434号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="42" customHeight="1">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001302</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>荒沢不動産</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P139" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q139" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R139" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S139" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T139" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001302号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="42" customHeight="1">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000109</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>関友商事株式会社</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P140" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q140" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R140" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S140" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T140" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000109号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="42" customHeight="1">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
           <t>RE-MLIT-08-00000203</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>関東鉄道株式会社</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
         <is>
           <t>関東</t>
         </is>
       </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="I131" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
         <is>
           <t>土地・事業用</t>
         </is>
       </c>
-      <c r="J131" s="2" t="inlineStr">
+      <c r="J141" s="2" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="K131" s="3" t="inlineStr">
+      <c r="K141" s="3" t="inlineStr">
         <is>
           <t>https://www.kantetsu.co.jp/realestate/</t>
         </is>
       </c>
-      <c r="L131" s="3" t="inlineStr">
+      <c r="L141" s="3" t="inlineStr">
         <is>
           <t>https://www.kantetsu.co.jp/contact</t>
         </is>
       </c>
-      <c r="M131" s="3" t="inlineStr">
+      <c r="M141" s="3" t="inlineStr">
         <is>
           <t>https://www.kantetsu.co.jp/realestate/</t>
         </is>
       </c>
-      <c r="N131" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="O131" s="2" t="inlineStr">
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
         <is>
           <t>公式サイトを自動確認。問い合わせ導線あり</t>
         </is>
       </c>
-      <c r="P131" s="3" t="inlineStr">
+      <c r="P141" s="3" t="inlineStr">
         <is>
           <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1 | https://www.kantetsu.co.jp/realestate/ | https://www.kantetsu.co.jp/contact</t>
         </is>
       </c>
-      <c r="Q131" s="2" t="inlineStr">
+      <c r="Q141" s="2" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="R131" s="2" t="inlineStr">
+      <c r="R141" s="2" t="inlineStr">
         <is>
           <t>自動確認済み</t>
         </is>
       </c>
-      <c r="S131" s="2" t="inlineStr">
+      <c r="S141" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="T131" s="2" t="inlineStr">
+      <c r="T141" s="2" t="inlineStr">
         <is>
           <t>免許行政庁: 茨城県; 免許番号: 第000203号; 自動追加日: 2026-07-23; 公式サイト自動確認日: 2026-07-25</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T131"/>
+  <autoFilter ref="A1:T141"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -14256,14 +15276,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P128" r:id="rId196"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P129" r:id="rId197"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P130" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L131" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M131" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P131" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P131" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P132" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P133" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P134" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P135" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P136" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P137" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P138" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P139" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P140" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K141" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L141" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M141" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P141" r:id="rId212"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId203"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId213"/>
   </tableParts>
 </worksheet>
 </file>
@@ -14274,7 +15304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T122"/>
+  <dimension ref="A1:T132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -25726,12 +26756,12 @@
     <row r="113" ht="42" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000204</t>
+          <t>RE-MLIT-08-00001443</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>一般財団法人笠間市開発公社</t>
+          <t>マルカン商事有限会社</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -25801,12 +26831,12 @@
       </c>
       <c r="P113" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R113" s="2" t="inlineStr">
@@ -25821,19 +26851,19 @@
       </c>
       <c r="T113" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000204号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第001443号; 自動追加日: 2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="114" ht="42" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000014</t>
+          <t>RE-MLIT-08-00000204</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>下館土地株式会社</t>
+          <t>一般財団法人笠間市開発公社</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -25923,19 +26953,19 @@
       </c>
       <c r="T114" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000014号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000204号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="115" ht="42" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000167</t>
+          <t>RE-MLIT-08-00000014</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>公益財団法人茨城県開発公社</t>
+          <t>下館土地株式会社</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -26025,19 +27055,19 @@
       </c>
       <c r="T115" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000167号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000014号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="116" ht="42" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000036</t>
+          <t>RE-MLIT-08-00000167</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>平和不動産株式会社</t>
+          <t>公益財団法人茨城県開発公社</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -26127,19 +27157,19 @@
       </c>
       <c r="T116" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000036号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000167号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="117" ht="42" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000106</t>
+          <t>RE-MLIT-08-00001278</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>有限会社岩田不動産</t>
+          <t>大みか不動産株式会社</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -26209,12 +27239,12 @@
       </c>
       <c r="P117" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R117" s="2" t="inlineStr">
@@ -26229,19 +27259,19 @@
       </c>
       <c r="T117" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000106号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第001278号; 自動追加日: 2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="118" ht="42" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000058</t>
+          <t>RE-MLIT-08-00000036</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>有限会社栄進</t>
+          <t>平和不動産株式会社</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -26331,19 +27361,19 @@
       </c>
       <c r="T118" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000058号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000036号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="119" ht="42" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000021</t>
+          <t>RE-MLIT-08-00001437</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>有限会社高橋商事</t>
+          <t>斉丸土地</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -26413,12 +27443,12 @@
       </c>
       <c r="P119" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R119" s="2" t="inlineStr">
@@ -26433,19 +27463,19 @@
       </c>
       <c r="T119" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000021号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第001437号; 自動追加日: 2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="120" ht="42" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000110</t>
+          <t>RE-MLIT-08-00000106</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>株式会社野口物産</t>
+          <t>有限会社岩田不動産</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -26535,19 +27565,19 @@
       </c>
       <c r="T120" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000110号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000106号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="121" ht="42" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000109</t>
+          <t>RE-MLIT-08-00001391</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>関友商事株式会社</t>
+          <t>有限会社東栄</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -26617,12 +27647,12 @@
       </c>
       <c r="P121" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R121" s="2" t="inlineStr">
@@ -26637,114 +27667,1134 @@
       </c>
       <c r="T121" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000109号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第001391号; 自動追加日: 2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="122" ht="42" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>RE-MLIT-08-00000058</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>有限会社栄進</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P122" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q122" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R122" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S122" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T122" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000058号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="42" customHeight="1">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000021</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>有限会社高橋商事</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P123" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q123" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R123" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S123" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T123" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000021号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="42" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001345</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>株式会社中野商事</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P124" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q124" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R124" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S124" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T124" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001345号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="42" customHeight="1">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001306</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>株式会社新栄土地</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P125" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q125" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R125" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S125" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T125" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001306号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="42" customHeight="1">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001321</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>株式会社水戸地産</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P126" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q126" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R126" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S126" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T126" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001321号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="42" customHeight="1">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001262</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>株式会社赤尾杉</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P127" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q127" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R127" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S127" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T127" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001262号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="42" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000110</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>株式会社野口物産</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P128" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q128" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R128" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S128" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T128" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000110号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="42" customHeight="1">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001434</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>池田林業株式会社</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P129" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q129" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R129" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S129" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T129" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001434号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="42" customHeight="1">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001302</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>荒沢不動産</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P130" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q130" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R130" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S130" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T130" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001302号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="42" customHeight="1">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000109</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>関友商事株式会社</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P131" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q131" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R131" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S131" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T131" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000109号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="42" customHeight="1">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
           <t>RE-MLIT-08-00000203</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>関東鉄道株式会社</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
+      <c r="C132" s="2" t="inlineStr">
         <is>
           <t>関東</t>
         </is>
       </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
         <is>
           <t>土地・事業用</t>
         </is>
       </c>
-      <c r="J122" s="2" t="inlineStr">
+      <c r="J132" s="2" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="K122" s="3" t="inlineStr">
+      <c r="K132" s="3" t="inlineStr">
         <is>
           <t>https://www.kantetsu.co.jp/realestate/</t>
         </is>
       </c>
-      <c r="L122" s="3" t="inlineStr">
+      <c r="L132" s="3" t="inlineStr">
         <is>
           <t>https://www.kantetsu.co.jp/contact</t>
         </is>
       </c>
-      <c r="M122" s="3" t="inlineStr">
+      <c r="M132" s="3" t="inlineStr">
         <is>
           <t>https://www.kantetsu.co.jp/realestate/</t>
         </is>
       </c>
-      <c r="N122" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="O122" s="2" t="inlineStr">
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
         <is>
           <t>公式サイトを自動確認。問い合わせ導線あり</t>
         </is>
       </c>
-      <c r="P122" s="3" t="inlineStr">
+      <c r="P132" s="3" t="inlineStr">
         <is>
           <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1 | https://www.kantetsu.co.jp/realestate/ | https://www.kantetsu.co.jp/contact</t>
         </is>
       </c>
-      <c r="Q122" s="2" t="inlineStr">
+      <c r="Q132" s="2" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="R122" s="2" t="inlineStr">
+      <c r="R132" s="2" t="inlineStr">
         <is>
           <t>自動確認済み</t>
         </is>
       </c>
-      <c r="S122" s="2" t="inlineStr">
+      <c r="S132" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="T122" s="2" t="inlineStr">
+      <c r="T132" s="2" t="inlineStr">
         <is>
           <t>免許行政庁: 茨城県; 免許番号: 第000203号; 自動追加日: 2026-07-23; 公式サイト自動確認日: 2026-07-25</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T122"/>
+  <autoFilter ref="A1:T132"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId2"/>
@@ -26908,14 +28958,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P119" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P120" r:id="rId161"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P121" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K122" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L122" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M122" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P122" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P122" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P123" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P124" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P125" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P126" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P127" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P128" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P129" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P130" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P131" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L132" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M132" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P132" r:id="rId176"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId167"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId177"/>
   </tableParts>
 </worksheet>
 </file>

--- a/database/real_estate_brokers.xlsx
+++ b/database/real_estate_brokers.xlsx
@@ -17,8 +17,8 @@
     <sheet name="データ辞書" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全社一覧'!$A$1:$T$141</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'関東'!$A$1:$T$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全社一覧'!$A$1:$T$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'関東'!$A$1:$T$142</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'北海道・東北'!$A$1:$T$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'近畿'!$A$1:$T$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'中国・四国'!$A$1:$T$2</definedName>
@@ -177,8 +177,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_9e7587520fcb" displayName="T_9e7587520fcb" ref="A1:T141" headerRowCount="1">
-  <autoFilter ref="A1:T141"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_9e7587520fcb" displayName="T_9e7587520fcb" ref="A1:T151" headerRowCount="1">
+  <autoFilter ref="A1:T151"/>
   <tableColumns count="20">
     <tableColumn id="1" name="会社ID"/>
     <tableColumn id="2" name="会社名"/>
@@ -206,8 +206,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_92ae89f64a96" displayName="T_92ae89f64a96" ref="A1:T132" headerRowCount="1">
-  <autoFilter ref="A1:T132"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_92ae89f64a96" displayName="T_92ae89f64a96" ref="A1:T142" headerRowCount="1">
+  <autoFilter ref="A1:T142"/>
   <tableColumns count="20">
     <tableColumn id="1" name="会社ID"/>
     <tableColumn id="2" name="会社名"/>
@@ -668,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T141"/>
+  <dimension ref="A1:T151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4102,52 +4102,52 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>土地・事業用</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>https://www.shamaison.com/saitama/shop/area/11215/2012100011123/</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>https://www.shamaison.com/contact-24h.html</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>https://www.shamaison.com/saitama/shop/area/11215/2012100011123/</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>04-2959-4560</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>公式サイトを自動確認。戸建て取扱表記あり。問い合わせ導線あり</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2 | https://www.shamaison.com/saitama/shop/area/11215/2012100011123/ | https://www.shamaison.com/contact-24h.html</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>自動確認済み</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 埼玉県; 免許番号: 第001778号; 自動追加日: 2026-07-28</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第001778号; 自動追加日: 2026-07-28; 公式サイト自動確認日: 2026-07-31</t>
         </is>
       </c>
     </row>
@@ -8958,12 +8958,12 @@
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-09-00000002</t>
+          <t>RE-MLIT-09-00000905</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>丸栃不動産倉庫 株式会社</t>
+          <t>万不動産 株式会社</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -9033,12 +9033,12 @@
       </c>
       <c r="P82" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R82" s="2" t="inlineStr">
@@ -9053,19 +9053,19 @@
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 栃木県; 免許番号: 第000002号; 自動追加日: 2026-07-24</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000905号; 自動追加日: 2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-09-00000064</t>
+          <t>RE-MLIT-09-00000002</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>前田不動産 株式会社</t>
+          <t>丸栃不動産倉庫 株式会社</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -9155,19 +9155,19 @@
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 栃木県; 免許番号: 第000064号; 自動追加日: 2026-07-24</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000002号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-09-00000108</t>
+          <t>RE-MLIT-09-00000919</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>協立不動産 株式会社</t>
+          <t>八汐土地開発 株式会社</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="P84" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R84" s="2" t="inlineStr">
@@ -9257,19 +9257,19 @@
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 栃木県; 免許番号: 第000108号; 自動追加日: 2026-07-24</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000919号; 自動追加日: 2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-09-00000159</t>
+          <t>RE-MLIT-09-00000064</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>大国不動産 株式会社</t>
+          <t>前田不動産 株式会社</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -9359,19 +9359,19 @@
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 栃木県; 免許番号: 第000159号; 自動追加日: 2026-07-24</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000064号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="86" ht="42" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-09-00000168</t>
+          <t>RE-MLIT-09-00000108</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>小山土地建物 株式会社</t>
+          <t>協立不動産 株式会社</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -9461,19 +9461,19 @@
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 栃木県; 免許番号: 第000168号; 自動追加日: 2026-07-24</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000108号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="87" ht="42" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-09-00000062</t>
+          <t>RE-MLIT-09-00000159</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>小金井不動産 株式会社</t>
+          <t>大国不動産 株式会社</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -9563,19 +9563,19 @@
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 栃木県; 免許番号: 第000062号; 自動追加日: 2026-07-24</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000159号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-09-00000054</t>
+          <t>RE-MLIT-09-00000168</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>昭和商事 株式会社</t>
+          <t>小山土地建物 株式会社</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -9665,19 +9665,19 @@
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 栃木県; 免許番号: 第000054号; 自動追加日: 2026-07-24</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000168号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="89" ht="42" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-09-00000022</t>
+          <t>RE-MLIT-09-00000062</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>有限会社 カワシマ不動産</t>
+          <t>小金井不動産 株式会社</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -9767,19 +9767,19 @@
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 栃木県; 免許番号: 第000022号; 自動追加日: 2026-07-24</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000062号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="90" ht="42" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-09-00000182</t>
+          <t>RE-MLIT-09-00000054</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>有限会社 東栄不動産</t>
+          <t>昭和商事 株式会社</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -9869,19 +9869,19 @@
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 栃木県; 免許番号: 第000182号; 自動追加日: 2026-07-24</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000054号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="91" ht="42" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-09-00000117</t>
+          <t>RE-MLIT-09-00000022</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>株式会社 万建設興業</t>
+          <t>有限会社 カワシマ不動産</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -9971,19 +9971,19 @@
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 栃木県; 免許番号: 第000117号; 自動追加日: 2026-07-24</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000022号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="92" ht="42" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00001852</t>
+          <t>RE-MLIT-09-00001009</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>オーナーズ商事 有限会社</t>
+          <t>有限会社 大福不動産</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -10053,12 +10053,12 @@
       </c>
       <c r="P92" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R92" s="2" t="inlineStr">
@@ -10073,19 +10073,19 @@
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第001852号; 自動追加日: 2026-07-27</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第001009号; 自動追加日: 2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="93" ht="42" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00001691</t>
+          <t>RE-MLIT-09-00000182</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>一般財団法人 伊勢原市事業公社</t>
+          <t>有限会社 東栄不動産</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -10105,7 +10105,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -10155,12 +10155,12 @@
       </c>
       <c r="P93" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R93" s="2" t="inlineStr">
@@ -10175,19 +10175,19 @@
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第001691号; 自動追加日: 2026-07-27</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000182号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="94" ht="42" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00001737</t>
+          <t>RE-MLIT-09-00001050</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>丸万不動産 有限会社</t>
+          <t>有限会社 栃信総業</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="P94" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R94" s="2" t="inlineStr">
@@ -10277,19 +10277,19 @@
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第001737号; 自動追加日: 2026-07-27</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第001050号; 自動追加日: 2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="95" ht="42" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00001740</t>
+          <t>RE-MLIT-09-00000976</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>大和商事 株式会社</t>
+          <t>東照商事 株式会社</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="P95" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R95" s="2" t="inlineStr">
@@ -10379,19 +10379,19 @@
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第001740号; 自動追加日: 2026-07-27</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000976号; 自動追加日: 2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="96" ht="42" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000181</t>
+          <t>RE-MLIT-09-00000883</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>大栄興業 株式会社</t>
+          <t>株式会社 むぎくら</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -10461,12 +10461,12 @@
       </c>
       <c r="P96" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R96" s="2" t="inlineStr">
@@ -10481,19 +10481,19 @@
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000181号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000883号; 自動追加日: 2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="97" ht="42" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00001608</t>
+          <t>RE-MLIT-09-00000117</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>川崎北部開発 株式会社</t>
+          <t>株式会社 万建設興業</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -10503,7 +10503,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="P97" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R97" s="2" t="inlineStr">
@@ -10583,19 +10583,19 @@
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第001608号; 自動追加日: 2026-07-27</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000117号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="98" ht="42" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000260</t>
+          <t>RE-MLIT-09-00000903</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>有限会社 協和商事</t>
+          <t>株式会社 大竹不動産</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -10615,7 +10615,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -10665,12 +10665,12 @@
       </c>
       <c r="P98" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R98" s="2" t="inlineStr">
@@ -10685,19 +10685,19 @@
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000260号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000903号; 自動追加日: 2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="99" ht="42" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00001851</t>
+          <t>RE-MLIT-09-00000949</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>有限会社 吉浜不動産</t>
+          <t>株式会社 大那商事</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -10767,12 +10767,12 @@
       </c>
       <c r="P99" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R99" s="2" t="inlineStr">
@@ -10787,19 +10787,19 @@
       </c>
       <c r="T99" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第001851号; 自動追加日: 2026-07-27</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000949号; 自動追加日: 2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="100" ht="42" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000365</t>
+          <t>RE-MLIT-09-00000916</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>有限会社 小沢建設商事</t>
+          <t>株式会社 西崎</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -10819,7 +10819,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="P100" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R100" s="2" t="inlineStr">
@@ -10889,19 +10889,19 @@
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000365号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000916号; 自動追加日: 2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="101" ht="42" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00001610</t>
+          <t>RE-MLIT-09-00000984</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>有限会社 柏菱</t>
+          <t>関東地所 株式会社</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -10971,12 +10971,12 @@
       </c>
       <c r="P101" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R101" s="2" t="inlineStr">
@@ -10991,19 +10991,19 @@
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第001610号; 自動追加日: 2026-07-27</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000984号; 自動追加日: 2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="102" ht="42" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000162</t>
+          <t>RE-MLIT-14-00001852</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>有限会社 濱屋</t>
+          <t>オーナーズ商事 有限会社</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -11073,12 +11073,12 @@
       </c>
       <c r="P102" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R102" s="2" t="inlineStr">
@@ -11093,19 +11093,19 @@
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000162号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001852号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="103" ht="42" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00001724</t>
+          <t>RE-MLIT-14-00001691</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>末広土地建物 株式会社</t>
+          <t>一般財団法人 伊勢原市事業公社</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -11195,19 +11195,19 @@
       </c>
       <c r="T103" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第001724号; 自動追加日: 2026-07-27</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001691号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="104" ht="42" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000071</t>
+          <t>RE-MLIT-14-00001737</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>東栄商事 株式会社</t>
+          <t>丸万不動産 有限会社</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -11277,12 +11277,12 @@
       </c>
       <c r="P104" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R104" s="2" t="inlineStr">
@@ -11297,19 +11297,19 @@
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000071号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001737号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="105" ht="42" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000060</t>
+          <t>RE-MLIT-14-00001740</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>東横不動産 株式会社</t>
+          <t>大和商事 株式会社</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="P105" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R105" s="2" t="inlineStr">
@@ -11399,19 +11399,19 @@
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001740号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="106" ht="42" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000013</t>
+          <t>RE-MLIT-14-00000181</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>株式会社 大谷商事</t>
+          <t>大栄興業 株式会社</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -11501,19 +11501,19 @@
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000013号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000181号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="107" ht="42" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00001771</t>
+          <t>RE-MLIT-14-00001608</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>株式会社 日建</t>
+          <t>川崎北部開発 株式会社</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -11603,19 +11603,19 @@
       </c>
       <c r="T107" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第001771号; 自動追加日: 2026-07-27</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001608号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="108" ht="42" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000024</t>
+          <t>RE-MLIT-14-00000260</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>浅間建設 株式会社</t>
+          <t>有限会社 協和商事</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -11705,19 +11705,19 @@
       </c>
       <c r="T108" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000024号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000260号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="109" ht="42" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000066</t>
+          <t>RE-MLIT-14-00001851</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>相澤土地 株式会社</t>
+          <t>有限会社 吉浜不動産</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="P109" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R109" s="2" t="inlineStr">
@@ -11807,19 +11807,19 @@
       </c>
       <c r="T109" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000066号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001851号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="110" ht="42" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00001880</t>
+          <t>RE-MLIT-14-00000365</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>第一商事 株式会社</t>
+          <t>有限会社 小沢建設商事</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="P110" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R110" s="2" t="inlineStr">
@@ -11909,19 +11909,19 @@
       </c>
       <c r="T110" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第001880号; 自動追加日: 2026-07-27</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000365号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="111" ht="42" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000198</t>
+          <t>RE-MLIT-14-00001610</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>親和商事 有限会社</t>
+          <t>有限会社 柏菱</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -11991,12 +11991,12 @@
       </c>
       <c r="P111" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R111" s="2" t="inlineStr">
@@ -12011,19 +12011,19 @@
       </c>
       <c r="T111" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000198号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001610号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="112" ht="42" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000114</t>
+          <t>RE-MLIT-14-00000162</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>上信電鉄株式会社</t>
+          <t>有限会社 濱屋</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -12033,7 +12033,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -12043,7 +12043,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -12093,12 +12093,12 @@
       </c>
       <c r="P112" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R112" s="2" t="inlineStr">
@@ -12113,19 +12113,19 @@
       </c>
       <c r="T112" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000114号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000162号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="113" ht="42" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000292</t>
+          <t>RE-MLIT-14-00001724</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>小林工業株式会社</t>
+          <t>末広土地建物 株式会社</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -12135,7 +12135,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -12145,7 +12145,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -12195,12 +12195,12 @@
       </c>
       <c r="P113" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R113" s="2" t="inlineStr">
@@ -12215,19 +12215,19 @@
       </c>
       <c r="T113" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000292号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001724号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="114" ht="42" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000146</t>
+          <t>RE-MLIT-14-00000071</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>有限会社前橋不動産</t>
+          <t>東栄商事 株式会社</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -12247,7 +12247,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="P114" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R114" s="2" t="inlineStr">
@@ -12317,19 +12317,19 @@
       </c>
       <c r="T114" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000146号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000071号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="115" ht="42" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000098</t>
+          <t>RE-MLIT-14-00000060</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>有限会社田口不動産</t>
+          <t>東横不動産 株式会社</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -12339,7 +12339,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -12399,12 +12399,12 @@
       </c>
       <c r="P115" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R115" s="2" t="inlineStr">
@@ -12419,19 +12419,19 @@
       </c>
       <c r="T115" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000098号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="116" ht="42" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000302</t>
+          <t>RE-MLIT-14-00000013</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>朝日開発興業株式会社</t>
+          <t>株式会社 大谷商事</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="P116" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R116" s="2" t="inlineStr">
@@ -12521,19 +12521,19 @@
       </c>
       <c r="T116" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000302号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000013号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="117" ht="42" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000257</t>
+          <t>RE-MLIT-14-00001771</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>東神不動産株式会社</t>
+          <t>株式会社 日建</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -12543,7 +12543,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -12553,7 +12553,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -12603,12 +12603,12 @@
       </c>
       <c r="P117" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R117" s="2" t="inlineStr">
@@ -12623,19 +12623,19 @@
       </c>
       <c r="T117" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000257号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001771号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="118" ht="42" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000038</t>
+          <t>RE-MLIT-14-00000024</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>株式会社ティーエムエフ</t>
+          <t>浅間建設 株式会社</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -12645,7 +12645,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -12655,7 +12655,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -12705,12 +12705,12 @@
       </c>
       <c r="P118" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R118" s="2" t="inlineStr">
@@ -12725,19 +12725,19 @@
       </c>
       <c r="T118" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000038号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000024号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="119" ht="42" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000230</t>
+          <t>RE-MLIT-14-00000066</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>石橋建設工業株式会社 ※</t>
+          <t>相澤土地 株式会社</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -12747,7 +12747,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -12757,7 +12757,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -12807,12 +12807,12 @@
       </c>
       <c r="P119" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R119" s="2" t="inlineStr">
@@ -12827,19 +12827,19 @@
       </c>
       <c r="T119" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000230号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000066号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="120" ht="42" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000227</t>
+          <t>RE-MLIT-14-00001880</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>群馬不動産株式会社 ※</t>
+          <t>第一商事 株式会社</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -12859,7 +12859,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -12909,12 +12909,12 @@
       </c>
       <c r="P120" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R120" s="2" t="inlineStr">
@@ -12929,19 +12929,19 @@
       </c>
       <c r="T120" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000227号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001880号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="121" ht="42" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000075</t>
+          <t>RE-MLIT-14-00000198</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>鵜川興業株式会社</t>
+          <t>親和商事 有限会社</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -12951,7 +12951,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -12961,7 +12961,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -13011,12 +13011,12 @@
       </c>
       <c r="P121" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R121" s="2" t="inlineStr">
@@ -13031,19 +13031,19 @@
       </c>
       <c r="T121" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000075号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000198号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="122" ht="42" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001443</t>
+          <t>RE-MLIT-10-00000114</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>マルカン商事有限会社</t>
+          <t>上信電鉄株式会社</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -13063,7 +13063,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -13113,12 +13113,12 @@
       </c>
       <c r="P122" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R122" s="2" t="inlineStr">
@@ -13133,19 +13133,19 @@
       </c>
       <c r="T122" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001443号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000114号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="123" ht="42" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000204</t>
+          <t>RE-MLIT-10-00000292</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>一般財団法人笠間市開発公社</t>
+          <t>小林工業株式会社</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -13155,7 +13155,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -13165,7 +13165,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -13215,12 +13215,12 @@
       </c>
       <c r="P123" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R123" s="2" t="inlineStr">
@@ -13235,19 +13235,19 @@
       </c>
       <c r="T123" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000204号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000292号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="124" ht="42" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000014</t>
+          <t>RE-MLIT-10-00000146</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>下館土地株式会社</t>
+          <t>有限会社前橋不動産</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="P124" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R124" s="2" t="inlineStr">
@@ -13337,19 +13337,19 @@
       </c>
       <c r="T124" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000014号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000146号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="125" ht="42" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000167</t>
+          <t>RE-MLIT-10-00000098</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>公益財団法人茨城県開発公社</t>
+          <t>有限会社田口不動産</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -13369,7 +13369,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="P125" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R125" s="2" t="inlineStr">
@@ -13439,19 +13439,19 @@
       </c>
       <c r="T125" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000167号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000098号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="126" ht="42" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001278</t>
+          <t>RE-MLIT-10-00000302</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>大みか不動産株式会社</t>
+          <t>朝日開発興業株式会社</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -13521,12 +13521,12 @@
       </c>
       <c r="P126" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R126" s="2" t="inlineStr">
@@ -13541,19 +13541,19 @@
       </c>
       <c r="T126" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001278号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000302号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="127" ht="42" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000036</t>
+          <t>RE-MLIT-10-00000257</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>平和不動産株式会社</t>
+          <t>東神不動産株式会社</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -13563,7 +13563,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -13623,12 +13623,12 @@
       </c>
       <c r="P127" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R127" s="2" t="inlineStr">
@@ -13643,19 +13643,19 @@
       </c>
       <c r="T127" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000036号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000257号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="128" ht="42" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001437</t>
+          <t>RE-MLIT-10-00000038</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>斉丸土地</t>
+          <t>株式会社ティーエムエフ</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -13665,7 +13665,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -13675,7 +13675,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -13725,12 +13725,12 @@
       </c>
       <c r="P128" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R128" s="2" t="inlineStr">
@@ -13745,19 +13745,19 @@
       </c>
       <c r="T128" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001437号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000038号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="129" ht="42" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000106</t>
+          <t>RE-MLIT-10-00000230</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>有限会社岩田不動産</t>
+          <t>石橋建設工業株式会社 ※</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -13777,7 +13777,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -13827,12 +13827,12 @@
       </c>
       <c r="P129" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R129" s="2" t="inlineStr">
@@ -13847,19 +13847,19 @@
       </c>
       <c r="T129" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000106号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000230号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="130" ht="42" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001391</t>
+          <t>RE-MLIT-10-00000227</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>有限会社東栄</t>
+          <t>群馬不動産株式会社 ※</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -13869,7 +13869,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -13879,7 +13879,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -13929,12 +13929,12 @@
       </c>
       <c r="P130" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R130" s="2" t="inlineStr">
@@ -13949,19 +13949,19 @@
       </c>
       <c r="T130" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001391号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000227号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="131" ht="42" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000058</t>
+          <t>RE-MLIT-10-00000075</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>有限会社栄進</t>
+          <t>鵜川興業株式会社</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -13981,7 +13981,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -14031,12 +14031,12 @@
       </c>
       <c r="P131" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R131" s="2" t="inlineStr">
@@ -14051,19 +14051,19 @@
       </c>
       <c r="T131" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000058号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000075号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="132" ht="42" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000021</t>
+          <t>RE-MLIT-08-00001443</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>有限会社高橋商事</t>
+          <t>マルカン商事有限会社</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -14133,12 +14133,12 @@
       </c>
       <c r="P132" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R132" s="2" t="inlineStr">
@@ -14153,19 +14153,19 @@
       </c>
       <c r="T132" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000021号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第001443号; 自動追加日: 2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="133" ht="42" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001345</t>
+          <t>RE-MLIT-08-00000204</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>株式会社中野商事</t>
+          <t>一般財団法人笠間市開発公社</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -14235,12 +14235,12 @@
       </c>
       <c r="P133" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R133" s="2" t="inlineStr">
@@ -14255,19 +14255,19 @@
       </c>
       <c r="T133" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001345号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000204号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="134" ht="42" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001306</t>
+          <t>RE-MLIT-08-00000014</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>株式会社新栄土地</t>
+          <t>下館土地株式会社</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="P134" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R134" s="2" t="inlineStr">
@@ -14357,19 +14357,19 @@
       </c>
       <c r="T134" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001306号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000014号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="135" ht="42" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001321</t>
+          <t>RE-MLIT-08-00000167</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>株式会社水戸地産</t>
+          <t>公益財団法人茨城県開発公社</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -14439,12 +14439,12 @@
       </c>
       <c r="P135" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R135" s="2" t="inlineStr">
@@ -14459,19 +14459,19 @@
       </c>
       <c r="T135" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001321号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000167号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="136" ht="42" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001262</t>
+          <t>RE-MLIT-08-00001278</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>株式会社赤尾杉</t>
+          <t>大みか不動産株式会社</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -14561,19 +14561,19 @@
       </c>
       <c r="T136" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001262号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第001278号; 自動追加日: 2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="137" ht="42" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000110</t>
+          <t>RE-MLIT-08-00000036</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>株式会社野口物産</t>
+          <t>平和不動産株式会社</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -14663,19 +14663,19 @@
       </c>
       <c r="T137" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000110号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000036号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="138" ht="42" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001434</t>
+          <t>RE-MLIT-08-00001437</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>池田林業株式会社</t>
+          <t>斉丸土地</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -14765,19 +14765,19 @@
       </c>
       <c r="T138" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001434号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第001437号; 自動追加日: 2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="139" ht="42" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001302</t>
+          <t>RE-MLIT-08-00000106</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>荒沢不動産</t>
+          <t>有限会社岩田不動産</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -14847,12 +14847,12 @@
       </c>
       <c r="P139" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R139" s="2" t="inlineStr">
@@ -14867,19 +14867,19 @@
       </c>
       <c r="T139" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001302号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000106号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="140" ht="42" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000109</t>
+          <t>RE-MLIT-08-00001391</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>関友商事株式会社</t>
+          <t>有限会社東栄</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -14949,12 +14949,12 @@
       </c>
       <c r="P140" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R140" s="2" t="inlineStr">
@@ -14969,114 +14969,1134 @@
       </c>
       <c r="T140" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000109号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第001391号; 自動追加日: 2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="141" ht="42" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>RE-MLIT-08-00000058</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>有限会社栄進</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P141" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q141" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R141" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S141" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T141" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000058号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="42" customHeight="1">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000021</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>有限会社高橋商事</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P142" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q142" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R142" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S142" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T142" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000021号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="42" customHeight="1">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001345</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>株式会社中野商事</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P143" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q143" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R143" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S143" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T143" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001345号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="42" customHeight="1">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001306</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>株式会社新栄土地</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P144" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q144" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R144" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S144" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T144" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001306号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="42" customHeight="1">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001321</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>株式会社水戸地産</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P145" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q145" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R145" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S145" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T145" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001321号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="42" customHeight="1">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001262</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>株式会社赤尾杉</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P146" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q146" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R146" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S146" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T146" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001262号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="42" customHeight="1">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000110</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>株式会社野口物産</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P147" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q147" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R147" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S147" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T147" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000110号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="42" customHeight="1">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001434</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>池田林業株式会社</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P148" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q148" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R148" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S148" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T148" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001434号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="42" customHeight="1">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001302</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>荒沢不動産</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P149" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q149" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R149" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S149" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T149" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001302号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="42" customHeight="1">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000109</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>関友商事株式会社</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P150" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q150" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R150" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S150" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T150" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000109号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="42" customHeight="1">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
           <t>RE-MLIT-08-00000203</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>関東鉄道株式会社</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
         <is>
           <t>関東</t>
         </is>
       </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="I141" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
         <is>
           <t>土地・事業用</t>
         </is>
       </c>
-      <c r="J141" s="2" t="inlineStr">
+      <c r="J151" s="2" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="K141" s="3" t="inlineStr">
+      <c r="K151" s="3" t="inlineStr">
         <is>
           <t>https://www.kantetsu.co.jp/realestate/</t>
         </is>
       </c>
-      <c r="L141" s="3" t="inlineStr">
+      <c r="L151" s="3" t="inlineStr">
         <is>
           <t>https://www.kantetsu.co.jp/contact</t>
         </is>
       </c>
-      <c r="M141" s="3" t="inlineStr">
+      <c r="M151" s="3" t="inlineStr">
         <is>
           <t>https://www.kantetsu.co.jp/realestate/</t>
         </is>
       </c>
-      <c r="N141" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="O141" s="2" t="inlineStr">
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
         <is>
           <t>公式サイトを自動確認。問い合わせ導線あり</t>
         </is>
       </c>
-      <c r="P141" s="3" t="inlineStr">
+      <c r="P151" s="3" t="inlineStr">
         <is>
           <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1 | https://www.kantetsu.co.jp/realestate/ | https://www.kantetsu.co.jp/contact</t>
         </is>
       </c>
-      <c r="Q141" s="2" t="inlineStr">
+      <c r="Q151" s="2" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="R141" s="2" t="inlineStr">
+      <c r="R151" s="2" t="inlineStr">
         <is>
           <t>自動確認済み</t>
         </is>
       </c>
-      <c r="S141" s="2" t="inlineStr">
+      <c r="S151" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="T141" s="2" t="inlineStr">
+      <c r="T151" s="2" t="inlineStr">
         <is>
           <t>免許行政庁: 茨城県; 免許番号: 第000203号; 自動追加日: 2026-07-23; 公式サイト自動確認日: 2026-07-25</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T141"/>
+  <autoFilter ref="A1:T151"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -15144,156 +16164,169 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P45" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P50" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P52" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P53" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P54" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P55" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P56" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P57" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P58" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P59" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P60" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P61" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P62" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P63" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P64" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P65" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P66" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P67" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P68" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P69" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P70" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P71" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P72" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P73" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P74" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L75" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P75" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L76" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M76" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P76" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M77" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P77" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P78" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P79" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L80" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P80" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P81" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P82" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P83" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P84" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P85" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P86" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P87" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P88" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P89" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P90" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P91" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P92" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P93" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P94" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P95" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P96" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P97" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P98" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P99" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P100" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P101" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P102" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P103" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P104" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P105" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P106" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P107" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P108" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P109" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P110" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P111" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P112" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P113" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P114" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P115" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P116" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P117" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P118" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P119" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P120" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P121" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P122" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P123" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P124" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P125" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P126" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P127" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P128" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P129" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P130" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P131" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P132" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P133" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P134" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P135" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P136" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P137" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P138" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P139" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P140" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K141" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L141" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M141" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P45" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P50" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P52" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P53" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P54" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P55" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P56" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P57" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P58" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P59" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P60" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P61" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P62" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P63" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P64" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P65" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P66" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P67" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P68" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P69" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P70" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P71" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P72" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P73" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P74" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L75" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P75" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L76" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M76" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P76" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M77" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P77" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P78" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P79" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L80" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P80" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P81" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P82" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P83" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P84" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P85" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P86" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P87" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P88" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P89" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P90" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P91" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P92" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P93" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P94" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P95" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P96" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P97" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P98" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P99" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P100" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P101" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P102" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P103" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P104" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P105" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P106" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P107" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P108" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P109" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P110" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P111" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P112" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P113" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P114" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P115" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P116" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P117" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P118" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P119" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P120" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P121" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P122" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P123" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P124" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P125" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P126" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P127" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P128" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P129" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P130" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P131" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P132" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P133" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P134" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P135" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P136" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P137" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P138" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P139" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P140" r:id="rId211"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P141" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P142" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P143" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P144" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P145" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P146" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P147" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P148" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P149" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P150" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K151" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L151" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M151" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P151" r:id="rId225"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId213"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId226"/>
   </tableParts>
 </worksheet>
 </file>
@@ -15304,7 +16337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T132"/>
+  <dimension ref="A1:T142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17810,7 +18843,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -17820,52 +18853,52 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>土地・事業用</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.shamaison.com/saitama/shop/area/11215/2012100011123/</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.shamaison.com/contact-24h.html</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.shamaison.com/saitama/shop/area/11215/2012100011123/</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>04-2959-4560</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>公式サイトを自動確認。戸建て取扱表記あり。問い合わせ導線あり</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=11&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2 | https://www.shamaison.com/saitama/shop/area/11215/2012100011123/ | https://www.shamaison.com/contact-24h.html</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>自動確認済み</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -17875,7 +18908,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 埼玉県; 免許番号: 第001778号; 自動追加日: 2026-07-28</t>
+          <t>免許行政庁: 埼玉県; 免許番号: 第001778号; 自動追加日: 2026-07-28; 公式サイト自動確認日: 2026-07-31</t>
         </is>
       </c>
     </row>
@@ -22676,12 +23709,12 @@
     <row r="73" ht="42" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-09-00000002</t>
+          <t>RE-MLIT-09-00000905</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>丸栃不動産倉庫 株式会社</t>
+          <t>万不動産 株式会社</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -22751,12 +23784,12 @@
       </c>
       <c r="P73" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R73" s="2" t="inlineStr">
@@ -22771,19 +23804,19 @@
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 栃木県; 免許番号: 第000002号; 自動追加日: 2026-07-24</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000905号; 自動追加日: 2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="74" ht="42" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-09-00000064</t>
+          <t>RE-MLIT-09-00000002</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>前田不動産 株式会社</t>
+          <t>丸栃不動産倉庫 株式会社</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -22873,19 +23906,19 @@
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 栃木県; 免許番号: 第000064号; 自動追加日: 2026-07-24</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000002号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="75" ht="42" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-09-00000108</t>
+          <t>RE-MLIT-09-00000919</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>協立不動産 株式会社</t>
+          <t>八汐土地開発 株式会社</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -22955,12 +23988,12 @@
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R75" s="2" t="inlineStr">
@@ -22975,19 +24008,19 @@
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 栃木県; 免許番号: 第000108号; 自動追加日: 2026-07-24</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000919号; 自動追加日: 2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="76" ht="42" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-09-00000159</t>
+          <t>RE-MLIT-09-00000064</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>大国不動産 株式会社</t>
+          <t>前田不動産 株式会社</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -23077,19 +24110,19 @@
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 栃木県; 免許番号: 第000159号; 自動追加日: 2026-07-24</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000064号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="77" ht="42" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-09-00000168</t>
+          <t>RE-MLIT-09-00000108</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>小山土地建物 株式会社</t>
+          <t>協立不動産 株式会社</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -23179,19 +24212,19 @@
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 栃木県; 免許番号: 第000168号; 自動追加日: 2026-07-24</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000108号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="78" ht="42" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-09-00000062</t>
+          <t>RE-MLIT-09-00000159</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>小金井不動産 株式会社</t>
+          <t>大国不動産 株式会社</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -23281,19 +24314,19 @@
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 栃木県; 免許番号: 第000062号; 自動追加日: 2026-07-24</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000159号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="79" ht="42" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-09-00000054</t>
+          <t>RE-MLIT-09-00000168</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>昭和商事 株式会社</t>
+          <t>小山土地建物 株式会社</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -23383,19 +24416,19 @@
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 栃木県; 免許番号: 第000054号; 自動追加日: 2026-07-24</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000168号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="80" ht="42" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-09-00000022</t>
+          <t>RE-MLIT-09-00000062</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>有限会社 カワシマ不動産</t>
+          <t>小金井不動産 株式会社</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -23485,19 +24518,19 @@
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 栃木県; 免許番号: 第000022号; 自動追加日: 2026-07-24</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000062号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="81" ht="42" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-09-00000182</t>
+          <t>RE-MLIT-09-00000054</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>有限会社 東栄不動産</t>
+          <t>昭和商事 株式会社</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -23587,19 +24620,19 @@
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 栃木県; 免許番号: 第000182号; 自動追加日: 2026-07-24</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000054号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-09-00000117</t>
+          <t>RE-MLIT-09-00000022</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>株式会社 万建設興業</t>
+          <t>有限会社 カワシマ不動産</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -23689,19 +24722,19 @@
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 栃木県; 免許番号: 第000117号; 自動追加日: 2026-07-24</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000022号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00001852</t>
+          <t>RE-MLIT-09-00001009</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>オーナーズ商事 有限会社</t>
+          <t>有限会社 大福不動産</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -23711,7 +24744,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -23721,7 +24754,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -23771,12 +24804,12 @@
       </c>
       <c r="P83" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R83" s="2" t="inlineStr">
@@ -23791,19 +24824,19 @@
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第001852号; 自動追加日: 2026-07-27</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第001009号; 自動追加日: 2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00001691</t>
+          <t>RE-MLIT-09-00000182</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>一般財団法人 伊勢原市事業公社</t>
+          <t>有限会社 東栄不動産</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -23813,7 +24846,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -23823,7 +24856,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -23873,12 +24906,12 @@
       </c>
       <c r="P84" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R84" s="2" t="inlineStr">
@@ -23893,19 +24926,19 @@
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第001691号; 自動追加日: 2026-07-27</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000182号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00001737</t>
+          <t>RE-MLIT-09-00001050</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>丸万不動産 有限会社</t>
+          <t>有限会社 栃信総業</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -23915,7 +24948,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -23925,7 +24958,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -23975,12 +25008,12 @@
       </c>
       <c r="P85" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R85" s="2" t="inlineStr">
@@ -23995,19 +25028,19 @@
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第001737号; 自動追加日: 2026-07-27</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第001050号; 自動追加日: 2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="86" ht="42" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00001740</t>
+          <t>RE-MLIT-09-00000976</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>大和商事 株式会社</t>
+          <t>東照商事 株式会社</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -24017,7 +25050,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -24027,7 +25060,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -24077,12 +25110,12 @@
       </c>
       <c r="P86" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R86" s="2" t="inlineStr">
@@ -24097,19 +25130,19 @@
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第001740号; 自動追加日: 2026-07-27</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000976号; 自動追加日: 2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="87" ht="42" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000181</t>
+          <t>RE-MLIT-09-00000883</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>大栄興業 株式会社</t>
+          <t>株式会社 むぎくら</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -24119,7 +25152,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -24129,7 +25162,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -24179,12 +25212,12 @@
       </c>
       <c r="P87" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R87" s="2" t="inlineStr">
@@ -24199,19 +25232,19 @@
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000181号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000883号; 自動追加日: 2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00001608</t>
+          <t>RE-MLIT-09-00000117</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>川崎北部開発 株式会社</t>
+          <t>株式会社 万建設興業</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -24221,7 +25254,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -24231,7 +25264,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -24281,12 +25314,12 @@
       </c>
       <c r="P88" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R88" s="2" t="inlineStr">
@@ -24301,19 +25334,19 @@
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第001608号; 自動追加日: 2026-07-27</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000117号; 自動追加日: 2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="89" ht="42" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000260</t>
+          <t>RE-MLIT-09-00000903</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>有限会社 協和商事</t>
+          <t>株式会社 大竹不動産</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -24323,7 +25356,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -24333,7 +25366,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -24383,12 +25416,12 @@
       </c>
       <c r="P89" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R89" s="2" t="inlineStr">
@@ -24403,19 +25436,19 @@
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000260号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000903号; 自動追加日: 2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="90" ht="42" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00001851</t>
+          <t>RE-MLIT-09-00000949</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>有限会社 吉浜不動産</t>
+          <t>株式会社 大那商事</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -24425,7 +25458,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -24435,7 +25468,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -24485,12 +25518,12 @@
       </c>
       <c r="P90" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R90" s="2" t="inlineStr">
@@ -24505,19 +25538,19 @@
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第001851号; 自動追加日: 2026-07-27</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000949号; 自動追加日: 2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="91" ht="42" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000365</t>
+          <t>RE-MLIT-09-00000916</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>有限会社 小沢建設商事</t>
+          <t>株式会社 西崎</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -24527,7 +25560,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -24537,7 +25570,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -24587,12 +25620,12 @@
       </c>
       <c r="P91" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R91" s="2" t="inlineStr">
@@ -24607,19 +25640,19 @@
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000365号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000916号; 自動追加日: 2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="92" ht="42" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00001610</t>
+          <t>RE-MLIT-09-00000984</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>有限会社 柏菱</t>
+          <t>関東地所 株式会社</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -24629,7 +25662,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -24639,7 +25672,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -24689,12 +25722,12 @@
       </c>
       <c r="P92" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=09&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R92" s="2" t="inlineStr">
@@ -24709,19 +25742,19 @@
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第001610号; 自動追加日: 2026-07-27</t>
+          <t>免許行政庁: 栃木県; 免許番号: 第000984号; 自動追加日: 2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="93" ht="42" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000162</t>
+          <t>RE-MLIT-14-00001852</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>有限会社 濱屋</t>
+          <t>オーナーズ商事 有限会社</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -24791,12 +25824,12 @@
       </c>
       <c r="P93" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R93" s="2" t="inlineStr">
@@ -24811,19 +25844,19 @@
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000162号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001852号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="94" ht="42" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00001724</t>
+          <t>RE-MLIT-14-00001691</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>末広土地建物 株式会社</t>
+          <t>一般財団法人 伊勢原市事業公社</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -24913,19 +25946,19 @@
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第001724号; 自動追加日: 2026-07-27</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001691号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="95" ht="42" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000071</t>
+          <t>RE-MLIT-14-00001737</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>東栄商事 株式会社</t>
+          <t>丸万不動産 有限会社</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -24995,12 +26028,12 @@
       </c>
       <c r="P95" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R95" s="2" t="inlineStr">
@@ -25015,19 +26048,19 @@
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000071号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001737号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="96" ht="42" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000060</t>
+          <t>RE-MLIT-14-00001740</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>東横不動産 株式会社</t>
+          <t>大和商事 株式会社</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -25097,12 +26130,12 @@
       </c>
       <c r="P96" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R96" s="2" t="inlineStr">
@@ -25117,19 +26150,19 @@
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001740号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="97" ht="42" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000013</t>
+          <t>RE-MLIT-14-00000181</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>株式会社 大谷商事</t>
+          <t>大栄興業 株式会社</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -25219,19 +26252,19 @@
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000013号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000181号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="98" ht="42" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00001771</t>
+          <t>RE-MLIT-14-00001608</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>株式会社 日建</t>
+          <t>川崎北部開発 株式会社</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -25321,19 +26354,19 @@
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第001771号; 自動追加日: 2026-07-27</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001608号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="99" ht="42" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000024</t>
+          <t>RE-MLIT-14-00000260</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>浅間建設 株式会社</t>
+          <t>有限会社 協和商事</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -25423,19 +26456,19 @@
       </c>
       <c r="T99" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000024号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000260号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="100" ht="42" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000066</t>
+          <t>RE-MLIT-14-00001851</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>相澤土地 株式会社</t>
+          <t>有限会社 吉浜不動産</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -25505,12 +26538,12 @@
       </c>
       <c r="P100" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R100" s="2" t="inlineStr">
@@ -25525,19 +26558,19 @@
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000066号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001851号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="101" ht="42" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00001880</t>
+          <t>RE-MLIT-14-00000365</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>第一商事 株式会社</t>
+          <t>有限会社 小沢建設商事</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -25607,12 +26640,12 @@
       </c>
       <c r="P101" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R101" s="2" t="inlineStr">
@@ -25627,19 +26660,19 @@
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第001880号; 自動追加日: 2026-07-27</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000365号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="102" ht="42" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000198</t>
+          <t>RE-MLIT-14-00001610</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>親和商事 有限会社</t>
+          <t>有限会社 柏菱</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -25709,12 +26742,12 @@
       </c>
       <c r="P102" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R102" s="2" t="inlineStr">
@@ -25729,19 +26762,19 @@
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000198号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001610号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="103" ht="42" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000114</t>
+          <t>RE-MLIT-14-00000162</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>上信電鉄株式会社</t>
+          <t>有限会社 濱屋</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -25751,7 +26784,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -25761,7 +26794,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -25811,12 +26844,12 @@
       </c>
       <c r="P103" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R103" s="2" t="inlineStr">
@@ -25831,19 +26864,19 @@
       </c>
       <c r="T103" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000114号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000162号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="104" ht="42" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000292</t>
+          <t>RE-MLIT-14-00001724</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>小林工業株式会社</t>
+          <t>末広土地建物 株式会社</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -25853,7 +26886,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -25863,7 +26896,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -25913,12 +26946,12 @@
       </c>
       <c r="P104" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R104" s="2" t="inlineStr">
@@ -25933,19 +26966,19 @@
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000292号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001724号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="105" ht="42" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000146</t>
+          <t>RE-MLIT-14-00000071</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>有限会社前橋不動産</t>
+          <t>東栄商事 株式会社</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -25955,7 +26988,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -25965,7 +26998,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -26015,12 +27048,12 @@
       </c>
       <c r="P105" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R105" s="2" t="inlineStr">
@@ -26035,19 +27068,19 @@
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000146号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000071号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="106" ht="42" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000098</t>
+          <t>RE-MLIT-14-00000060</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>有限会社田口不動産</t>
+          <t>東横不動産 株式会社</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -26057,7 +27090,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -26067,7 +27100,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -26117,12 +27150,12 @@
       </c>
       <c r="P106" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R106" s="2" t="inlineStr">
@@ -26137,19 +27170,19 @@
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000098号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="107" ht="42" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000302</t>
+          <t>RE-MLIT-14-00000013</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>朝日開発興業株式会社</t>
+          <t>株式会社 大谷商事</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -26159,7 +27192,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -26169,7 +27202,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -26219,12 +27252,12 @@
       </c>
       <c r="P107" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R107" s="2" t="inlineStr">
@@ -26239,19 +27272,19 @@
       </c>
       <c r="T107" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000302号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000013号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="108" ht="42" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000257</t>
+          <t>RE-MLIT-14-00001771</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>東神不動産株式会社</t>
+          <t>株式会社 日建</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -26261,7 +27294,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -26271,7 +27304,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -26321,12 +27354,12 @@
       </c>
       <c r="P108" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R108" s="2" t="inlineStr">
@@ -26341,19 +27374,19 @@
       </c>
       <c r="T108" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000257号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001771号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="109" ht="42" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000038</t>
+          <t>RE-MLIT-14-00000024</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>株式会社ティーエムエフ</t>
+          <t>浅間建設 株式会社</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -26363,7 +27396,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -26373,7 +27406,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -26423,12 +27456,12 @@
       </c>
       <c r="P109" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R109" s="2" t="inlineStr">
@@ -26443,19 +27476,19 @@
       </c>
       <c r="T109" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000038号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000024号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="110" ht="42" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000230</t>
+          <t>RE-MLIT-14-00000066</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>石橋建設工業株式会社 ※</t>
+          <t>相澤土地 株式会社</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -26465,7 +27498,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -26475,7 +27508,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -26525,12 +27558,12 @@
       </c>
       <c r="P110" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R110" s="2" t="inlineStr">
@@ -26545,19 +27578,19 @@
       </c>
       <c r="T110" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000230号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000066号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="111" ht="42" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000227</t>
+          <t>RE-MLIT-14-00001880</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>群馬不動産株式会社 ※</t>
+          <t>第一商事 株式会社</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -26567,7 +27600,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -26577,7 +27610,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -26627,12 +27660,12 @@
       </c>
       <c r="P111" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R111" s="2" t="inlineStr">
@@ -26647,19 +27680,19 @@
       </c>
       <c r="T111" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000227号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001880号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="112" ht="42" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000075</t>
+          <t>RE-MLIT-14-00000198</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>鵜川興業株式会社</t>
+          <t>親和商事 有限会社</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -26669,7 +27702,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -26679,7 +27712,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -26729,12 +27762,12 @@
       </c>
       <c r="P112" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R112" s="2" t="inlineStr">
@@ -26749,19 +27782,19 @@
       </c>
       <c r="T112" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000075号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000198号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="113" ht="42" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001443</t>
+          <t>RE-MLIT-10-00000114</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>マルカン商事有限会社</t>
+          <t>上信電鉄株式会社</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -26771,7 +27804,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -26781,7 +27814,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -26831,12 +27864,12 @@
       </c>
       <c r="P113" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R113" s="2" t="inlineStr">
@@ -26851,19 +27884,19 @@
       </c>
       <c r="T113" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001443号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000114号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="114" ht="42" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000204</t>
+          <t>RE-MLIT-10-00000292</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>一般財団法人笠間市開発公社</t>
+          <t>小林工業株式会社</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -26873,7 +27906,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -26883,7 +27916,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -26933,12 +27966,12 @@
       </c>
       <c r="P114" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R114" s="2" t="inlineStr">
@@ -26953,19 +27986,19 @@
       </c>
       <c r="T114" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000204号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000292号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="115" ht="42" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000014</t>
+          <t>RE-MLIT-10-00000146</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>下館土地株式会社</t>
+          <t>有限会社前橋不動産</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -26975,7 +28008,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -26985,7 +28018,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -27035,12 +28068,12 @@
       </c>
       <c r="P115" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R115" s="2" t="inlineStr">
@@ -27055,19 +28088,19 @@
       </c>
       <c r="T115" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000014号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000146号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="116" ht="42" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000167</t>
+          <t>RE-MLIT-10-00000098</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>公益財団法人茨城県開発公社</t>
+          <t>有限会社田口不動産</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -27077,7 +28110,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -27087,7 +28120,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -27137,12 +28170,12 @@
       </c>
       <c r="P116" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R116" s="2" t="inlineStr">
@@ -27157,19 +28190,19 @@
       </c>
       <c r="T116" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000167号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000098号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="117" ht="42" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001278</t>
+          <t>RE-MLIT-10-00000302</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>大みか不動産株式会社</t>
+          <t>朝日開発興業株式会社</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -27179,7 +28212,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -27189,7 +28222,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -27239,12 +28272,12 @@
       </c>
       <c r="P117" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R117" s="2" t="inlineStr">
@@ -27259,19 +28292,19 @@
       </c>
       <c r="T117" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001278号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000302号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="118" ht="42" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000036</t>
+          <t>RE-MLIT-10-00000257</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>平和不動産株式会社</t>
+          <t>東神不動産株式会社</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -27281,7 +28314,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -27291,7 +28324,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -27341,12 +28374,12 @@
       </c>
       <c r="P118" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R118" s="2" t="inlineStr">
@@ -27361,19 +28394,19 @@
       </c>
       <c r="T118" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000036号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000257号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="119" ht="42" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001437</t>
+          <t>RE-MLIT-10-00000038</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>斉丸土地</t>
+          <t>株式会社ティーエムエフ</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -27383,7 +28416,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -27393,7 +28426,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -27443,12 +28476,12 @@
       </c>
       <c r="P119" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R119" s="2" t="inlineStr">
@@ -27463,19 +28496,19 @@
       </c>
       <c r="T119" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001437号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000038号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="120" ht="42" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000106</t>
+          <t>RE-MLIT-10-00000230</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>有限会社岩田不動産</t>
+          <t>石橋建設工業株式会社 ※</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -27485,7 +28518,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -27495,7 +28528,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -27545,12 +28578,12 @@
       </c>
       <c r="P120" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R120" s="2" t="inlineStr">
@@ -27565,19 +28598,19 @@
       </c>
       <c r="T120" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000106号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000230号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="121" ht="42" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001391</t>
+          <t>RE-MLIT-10-00000227</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>有限会社東栄</t>
+          <t>群馬不動産株式会社 ※</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -27587,7 +28620,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -27597,7 +28630,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -27647,12 +28680,12 @@
       </c>
       <c r="P121" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R121" s="2" t="inlineStr">
@@ -27667,19 +28700,19 @@
       </c>
       <c r="T121" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001391号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000227号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="122" ht="42" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000058</t>
+          <t>RE-MLIT-10-00000075</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>有限会社栄進</t>
+          <t>鵜川興業株式会社</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -27689,7 +28722,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -27699,7 +28732,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -27749,12 +28782,12 @@
       </c>
       <c r="P122" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R122" s="2" t="inlineStr">
@@ -27769,19 +28802,19 @@
       </c>
       <c r="T122" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000058号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000075号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="123" ht="42" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000021</t>
+          <t>RE-MLIT-08-00001443</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>有限会社高橋商事</t>
+          <t>マルカン商事有限会社</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -27851,12 +28884,12 @@
       </c>
       <c r="P123" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R123" s="2" t="inlineStr">
@@ -27871,19 +28904,19 @@
       </c>
       <c r="T123" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000021号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第001443号; 自動追加日: 2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="124" ht="42" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001345</t>
+          <t>RE-MLIT-08-00000204</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>株式会社中野商事</t>
+          <t>一般財団法人笠間市開発公社</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -27953,12 +28986,12 @@
       </c>
       <c r="P124" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R124" s="2" t="inlineStr">
@@ -27973,19 +29006,19 @@
       </c>
       <c r="T124" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001345号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000204号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="125" ht="42" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001306</t>
+          <t>RE-MLIT-08-00000014</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>株式会社新栄土地</t>
+          <t>下館土地株式会社</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -28055,12 +29088,12 @@
       </c>
       <c r="P125" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R125" s="2" t="inlineStr">
@@ -28075,19 +29108,19 @@
       </c>
       <c r="T125" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001306号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000014号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="126" ht="42" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001321</t>
+          <t>RE-MLIT-08-00000167</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>株式会社水戸地産</t>
+          <t>公益財団法人茨城県開発公社</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -28157,12 +29190,12 @@
       </c>
       <c r="P126" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R126" s="2" t="inlineStr">
@@ -28177,19 +29210,19 @@
       </c>
       <c r="T126" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001321号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000167号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="127" ht="42" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001262</t>
+          <t>RE-MLIT-08-00001278</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>株式会社赤尾杉</t>
+          <t>大みか不動産株式会社</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -28279,19 +29312,19 @@
       </c>
       <c r="T127" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001262号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第001278号; 自動追加日: 2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="128" ht="42" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000110</t>
+          <t>RE-MLIT-08-00000036</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>株式会社野口物産</t>
+          <t>平和不動産株式会社</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -28381,19 +29414,19 @@
       </c>
       <c r="T128" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000110号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000036号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="129" ht="42" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001434</t>
+          <t>RE-MLIT-08-00001437</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>池田林業株式会社</t>
+          <t>斉丸土地</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -28483,19 +29516,19 @@
       </c>
       <c r="T129" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001434号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第001437号; 自動追加日: 2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="130" ht="42" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001302</t>
+          <t>RE-MLIT-08-00000106</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>荒沢不動産</t>
+          <t>有限会社岩田不動産</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -28565,12 +29598,12 @@
       </c>
       <c r="P130" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R130" s="2" t="inlineStr">
@@ -28585,19 +29618,19 @@
       </c>
       <c r="T130" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001302号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000106号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="131" ht="42" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000109</t>
+          <t>RE-MLIT-08-00001391</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>関友商事株式会社</t>
+          <t>有限会社東栄</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -28667,12 +29700,12 @@
       </c>
       <c r="P131" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R131" s="2" t="inlineStr">
@@ -28687,114 +29720,1134 @@
       </c>
       <c r="T131" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000109号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第001391号; 自動追加日: 2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="132" ht="42" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>RE-MLIT-08-00000058</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>有限会社栄進</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P132" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q132" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R132" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S132" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T132" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000058号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="42" customHeight="1">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000021</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>有限会社高橋商事</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P133" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q133" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R133" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S133" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T133" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000021号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="42" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001345</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>株式会社中野商事</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P134" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q134" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R134" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S134" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T134" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001345号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="42" customHeight="1">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001306</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>株式会社新栄土地</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P135" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q135" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R135" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S135" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T135" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001306号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="42" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001321</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>株式会社水戸地産</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P136" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q136" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R136" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S136" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T136" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001321号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="42" customHeight="1">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001262</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>株式会社赤尾杉</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P137" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q137" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R137" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S137" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T137" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001262号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="42" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000110</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>株式会社野口物産</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P138" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q138" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R138" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S138" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T138" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000110号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="42" customHeight="1">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001434</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>池田林業株式会社</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P139" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q139" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R139" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S139" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T139" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001434号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="42" customHeight="1">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001302</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>荒沢不動産</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P140" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q140" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R140" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S140" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T140" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001302号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="42" customHeight="1">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000109</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>関友商事株式会社</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P141" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q141" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R141" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S141" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T141" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000109号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="42" customHeight="1">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
           <t>RE-MLIT-08-00000203</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>関東鉄道株式会社</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
         <is>
           <t>関東</t>
         </is>
       </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="I132" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
         <is>
           <t>土地・事業用</t>
         </is>
       </c>
-      <c r="J132" s="2" t="inlineStr">
+      <c r="J142" s="2" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="K132" s="3" t="inlineStr">
+      <c r="K142" s="3" t="inlineStr">
         <is>
           <t>https://www.kantetsu.co.jp/realestate/</t>
         </is>
       </c>
-      <c r="L132" s="3" t="inlineStr">
+      <c r="L142" s="3" t="inlineStr">
         <is>
           <t>https://www.kantetsu.co.jp/contact</t>
         </is>
       </c>
-      <c r="M132" s="3" t="inlineStr">
+      <c r="M142" s="3" t="inlineStr">
         <is>
           <t>https://www.kantetsu.co.jp/realestate/</t>
         </is>
       </c>
-      <c r="N132" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="O132" s="2" t="inlineStr">
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
         <is>
           <t>公式サイトを自動確認。問い合わせ導線あり</t>
         </is>
       </c>
-      <c r="P132" s="3" t="inlineStr">
+      <c r="P142" s="3" t="inlineStr">
         <is>
           <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1 | https://www.kantetsu.co.jp/realestate/ | https://www.kantetsu.co.jp/contact</t>
         </is>
       </c>
-      <c r="Q132" s="2" t="inlineStr">
+      <c r="Q142" s="2" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="R132" s="2" t="inlineStr">
+      <c r="R142" s="2" t="inlineStr">
         <is>
           <t>自動確認済み</t>
         </is>
       </c>
-      <c r="S132" s="2" t="inlineStr">
+      <c r="S142" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="T132" s="2" t="inlineStr">
+      <c r="T142" s="2" t="inlineStr">
         <is>
           <t>免許行政庁: 茨城県; 免許番号: 第000203号; 自動追加日: 2026-07-23; 公式サイト自動確認日: 2026-07-25</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T132"/>
+  <autoFilter ref="A1:T142"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId2"/>
@@ -28826,156 +30879,169 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P45" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P50" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P52" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P53" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P54" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P55" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P56" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P57" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P58" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P59" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P60" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P61" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P62" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P63" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P64" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P65" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P66" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M67" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P67" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M68" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P68" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P69" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P70" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M71" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P71" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P72" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P73" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P74" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P75" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P76" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P77" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P78" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P79" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P80" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P81" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P82" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P83" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P84" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P85" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P86" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P87" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P88" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P89" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P90" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P91" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P92" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P93" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P94" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P95" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P96" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P97" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P98" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P99" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P100" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P101" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P102" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P103" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P104" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P105" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P106" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P107" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P108" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P109" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P110" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P111" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P112" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P113" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P114" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P115" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P116" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P117" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P118" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P119" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P120" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P121" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P122" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P123" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P124" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P125" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P126" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P127" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P128" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P129" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P130" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P131" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L132" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M132" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P45" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P50" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P52" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P53" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P54" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P55" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P56" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P57" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P58" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P59" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P60" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P61" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P62" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P63" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P64" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P65" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P66" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M67" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P67" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M68" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P68" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P69" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P70" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M71" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P71" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P72" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P73" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P74" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P75" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P76" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P77" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P78" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P79" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P80" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P81" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P82" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P83" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P84" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P85" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P86" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P87" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P88" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P89" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P90" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P91" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P92" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P93" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P94" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P95" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P96" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P97" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P98" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P99" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P100" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P101" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P102" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P103" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P104" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P105" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P106" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P107" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P108" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P109" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P110" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P111" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P112" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P113" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P114" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P115" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P116" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P117" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P118" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P119" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P120" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P121" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P122" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P123" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P124" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P125" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P126" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P127" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P128" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P129" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P130" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P131" r:id="rId175"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P132" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P133" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P134" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P135" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P136" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P137" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P138" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P139" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P140" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P141" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K142" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L142" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M142" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P142" r:id="rId189"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId177"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId190"/>
   </tableParts>
 </worksheet>
 </file>

--- a/database/real_estate_brokers.xlsx
+++ b/database/real_estate_brokers.xlsx
@@ -17,8 +17,8 @@
     <sheet name="データ辞書" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全社一覧'!$A$1:$T$151</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'関東'!$A$1:$T$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全社一覧'!$A$1:$T$161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'関東'!$A$1:$T$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'北海道・東北'!$A$1:$T$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'近畿'!$A$1:$T$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'中国・四国'!$A$1:$T$2</definedName>
@@ -177,8 +177,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_9e7587520fcb" displayName="T_9e7587520fcb" ref="A1:T151" headerRowCount="1">
-  <autoFilter ref="A1:T151"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_9e7587520fcb" displayName="T_9e7587520fcb" ref="A1:T161" headerRowCount="1">
+  <autoFilter ref="A1:T161"/>
   <tableColumns count="20">
     <tableColumn id="1" name="会社ID"/>
     <tableColumn id="2" name="会社名"/>
@@ -206,8 +206,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_92ae89f64a96" displayName="T_92ae89f64a96" ref="A1:T142" headerRowCount="1">
-  <autoFilter ref="A1:T142"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_92ae89f64a96" displayName="T_92ae89f64a96" ref="A1:T152" headerRowCount="1">
+  <autoFilter ref="A1:T152"/>
   <tableColumns count="20">
     <tableColumn id="1" name="会社ID"/>
     <tableColumn id="2" name="会社名"/>
@@ -668,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T151"/>
+  <dimension ref="A1:T161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cue-net.or.jp/index.html</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cue-net.or.jp/contact/index.html</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cue-net.or.jp/index.html</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>04-7134-2015</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>公式サイトを自動確認。問い合わせ導線あり</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2 | https://www.cue-net.or.jp/index.html | https://www.cue-net.or.jp/contact/index.html</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>自動確認済み</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 千葉県; 免許番号: 第001770号; 自動追加日: 2026-07-29</t>
+          <t>免許行政庁: 千葉県; 免許番号: 第001770号; 自動追加日: 2026-07-29; 公式サイト自動確認日: 2026-08-01</t>
         </is>
       </c>
     </row>
@@ -13140,12 +13140,12 @@
     <row r="123" ht="42" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000292</t>
+          <t>RE-MLIT-10-00001246</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>小林工業株式会社</t>
+          <t>五料不動産</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -13215,12 +13215,12 @@
       </c>
       <c r="P123" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R123" s="2" t="inlineStr">
@@ -13235,19 +13235,19 @@
       </c>
       <c r="T123" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000292号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001246号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="124" ht="42" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000146</t>
+          <t>RE-MLIT-10-00001228</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>有限会社前橋不動産</t>
+          <t>吾妻開発株式会社</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="P124" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R124" s="2" t="inlineStr">
@@ -13337,19 +13337,19 @@
       </c>
       <c r="T124" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000146号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001228号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="125" ht="42" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000098</t>
+          <t>RE-MLIT-10-00001285</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>有限会社田口不動産</t>
+          <t>大誠不動産商事有限会社</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="P125" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R125" s="2" t="inlineStr">
@@ -13439,19 +13439,19 @@
       </c>
       <c r="T125" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000098号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001285号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="126" ht="42" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000302</t>
+          <t>RE-MLIT-10-00000292</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>朝日開発興業株式会社</t>
+          <t>小林工業株式会社</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -13541,19 +13541,19 @@
       </c>
       <c r="T126" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000302号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000292号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="127" ht="42" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000257</t>
+          <t>RE-MLIT-10-00001354</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>東神不動産株式会社</t>
+          <t>小此木不動産建設有限会社</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -13623,12 +13623,12 @@
       </c>
       <c r="P127" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R127" s="2" t="inlineStr">
@@ -13643,19 +13643,19 @@
       </c>
       <c r="T127" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000257号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001354号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="128" ht="42" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000038</t>
+          <t>RE-MLIT-10-00001234</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>株式会社ティーエムエフ</t>
+          <t>小野里工業株式会社</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -13725,12 +13725,12 @@
       </c>
       <c r="P128" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R128" s="2" t="inlineStr">
@@ -13745,19 +13745,19 @@
       </c>
       <c r="T128" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000038号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001234号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="129" ht="42" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000230</t>
+          <t>RE-MLIT-10-00001334</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>石橋建設工業株式会社 ※</t>
+          <t>日聖産業株式会社</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -13827,12 +13827,12 @@
       </c>
       <c r="P129" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R129" s="2" t="inlineStr">
@@ -13847,19 +13847,19 @@
       </c>
       <c r="T129" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000230号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001334号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="130" ht="42" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000227</t>
+          <t>RE-MLIT-10-00000146</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>群馬不動産株式会社 ※</t>
+          <t>有限会社前橋不動産</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -13949,19 +13949,19 @@
       </c>
       <c r="T130" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000227号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000146号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="131" ht="42" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000075</t>
+          <t>RE-MLIT-10-00001358</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>鵜川興業株式会社</t>
+          <t>有限会社吾妻不動産</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -14031,12 +14031,12 @@
       </c>
       <c r="P131" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R131" s="2" t="inlineStr">
@@ -14051,19 +14051,19 @@
       </c>
       <c r="T131" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000075号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001358号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="132" ht="42" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001443</t>
+          <t>RE-MLIT-10-00000098</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>マルカン商事有限会社</t>
+          <t>有限会社田口不動産</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -14073,7 +14073,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -14083,7 +14083,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -14133,12 +14133,12 @@
       </c>
       <c r="P132" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R132" s="2" t="inlineStr">
@@ -14153,19 +14153,19 @@
       </c>
       <c r="T132" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001443号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000098号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="133" ht="42" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000204</t>
+          <t>RE-MLIT-10-00000302</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>一般財団法人笠間市開発公社</t>
+          <t>朝日開発興業株式会社</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -14175,7 +14175,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -14185,7 +14185,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -14235,12 +14235,12 @@
       </c>
       <c r="P133" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R133" s="2" t="inlineStr">
@@ -14255,19 +14255,19 @@
       </c>
       <c r="T133" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000204号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000302号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="134" ht="42" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000014</t>
+          <t>RE-MLIT-10-00000257</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>下館土地株式会社</t>
+          <t>東神不動産株式会社</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -14277,7 +14277,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -14287,7 +14287,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="P134" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R134" s="2" t="inlineStr">
@@ -14357,19 +14357,19 @@
       </c>
       <c r="T134" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000014号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000257号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="135" ht="42" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000167</t>
+          <t>RE-MLIT-10-00000038</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>公益財団法人茨城県開発公社</t>
+          <t>株式会社ティーエムエフ</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -14379,7 +14379,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -14389,7 +14389,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -14439,12 +14439,12 @@
       </c>
       <c r="P135" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R135" s="2" t="inlineStr">
@@ -14459,19 +14459,19 @@
       </c>
       <c r="T135" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000167号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000038号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="136" ht="42" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001278</t>
+          <t>RE-MLIT-10-00001331</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>大みか不動産株式会社</t>
+          <t>株式会社黒沢商事</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -14481,7 +14481,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -14491,7 +14491,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -14541,12 +14541,12 @@
       </c>
       <c r="P136" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R136" s="2" t="inlineStr">
@@ -14561,19 +14561,19 @@
       </c>
       <c r="T136" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001278号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001331号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="137" ht="42" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000036</t>
+          <t>RE-MLIT-10-00001355</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>平和不動産株式会社</t>
+          <t>橋本商事株式会社</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -14593,7 +14593,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -14643,12 +14643,12 @@
       </c>
       <c r="P137" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R137" s="2" t="inlineStr">
@@ -14663,19 +14663,19 @@
       </c>
       <c r="T137" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000036号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001355号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="138" ht="42" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001437</t>
+          <t>RE-MLIT-10-00000230</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>斉丸土地</t>
+          <t>石橋建設工業株式会社 ※</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -14745,12 +14745,12 @@
       </c>
       <c r="P138" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R138" s="2" t="inlineStr">
@@ -14765,19 +14765,19 @@
       </c>
       <c r="T138" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001437号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000230号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="139" ht="42" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000106</t>
+          <t>RE-MLIT-10-00000227</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>有限会社岩田不動産</t>
+          <t>群馬不動産株式会社 ※</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -14787,7 +14787,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -14797,7 +14797,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -14847,12 +14847,12 @@
       </c>
       <c r="P139" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R139" s="2" t="inlineStr">
@@ -14867,19 +14867,19 @@
       </c>
       <c r="T139" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000106号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000227号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="140" ht="42" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001391</t>
+          <t>RE-MLIT-10-00001324</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>有限会社東栄</t>
+          <t>高前産業株式会社</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -14889,7 +14889,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -14899,7 +14899,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -14949,12 +14949,12 @@
       </c>
       <c r="P140" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R140" s="2" t="inlineStr">
@@ -14969,19 +14969,19 @@
       </c>
       <c r="T140" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001391号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001324号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="141" ht="42" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000058</t>
+          <t>RE-MLIT-10-00000075</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>有限会社栄進</t>
+          <t>鵜川興業株式会社</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -15001,7 +15001,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -15051,12 +15051,12 @@
       </c>
       <c r="P141" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R141" s="2" t="inlineStr">
@@ -15071,19 +15071,19 @@
       </c>
       <c r="T141" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000058号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000075号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="142" ht="42" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000021</t>
+          <t>RE-MLIT-08-00001443</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>有限会社高橋商事</t>
+          <t>マルカン商事有限会社</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -15153,12 +15153,12 @@
       </c>
       <c r="P142" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R142" s="2" t="inlineStr">
@@ -15173,19 +15173,19 @@
       </c>
       <c r="T142" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000021号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第001443号; 自動追加日: 2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="143" ht="42" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001345</t>
+          <t>RE-MLIT-08-00000204</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>株式会社中野商事</t>
+          <t>一般財団法人笠間市開発公社</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -15255,12 +15255,12 @@
       </c>
       <c r="P143" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R143" s="2" t="inlineStr">
@@ -15275,19 +15275,19 @@
       </c>
       <c r="T143" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001345号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000204号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="144" ht="42" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001306</t>
+          <t>RE-MLIT-08-00000014</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>株式会社新栄土地</t>
+          <t>下館土地株式会社</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -15357,12 +15357,12 @@
       </c>
       <c r="P144" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R144" s="2" t="inlineStr">
@@ -15377,19 +15377,19 @@
       </c>
       <c r="T144" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001306号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000014号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="145" ht="42" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001321</t>
+          <t>RE-MLIT-08-00000167</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>株式会社水戸地産</t>
+          <t>公益財団法人茨城県開発公社</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -15459,12 +15459,12 @@
       </c>
       <c r="P145" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R145" s="2" t="inlineStr">
@@ -15479,19 +15479,19 @@
       </c>
       <c r="T145" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001321号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000167号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="146" ht="42" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001262</t>
+          <t>RE-MLIT-08-00001278</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>株式会社赤尾杉</t>
+          <t>大みか不動産株式会社</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -15581,19 +15581,19 @@
       </c>
       <c r="T146" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001262号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第001278号; 自動追加日: 2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="147" ht="42" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000110</t>
+          <t>RE-MLIT-08-00000036</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>株式会社野口物産</t>
+          <t>平和不動産株式会社</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -15683,19 +15683,19 @@
       </c>
       <c r="T147" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000110号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000036号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="148" ht="42" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001434</t>
+          <t>RE-MLIT-08-00001437</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>池田林業株式会社</t>
+          <t>斉丸土地</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -15785,19 +15785,19 @@
       </c>
       <c r="T148" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001434号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第001437号; 自動追加日: 2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="149" ht="42" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001302</t>
+          <t>RE-MLIT-08-00000106</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>荒沢不動産</t>
+          <t>有限会社岩田不動産</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -15867,12 +15867,12 @@
       </c>
       <c r="P149" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R149" s="2" t="inlineStr">
@@ -15887,19 +15887,19 @@
       </c>
       <c r="T149" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001302号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000106号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="150" ht="42" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000109</t>
+          <t>RE-MLIT-08-00001391</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>関友商事株式会社</t>
+          <t>有限会社東栄</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -15969,12 +15969,12 @@
       </c>
       <c r="P150" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R150" s="2" t="inlineStr">
@@ -15989,114 +15989,1134 @@
       </c>
       <c r="T150" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000109号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第001391号; 自動追加日: 2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="151" ht="42" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>RE-MLIT-08-00000058</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>有限会社栄進</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P151" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q151" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R151" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S151" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T151" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000058号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="42" customHeight="1">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000021</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>有限会社高橋商事</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P152" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R152" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S152" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T152" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000021号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="42" customHeight="1">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001345</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>株式会社中野商事</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P153" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q153" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R153" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S153" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T153" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001345号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="42" customHeight="1">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001306</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>株式会社新栄土地</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P154" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q154" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R154" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S154" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T154" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001306号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="42" customHeight="1">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001321</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>株式会社水戸地産</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P155" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q155" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R155" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S155" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T155" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001321号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="42" customHeight="1">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001262</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>株式会社赤尾杉</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P156" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q156" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R156" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S156" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T156" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001262号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="42" customHeight="1">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000110</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>株式会社野口物産</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P157" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q157" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R157" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S157" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T157" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000110号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="42" customHeight="1">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001434</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>池田林業株式会社</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P158" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q158" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R158" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S158" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T158" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001434号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="42" customHeight="1">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001302</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>荒沢不動産</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P159" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q159" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R159" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S159" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T159" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001302号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="42" customHeight="1">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000109</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>関友商事株式会社</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P160" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R160" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S160" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T160" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000109号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="42" customHeight="1">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
           <t>RE-MLIT-08-00000203</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>関東鉄道株式会社</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
         <is>
           <t>関東</t>
         </is>
       </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="H151" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="I151" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
         <is>
           <t>土地・事業用</t>
         </is>
       </c>
-      <c r="J151" s="2" t="inlineStr">
+      <c r="J161" s="2" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="K151" s="3" t="inlineStr">
+      <c r="K161" s="3" t="inlineStr">
         <is>
           <t>https://www.kantetsu.co.jp/realestate/</t>
         </is>
       </c>
-      <c r="L151" s="3" t="inlineStr">
+      <c r="L161" s="3" t="inlineStr">
         <is>
           <t>https://www.kantetsu.co.jp/contact</t>
         </is>
       </c>
-      <c r="M151" s="3" t="inlineStr">
+      <c r="M161" s="3" t="inlineStr">
         <is>
           <t>https://www.kantetsu.co.jp/realestate/</t>
         </is>
       </c>
-      <c r="N151" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="O151" s="2" t="inlineStr">
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
         <is>
           <t>公式サイトを自動確認。問い合わせ導線あり</t>
         </is>
       </c>
-      <c r="P151" s="3" t="inlineStr">
+      <c r="P161" s="3" t="inlineStr">
         <is>
           <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1 | https://www.kantetsu.co.jp/realestate/ | https://www.kantetsu.co.jp/contact</t>
         </is>
       </c>
-      <c r="Q151" s="2" t="inlineStr">
+      <c r="Q161" s="2" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="R151" s="2" t="inlineStr">
+      <c r="R161" s="2" t="inlineStr">
         <is>
           <t>自動確認済み</t>
         </is>
       </c>
-      <c r="S151" s="2" t="inlineStr">
+      <c r="S161" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="T151" s="2" t="inlineStr">
+      <c r="T161" s="2" t="inlineStr">
         <is>
           <t>免許行政庁: 茨城県; 免許番号: 第000203号; 自動追加日: 2026-07-23; 公式サイト自動確認日: 2026-07-25</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T151"/>
+  <autoFilter ref="A1:T161"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -16135,198 +17155,211 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P45" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P50" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P52" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P53" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P54" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P55" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P56" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P57" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P58" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P59" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P60" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P61" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P62" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P63" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P64" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P65" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P66" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P67" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P68" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P69" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P70" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P71" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P72" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P73" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P74" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L75" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P75" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L76" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M76" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P76" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M77" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P77" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P78" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P79" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L80" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P80" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P81" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P82" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P83" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P84" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P85" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P86" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P87" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P88" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P89" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P90" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P91" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P92" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P93" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P94" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P95" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P96" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P97" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P98" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P99" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P100" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P101" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P102" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P103" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P104" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P105" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P106" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P107" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P108" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P109" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P110" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P111" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P112" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P113" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P114" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P115" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P116" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P117" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P118" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P119" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P120" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P121" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P122" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P123" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P124" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P125" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P126" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P127" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P128" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P129" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P130" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P131" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P132" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P133" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P134" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P135" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P136" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P137" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P138" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P139" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P140" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P141" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P142" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P143" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P144" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P145" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P146" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P147" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P148" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P149" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P150" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K151" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L151" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M151" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P45" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P50" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P52" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P53" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P54" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P55" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P56" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P58" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P59" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P60" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P61" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P62" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P63" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P64" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P65" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P66" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P67" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P68" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P69" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P70" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P71" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P72" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P73" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P74" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L75" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P75" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L76" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M76" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P76" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M77" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P77" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P78" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P79" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L80" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P80" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P81" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P82" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P83" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P84" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P85" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P86" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P87" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P88" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P89" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P90" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P91" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P92" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P93" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P94" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P95" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P96" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P97" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P98" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P99" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P100" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P101" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P102" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P103" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P104" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P105" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P106" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P107" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P108" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P109" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P110" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P111" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P112" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P113" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P114" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P115" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P116" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P117" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P118" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P119" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P120" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P121" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P122" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P123" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P124" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P125" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P126" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P127" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P128" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P129" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P130" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P131" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P132" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P133" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P134" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P135" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P136" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P137" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P138" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P139" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P140" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P141" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P142" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P143" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P144" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P145" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P146" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P147" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P148" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P149" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P150" r:id="rId224"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P151" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P152" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P153" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P154" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P155" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P156" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P157" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P158" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P159" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P160" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K161" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L161" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M161" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P161" r:id="rId238"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId226"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId239"/>
   </tableParts>
 </worksheet>
 </file>
@@ -16337,7 +17370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T142"/>
+  <dimension ref="A1:T152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16614,47 +17647,47 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cue-net.or.jp/index.html</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cue-net.or.jp/contact/index.html</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cue-net.or.jp/index.html</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>04-7134-2015</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>公式サイトを自動確認。問い合わせ導線あり</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=12&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2 | https://www.cue-net.or.jp/index.html | https://www.cue-net.or.jp/contact/index.html</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>自動確認済み</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
@@ -16664,7 +17697,7 @@
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 千葉県; 免許番号: 第001770号; 自動追加日: 2026-07-29</t>
+          <t>免許行政庁: 千葉県; 免許番号: 第001770号; 自動追加日: 2026-07-29; 公式サイト自動確認日: 2026-08-01</t>
         </is>
       </c>
     </row>
@@ -27891,12 +28924,12 @@
     <row r="114" ht="42" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000292</t>
+          <t>RE-MLIT-10-00001246</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>小林工業株式会社</t>
+          <t>五料不動産</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -27966,12 +28999,12 @@
       </c>
       <c r="P114" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R114" s="2" t="inlineStr">
@@ -27986,19 +29019,19 @@
       </c>
       <c r="T114" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000292号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001246号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="115" ht="42" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000146</t>
+          <t>RE-MLIT-10-00001228</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>有限会社前橋不動産</t>
+          <t>吾妻開発株式会社</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -28068,12 +29101,12 @@
       </c>
       <c r="P115" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R115" s="2" t="inlineStr">
@@ -28088,19 +29121,19 @@
       </c>
       <c r="T115" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000146号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001228号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="116" ht="42" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000098</t>
+          <t>RE-MLIT-10-00001285</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>有限会社田口不動産</t>
+          <t>大誠不動産商事有限会社</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -28170,12 +29203,12 @@
       </c>
       <c r="P116" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R116" s="2" t="inlineStr">
@@ -28190,19 +29223,19 @@
       </c>
       <c r="T116" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000098号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001285号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="117" ht="42" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000302</t>
+          <t>RE-MLIT-10-00000292</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>朝日開発興業株式会社</t>
+          <t>小林工業株式会社</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -28292,19 +29325,19 @@
       </c>
       <c r="T117" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000302号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000292号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="118" ht="42" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000257</t>
+          <t>RE-MLIT-10-00001354</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>東神不動産株式会社</t>
+          <t>小此木不動産建設有限会社</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -28374,12 +29407,12 @@
       </c>
       <c r="P118" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R118" s="2" t="inlineStr">
@@ -28394,19 +29427,19 @@
       </c>
       <c r="T118" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000257号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001354号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="119" ht="42" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000038</t>
+          <t>RE-MLIT-10-00001234</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>株式会社ティーエムエフ</t>
+          <t>小野里工業株式会社</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -28476,12 +29509,12 @@
       </c>
       <c r="P119" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R119" s="2" t="inlineStr">
@@ -28496,19 +29529,19 @@
       </c>
       <c r="T119" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000038号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001234号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="120" ht="42" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000230</t>
+          <t>RE-MLIT-10-00001334</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>石橋建設工業株式会社 ※</t>
+          <t>日聖産業株式会社</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -28578,12 +29611,12 @@
       </c>
       <c r="P120" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R120" s="2" t="inlineStr">
@@ -28598,19 +29631,19 @@
       </c>
       <c r="T120" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000230号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001334号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="121" ht="42" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000227</t>
+          <t>RE-MLIT-10-00000146</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>群馬不動産株式会社 ※</t>
+          <t>有限会社前橋不動産</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -28700,19 +29733,19 @@
       </c>
       <c r="T121" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000227号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000146号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="122" ht="42" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000075</t>
+          <t>RE-MLIT-10-00001358</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>鵜川興業株式会社</t>
+          <t>有限会社吾妻不動産</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -28782,12 +29815,12 @@
       </c>
       <c r="P122" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R122" s="2" t="inlineStr">
@@ -28802,19 +29835,19 @@
       </c>
       <c r="T122" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000075号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001358号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="123" ht="42" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001443</t>
+          <t>RE-MLIT-10-00000098</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>マルカン商事有限会社</t>
+          <t>有限会社田口不動産</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -28824,7 +29857,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -28834,7 +29867,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -28884,12 +29917,12 @@
       </c>
       <c r="P123" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R123" s="2" t="inlineStr">
@@ -28904,19 +29937,19 @@
       </c>
       <c r="T123" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001443号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000098号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="124" ht="42" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000204</t>
+          <t>RE-MLIT-10-00000302</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>一般財団法人笠間市開発公社</t>
+          <t>朝日開発興業株式会社</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -28926,7 +29959,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -28936,7 +29969,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -28986,12 +30019,12 @@
       </c>
       <c r="P124" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R124" s="2" t="inlineStr">
@@ -29006,19 +30039,19 @@
       </c>
       <c r="T124" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000204号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000302号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="125" ht="42" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000014</t>
+          <t>RE-MLIT-10-00000257</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>下館土地株式会社</t>
+          <t>東神不動産株式会社</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -29028,7 +30061,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -29038,7 +30071,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -29088,12 +30121,12 @@
       </c>
       <c r="P125" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R125" s="2" t="inlineStr">
@@ -29108,19 +30141,19 @@
       </c>
       <c r="T125" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000014号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000257号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="126" ht="42" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000167</t>
+          <t>RE-MLIT-10-00000038</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>公益財団法人茨城県開発公社</t>
+          <t>株式会社ティーエムエフ</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -29130,7 +30163,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -29140,7 +30173,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -29190,12 +30223,12 @@
       </c>
       <c r="P126" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R126" s="2" t="inlineStr">
@@ -29210,19 +30243,19 @@
       </c>
       <c r="T126" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000167号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000038号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="127" ht="42" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001278</t>
+          <t>RE-MLIT-10-00001331</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>大みか不動産株式会社</t>
+          <t>株式会社黒沢商事</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -29232,7 +30265,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -29242,7 +30275,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -29292,12 +30325,12 @@
       </c>
       <c r="P127" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R127" s="2" t="inlineStr">
@@ -29312,19 +30345,19 @@
       </c>
       <c r="T127" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001278号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001331号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="128" ht="42" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000036</t>
+          <t>RE-MLIT-10-00001355</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>平和不動産株式会社</t>
+          <t>橋本商事株式会社</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -29334,7 +30367,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -29344,7 +30377,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -29394,12 +30427,12 @@
       </c>
       <c r="P128" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R128" s="2" t="inlineStr">
@@ -29414,19 +30447,19 @@
       </c>
       <c r="T128" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000036号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001355号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="129" ht="42" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001437</t>
+          <t>RE-MLIT-10-00000230</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>斉丸土地</t>
+          <t>石橋建設工業株式会社 ※</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -29436,7 +30469,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -29446,7 +30479,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -29496,12 +30529,12 @@
       </c>
       <c r="P129" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R129" s="2" t="inlineStr">
@@ -29516,19 +30549,19 @@
       </c>
       <c r="T129" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001437号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000230号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="130" ht="42" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000106</t>
+          <t>RE-MLIT-10-00000227</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>有限会社岩田不動産</t>
+          <t>群馬不動産株式会社 ※</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -29538,7 +30571,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -29548,7 +30581,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -29598,12 +30631,12 @@
       </c>
       <c r="P130" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R130" s="2" t="inlineStr">
@@ -29618,19 +30651,19 @@
       </c>
       <c r="T130" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000106号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000227号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="131" ht="42" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001391</t>
+          <t>RE-MLIT-10-00001324</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>有限会社東栄</t>
+          <t>高前産業株式会社</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -29640,7 +30673,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -29650,7 +30683,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -29700,12 +30733,12 @@
       </c>
       <c r="P131" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R131" s="2" t="inlineStr">
@@ -29720,19 +30753,19 @@
       </c>
       <c r="T131" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001391号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001324号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="132" ht="42" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000058</t>
+          <t>RE-MLIT-10-00000075</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>有限会社栄進</t>
+          <t>鵜川興業株式会社</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -29742,7 +30775,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -29752,7 +30785,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -29802,12 +30835,12 @@
       </c>
       <c r="P132" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R132" s="2" t="inlineStr">
@@ -29822,19 +30855,19 @@
       </c>
       <c r="T132" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000058号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000075号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="133" ht="42" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000021</t>
+          <t>RE-MLIT-08-00001443</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>有限会社高橋商事</t>
+          <t>マルカン商事有限会社</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -29904,12 +30937,12 @@
       </c>
       <c r="P133" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R133" s="2" t="inlineStr">
@@ -29924,19 +30957,19 @@
       </c>
       <c r="T133" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000021号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第001443号; 自動追加日: 2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="134" ht="42" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001345</t>
+          <t>RE-MLIT-08-00000204</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>株式会社中野商事</t>
+          <t>一般財団法人笠間市開発公社</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -30006,12 +31039,12 @@
       </c>
       <c r="P134" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R134" s="2" t="inlineStr">
@@ -30026,19 +31059,19 @@
       </c>
       <c r="T134" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001345号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000204号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="135" ht="42" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001306</t>
+          <t>RE-MLIT-08-00000014</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>株式会社新栄土地</t>
+          <t>下館土地株式会社</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -30108,12 +31141,12 @@
       </c>
       <c r="P135" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R135" s="2" t="inlineStr">
@@ -30128,19 +31161,19 @@
       </c>
       <c r="T135" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001306号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000014号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="136" ht="42" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001321</t>
+          <t>RE-MLIT-08-00000167</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>株式会社水戸地産</t>
+          <t>公益財団法人茨城県開発公社</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -30210,12 +31243,12 @@
       </c>
       <c r="P136" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R136" s="2" t="inlineStr">
@@ -30230,19 +31263,19 @@
       </c>
       <c r="T136" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001321号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000167号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="137" ht="42" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001262</t>
+          <t>RE-MLIT-08-00001278</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>株式会社赤尾杉</t>
+          <t>大みか不動産株式会社</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -30332,19 +31365,19 @@
       </c>
       <c r="T137" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001262号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第001278号; 自動追加日: 2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="138" ht="42" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000110</t>
+          <t>RE-MLIT-08-00000036</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>株式会社野口物産</t>
+          <t>平和不動産株式会社</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -30434,19 +31467,19 @@
       </c>
       <c r="T138" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000110号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000036号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="139" ht="42" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001434</t>
+          <t>RE-MLIT-08-00001437</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>池田林業株式会社</t>
+          <t>斉丸土地</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -30536,19 +31569,19 @@
       </c>
       <c r="T139" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001434号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第001437号; 自動追加日: 2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="140" ht="42" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001302</t>
+          <t>RE-MLIT-08-00000106</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>荒沢不動産</t>
+          <t>有限会社岩田不動産</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -30618,12 +31651,12 @@
       </c>
       <c r="P140" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R140" s="2" t="inlineStr">
@@ -30638,19 +31671,19 @@
       </c>
       <c r="T140" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001302号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000106号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="141" ht="42" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000109</t>
+          <t>RE-MLIT-08-00001391</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>関友商事株式会社</t>
+          <t>有限会社東栄</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -30720,12 +31753,12 @@
       </c>
       <c r="P141" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R141" s="2" t="inlineStr">
@@ -30740,308 +31773,1341 @@
       </c>
       <c r="T141" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000109号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第001391号; 自動追加日: 2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="142" ht="42" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>RE-MLIT-08-00000058</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>有限会社栄進</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P142" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q142" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R142" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S142" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T142" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000058号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="42" customHeight="1">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000021</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>有限会社高橋商事</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P143" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q143" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R143" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S143" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T143" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000021号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="42" customHeight="1">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001345</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>株式会社中野商事</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P144" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q144" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R144" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S144" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T144" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001345号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="42" customHeight="1">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001306</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>株式会社新栄土地</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P145" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q145" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R145" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S145" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T145" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001306号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="42" customHeight="1">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001321</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>株式会社水戸地産</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P146" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q146" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R146" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S146" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T146" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001321号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="42" customHeight="1">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001262</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>株式会社赤尾杉</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P147" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q147" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R147" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S147" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T147" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001262号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="42" customHeight="1">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000110</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>株式会社野口物産</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P148" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q148" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R148" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S148" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T148" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000110号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="42" customHeight="1">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001434</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>池田林業株式会社</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P149" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q149" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R149" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S149" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T149" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001434号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="42" customHeight="1">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00001302</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>荒沢不動産</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P150" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+        </is>
+      </c>
+      <c r="Q150" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="R150" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S150" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T150" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第001302号; 自動追加日: 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="42" customHeight="1">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>RE-MLIT-08-00000109</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>関友商事株式会社</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+        </is>
+      </c>
+      <c r="P151" s="3" t="inlineStr">
+        <is>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+        </is>
+      </c>
+      <c r="Q151" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="R151" s="2" t="inlineStr">
+        <is>
+          <t>公的登録確認・公式サイト要確認</t>
+        </is>
+      </c>
+      <c r="S151" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T151" s="2" t="inlineStr">
+        <is>
+          <t>免許行政庁: 茨城県; 免許番号: 第000109号; 自動追加日: 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="42" customHeight="1">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
           <t>RE-MLIT-08-00000203</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>関東鉄道株式会社</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
         <is>
           <t>関東</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="I142" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
         <is>
           <t>土地・事業用</t>
         </is>
       </c>
-      <c r="J142" s="2" t="inlineStr">
+      <c r="J152" s="2" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="K142" s="3" t="inlineStr">
+      <c r="K152" s="3" t="inlineStr">
         <is>
           <t>https://www.kantetsu.co.jp/realestate/</t>
         </is>
       </c>
-      <c r="L142" s="3" t="inlineStr">
+      <c r="L152" s="3" t="inlineStr">
         <is>
           <t>https://www.kantetsu.co.jp/contact</t>
         </is>
       </c>
-      <c r="M142" s="3" t="inlineStr">
+      <c r="M152" s="3" t="inlineStr">
         <is>
           <t>https://www.kantetsu.co.jp/realestate/</t>
         </is>
       </c>
-      <c r="N142" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="O142" s="2" t="inlineStr">
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
         <is>
           <t>公式サイトを自動確認。問い合わせ導線あり</t>
         </is>
       </c>
-      <c r="P142" s="3" t="inlineStr">
+      <c r="P152" s="3" t="inlineStr">
         <is>
           <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1 | https://www.kantetsu.co.jp/realestate/ | https://www.kantetsu.co.jp/contact</t>
         </is>
       </c>
-      <c r="Q142" s="2" t="inlineStr">
+      <c r="Q152" s="2" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="R142" s="2" t="inlineStr">
+      <c r="R152" s="2" t="inlineStr">
         <is>
           <t>自動確認済み</t>
         </is>
       </c>
-      <c r="S142" s="2" t="inlineStr">
+      <c r="S152" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="T142" s="2" t="inlineStr">
+      <c r="T152" s="2" t="inlineStr">
         <is>
           <t>免許行政庁: 茨城県; 免許番号: 第000203号; 自動追加日: 2026-07-23; 公式サイト自動確認日: 2026-07-25</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T142"/>
+  <autoFilter ref="A1:T152"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P45" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P50" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P52" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P53" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P54" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P55" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P56" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P57" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P58" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P59" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P60" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P61" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P62" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P63" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P64" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P65" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P66" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M67" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P67" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M68" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P68" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P69" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P70" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M71" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P71" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P72" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P73" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P74" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P75" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P76" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P77" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P78" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P79" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P80" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P81" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P82" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P83" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P84" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P85" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P86" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P87" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P88" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P89" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P90" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P91" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P92" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P93" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P94" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P95" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P96" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P97" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P98" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P99" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P100" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P101" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P102" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P103" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P104" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P105" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P106" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P107" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P108" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P109" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P110" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P111" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P112" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P113" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P114" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P115" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P116" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P117" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P118" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P119" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P120" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P121" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P122" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P123" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P124" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P125" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P126" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P127" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P128" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P129" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P130" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P131" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P132" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P133" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P134" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P135" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P136" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P137" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P138" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P139" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P140" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P141" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K142" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L142" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M142" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P45" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P50" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P52" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P53" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P54" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P55" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P56" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P57" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P58" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P59" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P60" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P61" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P62" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P63" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P64" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P65" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P66" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M67" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P67" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M68" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P68" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P69" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P70" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M71" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P71" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P72" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P73" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P74" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P75" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P76" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P77" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P78" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P79" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P80" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P81" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P82" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P83" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P84" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P85" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P86" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P87" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P88" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P89" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P90" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P91" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P92" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P93" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P94" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P95" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P96" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P97" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P98" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P99" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P100" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P101" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P102" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P103" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P104" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P105" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P106" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P107" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P108" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P109" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P110" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P111" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P112" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P113" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P114" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P115" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P116" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P117" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P118" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P119" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P120" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P121" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P122" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P123" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P124" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P125" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P126" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P127" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P128" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P129" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P130" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P131" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P132" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P133" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P134" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P135" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P136" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P137" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P138" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P139" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P140" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P141" r:id="rId188"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P142" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P143" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P144" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P145" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P146" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P147" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P148" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P149" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P150" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P151" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K152" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L152" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M152" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P152" r:id="rId202"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId190"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId203"/>
   </tableParts>
 </worksheet>
 </file>

--- a/database/real_estate_brokers.xlsx
+++ b/database/real_estate_brokers.xlsx
@@ -17,8 +17,8 @@
     <sheet name="データ辞書" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全社一覧'!$A$1:$T$171</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'関東'!$A$1:$T$162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全社一覧'!$A$1:$T$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'関東'!$A$1:$T$172</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'北海道・東北'!$A$1:$T$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'近畿'!$A$1:$T$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'中国・四国'!$A$1:$T$2</definedName>
@@ -177,8 +177,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_9e7587520fcb" displayName="T_9e7587520fcb" ref="A1:T171" headerRowCount="1">
-  <autoFilter ref="A1:T171"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_9e7587520fcb" displayName="T_9e7587520fcb" ref="A1:T181" headerRowCount="1">
+  <autoFilter ref="A1:T181"/>
   <tableColumns count="20">
     <tableColumn id="1" name="会社ID"/>
     <tableColumn id="2" name="会社名"/>
@@ -206,8 +206,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_92ae89f64a96" displayName="T_92ae89f64a96" ref="A1:T162" headerRowCount="1">
-  <autoFilter ref="A1:T162"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_92ae89f64a96" displayName="T_92ae89f64a96" ref="A1:T172" headerRowCount="1">
+  <autoFilter ref="A1:T172"/>
   <tableColumns count="20">
     <tableColumn id="1" name="会社ID"/>
     <tableColumn id="2" name="会社名"/>
@@ -668,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T171"/>
+  <dimension ref="A1:T181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12222,12 +12222,12 @@
     <row r="114" ht="42" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00001737</t>
+          <t>RE-MLIT-14-00002794</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>丸万不動産 有限会社</t>
+          <t>三宝商事 株式会社</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="P114" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=3&amp;pageListNo1=3&amp;pageListNo2=3</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R114" s="2" t="inlineStr">
@@ -12317,19 +12317,19 @@
       </c>
       <c r="T114" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第001737号; 自動追加日: 2026-07-27</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第002794号; 自動追加日: 2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="115" ht="42" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00001740</t>
+          <t>RE-MLIT-14-00002693</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>大和商事 株式会社</t>
+          <t>中央商事不動産</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -12399,12 +12399,12 @@
       </c>
       <c r="P115" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=3&amp;pageListNo1=3&amp;pageListNo2=3</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R115" s="2" t="inlineStr">
@@ -12419,19 +12419,19 @@
       </c>
       <c r="T115" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第001740号; 自動追加日: 2026-07-27</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第002693号; 自動追加日: 2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="116" ht="42" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000181</t>
+          <t>RE-MLIT-14-00001737</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>大栄興業 株式会社</t>
+          <t>丸万不動産 有限会社</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="P116" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R116" s="2" t="inlineStr">
@@ -12521,19 +12521,19 @@
       </c>
       <c r="T116" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000181号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001737号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="117" ht="42" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00001608</t>
+          <t>RE-MLIT-14-00001740</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>川崎北部開発 株式会社</t>
+          <t>大和商事 株式会社</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -12623,19 +12623,19 @@
       </c>
       <c r="T117" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第001608号; 自動追加日: 2026-07-27</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001740号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="118" ht="42" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000260</t>
+          <t>RE-MLIT-14-00000181</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>有限会社 協和商事</t>
+          <t>大栄興業 株式会社</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -12725,19 +12725,19 @@
       </c>
       <c r="T118" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000260号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000181号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="119" ht="42" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00001851</t>
+          <t>RE-MLIT-14-00001608</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>有限会社 吉浜不動産</t>
+          <t>川崎北部開発 株式会社</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -12827,19 +12827,19 @@
       </c>
       <c r="T119" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第001851号; 自動追加日: 2026-07-27</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001608号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="120" ht="42" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000365</t>
+          <t>RE-MLIT-14-00002826</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>有限会社 小沢建設商事</t>
+          <t>新見商事 有限会社</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -12909,12 +12909,12 @@
       </c>
       <c r="P120" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=3&amp;pageListNo1=3&amp;pageListNo2=3</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R120" s="2" t="inlineStr">
@@ -12929,19 +12929,19 @@
       </c>
       <c r="T120" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000365号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第002826号; 自動追加日: 2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="121" ht="42" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00001610</t>
+          <t>RE-MLIT-14-00002692</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>有限会社 柏菱</t>
+          <t>日比野不動産 株式会社</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -13011,12 +13011,12 @@
       </c>
       <c r="P121" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=3&amp;pageListNo1=3&amp;pageListNo2=3</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R121" s="2" t="inlineStr">
@@ -13031,19 +13031,19 @@
       </c>
       <c r="T121" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第001610号; 自動追加日: 2026-07-27</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第002692号; 自動追加日: 2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="122" ht="42" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000162</t>
+          <t>RE-MLIT-14-00000260</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>有限会社 濱屋</t>
+          <t>有限会社 協和商事</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -13133,19 +13133,19 @@
       </c>
       <c r="T122" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000162号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000260号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="123" ht="42" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00001724</t>
+          <t>RE-MLIT-14-00001851</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>末広土地建物 株式会社</t>
+          <t>有限会社 吉浜不動産</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -13235,19 +13235,19 @@
       </c>
       <c r="T123" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第001724号; 自動追加日: 2026-07-27</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001851号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="124" ht="42" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000071</t>
+          <t>RE-MLIT-14-00002784</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>東栄商事 株式会社</t>
+          <t>有限会社 大倉商事</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="P124" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=3&amp;pageListNo1=3&amp;pageListNo2=3</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R124" s="2" t="inlineStr">
@@ -13337,19 +13337,19 @@
       </c>
       <c r="T124" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000071号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第002784号; 自動追加日: 2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="125" ht="42" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000060</t>
+          <t>RE-MLIT-14-00000365</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>東横不動産 株式会社</t>
+          <t>有限会社 小沢建設商事</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -13439,19 +13439,19 @@
       </c>
       <c r="T125" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000365号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="126" ht="42" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000013</t>
+          <t>RE-MLIT-14-00002699</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>株式会社 大谷商事</t>
+          <t>有限会社 平不動産</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -13521,12 +13521,12 @@
       </c>
       <c r="P126" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=3&amp;pageListNo1=3&amp;pageListNo2=3</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R126" s="2" t="inlineStr">
@@ -13541,19 +13541,19 @@
       </c>
       <c r="T126" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000013号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第002699号; 自動追加日: 2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="127" ht="42" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00001771</t>
+          <t>RE-MLIT-14-00001610</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>株式会社 日建</t>
+          <t>有限会社 柏菱</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -13643,19 +13643,19 @@
       </c>
       <c r="T127" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第001771号; 自動追加日: 2026-07-27</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001610号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="128" ht="42" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000024</t>
+          <t>RE-MLIT-14-00000162</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>浅間建設 株式会社</t>
+          <t>有限会社 濱屋</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -13745,19 +13745,19 @@
       </c>
       <c r="T128" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000024号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000162号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="129" ht="42" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000066</t>
+          <t>RE-MLIT-14-00001724</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>相澤土地 株式会社</t>
+          <t>末広土地建物 株式会社</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -13827,12 +13827,12 @@
       </c>
       <c r="P129" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R129" s="2" t="inlineStr">
@@ -13847,19 +13847,19 @@
       </c>
       <c r="T129" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000066号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001724号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="130" ht="42" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00001880</t>
+          <t>RE-MLIT-14-00000071</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>第一商事 株式会社</t>
+          <t>東栄商事 株式会社</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -13929,12 +13929,12 @@
       </c>
       <c r="P130" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R130" s="2" t="inlineStr">
@@ -13949,19 +13949,19 @@
       </c>
       <c r="T130" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第001880号; 自動追加日: 2026-07-27</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000071号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="131" ht="42" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-14-00000198</t>
+          <t>RE-MLIT-14-00000060</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>親和商事 有限会社</t>
+          <t>東横不動産 株式会社</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -14051,19 +14051,19 @@
       </c>
       <c r="T131" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 神奈川県; 免許番号: 第000198号; 自動追加日: 2026-07-21</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000060号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="132" ht="42" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000114</t>
+          <t>RE-MLIT-14-00002679</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>上信電鉄株式会社</t>
+          <t>株式会社 トーソー</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -14073,7 +14073,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -14083,7 +14083,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -14133,12 +14133,12 @@
       </c>
       <c r="P132" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=3&amp;pageListNo1=3&amp;pageListNo2=3</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R132" s="2" t="inlineStr">
@@ -14153,19 +14153,19 @@
       </c>
       <c r="T132" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000114号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第002679号; 自動追加日: 2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="133" ht="42" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00001246</t>
+          <t>RE-MLIT-14-00000013</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>五料不動産</t>
+          <t>株式会社 大谷商事</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -14175,7 +14175,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -14185,7 +14185,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -14235,12 +14235,12 @@
       </c>
       <c r="P133" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R133" s="2" t="inlineStr">
@@ -14255,19 +14255,19 @@
       </c>
       <c r="T133" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第001246号; 自動追加日: 2026-08-01</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000013号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="134" ht="42" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00001228</t>
+          <t>RE-MLIT-14-00002788</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>吾妻開発株式会社</t>
+          <t>株式会社 小川組</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -14277,7 +14277,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -14287,7 +14287,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="P134" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=3&amp;pageListNo1=3&amp;pageListNo2=3</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R134" s="2" t="inlineStr">
@@ -14357,19 +14357,19 @@
       </c>
       <c r="T134" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第001228号; 自動追加日: 2026-08-01</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第002788号; 自動追加日: 2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="135" ht="42" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00001285</t>
+          <t>RE-MLIT-14-00002701</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>大誠不動産商事有限会社</t>
+          <t>株式会社 嶋崎不動産</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -14379,7 +14379,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -14389,7 +14389,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -14439,12 +14439,12 @@
       </c>
       <c r="P135" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=3&amp;pageListNo1=3&amp;pageListNo2=3</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R135" s="2" t="inlineStr">
@@ -14459,19 +14459,19 @@
       </c>
       <c r="T135" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第001285号; 自動追加日: 2026-08-01</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第002701号; 自動追加日: 2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="136" ht="42" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000292</t>
+          <t>RE-MLIT-14-00001771</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>小林工業株式会社</t>
+          <t>株式会社 日建</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -14481,7 +14481,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -14491,7 +14491,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -14541,12 +14541,12 @@
       </c>
       <c r="P136" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R136" s="2" t="inlineStr">
@@ -14561,19 +14561,19 @@
       </c>
       <c r="T136" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000292号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001771号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="137" ht="42" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00001354</t>
+          <t>RE-MLIT-14-00002811</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>小此木不動産建設有限会社</t>
+          <t>沢野商亊 株式会社</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -14593,7 +14593,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -14643,12 +14643,12 @@
       </c>
       <c r="P137" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=3&amp;pageListNo1=3&amp;pageListNo2=3</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="R137" s="2" t="inlineStr">
@@ -14663,19 +14663,19 @@
       </c>
       <c r="T137" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第001354号; 自動追加日: 2026-08-01</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第002811号; 自動追加日: 2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="138" ht="42" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00001234</t>
+          <t>RE-MLIT-14-00000024</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>小野里工業株式会社</t>
+          <t>浅間建設 株式会社</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -14745,12 +14745,12 @@
       </c>
       <c r="P138" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R138" s="2" t="inlineStr">
@@ -14765,19 +14765,19 @@
       </c>
       <c r="T138" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第001234号; 自動追加日: 2026-08-01</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000024号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="139" ht="42" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00001334</t>
+          <t>RE-MLIT-14-00000066</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>日聖産業株式会社</t>
+          <t>相澤土地 株式会社</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -14787,7 +14787,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -14797,7 +14797,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -14847,12 +14847,12 @@
       </c>
       <c r="P139" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R139" s="2" t="inlineStr">
@@ -14867,19 +14867,19 @@
       </c>
       <c r="T139" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第001334号; 自動追加日: 2026-08-01</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000066号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="140" ht="42" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000146</t>
+          <t>RE-MLIT-14-00001880</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>有限会社前橋不動産</t>
+          <t>第一商事 株式会社</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -14889,7 +14889,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -14899,7 +14899,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -14949,12 +14949,12 @@
       </c>
       <c r="P140" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R140" s="2" t="inlineStr">
@@ -14969,19 +14969,19 @@
       </c>
       <c r="T140" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000146号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第001880号; 自動追加日: 2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="141" ht="42" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00001358</t>
+          <t>RE-MLIT-14-00000198</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>有限会社吾妻不動産</t>
+          <t>親和商事 有限会社</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -15001,7 +15001,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -15051,12 +15051,12 @@
       </c>
       <c r="P141" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=14&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="R141" s="2" t="inlineStr">
@@ -15071,19 +15071,19 @@
       </c>
       <c r="T141" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第001358号; 自動追加日: 2026-08-01</t>
+          <t>免許行政庁: 神奈川県; 免許番号: 第000198号; 自動追加日: 2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="142" ht="42" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000098</t>
+          <t>RE-MLIT-10-00000114</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>有限会社田口不動産</t>
+          <t>上信電鉄株式会社</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -15173,19 +15173,19 @@
       </c>
       <c r="T142" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000098号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000114号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="143" ht="42" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000302</t>
+          <t>RE-MLIT-10-00001246</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>朝日開発興業株式会社</t>
+          <t>五料不動産</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -15255,12 +15255,12 @@
       </c>
       <c r="P143" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R143" s="2" t="inlineStr">
@@ -15275,19 +15275,19 @@
       </c>
       <c r="T143" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000302号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001246号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="144" ht="42" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000257</t>
+          <t>RE-MLIT-10-00001228</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>東神不動産株式会社</t>
+          <t>吾妻開発株式会社</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -15357,12 +15357,12 @@
       </c>
       <c r="P144" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R144" s="2" t="inlineStr">
@@ -15377,19 +15377,19 @@
       </c>
       <c r="T144" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000257号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001228号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="145" ht="42" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000038</t>
+          <t>RE-MLIT-10-00001285</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>株式会社ティーエムエフ</t>
+          <t>大誠不動産商事有限会社</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -15459,12 +15459,12 @@
       </c>
       <c r="P145" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R145" s="2" t="inlineStr">
@@ -15479,19 +15479,19 @@
       </c>
       <c r="T145" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000038号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001285号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="146" ht="42" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00001331</t>
+          <t>RE-MLIT-10-00000292</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>株式会社黒沢商事</t>
+          <t>小林工業株式会社</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -15561,12 +15561,12 @@
       </c>
       <c r="P146" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R146" s="2" t="inlineStr">
@@ -15581,19 +15581,19 @@
       </c>
       <c r="T146" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第001331号; 自動追加日: 2026-08-01</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000292号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="147" ht="42" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00001355</t>
+          <t>RE-MLIT-10-00001354</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>橋本商事株式会社</t>
+          <t>小此木不動産建設有限会社</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -15683,19 +15683,19 @@
       </c>
       <c r="T147" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第001355号; 自動追加日: 2026-08-01</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001354号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="148" ht="42" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000230</t>
+          <t>RE-MLIT-10-00001234</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>石橋建設工業株式会社 ※</t>
+          <t>小野里工業株式会社</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -15765,12 +15765,12 @@
       </c>
       <c r="P148" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R148" s="2" t="inlineStr">
@@ -15785,19 +15785,19 @@
       </c>
       <c r="T148" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000230号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001234号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="149" ht="42" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000227</t>
+          <t>RE-MLIT-10-00001334</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>群馬不動産株式会社 ※</t>
+          <t>日聖産業株式会社</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -15867,12 +15867,12 @@
       </c>
       <c r="P149" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R149" s="2" t="inlineStr">
@@ -15887,19 +15887,19 @@
       </c>
       <c r="T149" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000227号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001334号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="150" ht="42" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00001324</t>
+          <t>RE-MLIT-10-00000146</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>高前産業株式会社</t>
+          <t>有限会社前橋不動産</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -15969,12 +15969,12 @@
       </c>
       <c r="P150" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R150" s="2" t="inlineStr">
@@ -15989,19 +15989,19 @@
       </c>
       <c r="T150" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第001324号; 自動追加日: 2026-08-01</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000146号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="151" ht="42" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-10-00000075</t>
+          <t>RE-MLIT-10-00001358</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>鵜川興業株式会社</t>
+          <t>有限会社吾妻不動産</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -16071,12 +16071,12 @@
       </c>
       <c r="P151" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q151" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R151" s="2" t="inlineStr">
@@ -16091,19 +16091,19 @@
       </c>
       <c r="T151" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 群馬県; 免許番号: 第000075号; 自動追加日: 2026-07-25</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001358号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="152" ht="42" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001443</t>
+          <t>RE-MLIT-10-00000098</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>マルカン商事有限会社</t>
+          <t>有限会社田口不動産</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -16123,7 +16123,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -16173,12 +16173,12 @@
       </c>
       <c r="P152" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R152" s="2" t="inlineStr">
@@ -16193,19 +16193,19 @@
       </c>
       <c r="T152" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001443号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000098号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="153" ht="42" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000204</t>
+          <t>RE-MLIT-10-00000302</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>一般財団法人笠間市開発公社</t>
+          <t>朝日開発興業株式会社</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -16225,7 +16225,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="P153" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R153" s="2" t="inlineStr">
@@ -16295,19 +16295,19 @@
       </c>
       <c r="T153" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000204号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000302号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="154" ht="42" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000014</t>
+          <t>RE-MLIT-10-00000257</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>下館土地株式会社</t>
+          <t>東神不動産株式会社</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -16317,7 +16317,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -16327,7 +16327,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -16377,12 +16377,12 @@
       </c>
       <c r="P154" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R154" s="2" t="inlineStr">
@@ -16397,19 +16397,19 @@
       </c>
       <c r="T154" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000014号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000257号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="155" ht="42" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000167</t>
+          <t>RE-MLIT-10-00000038</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>公益財団法人茨城県開発公社</t>
+          <t>株式会社ティーエムエフ</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -16429,7 +16429,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -16479,12 +16479,12 @@
       </c>
       <c r="P155" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R155" s="2" t="inlineStr">
@@ -16499,19 +16499,19 @@
       </c>
       <c r="T155" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000167号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000038号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="156" ht="42" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001278</t>
+          <t>RE-MLIT-10-00001331</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>大みか不動産株式会社</t>
+          <t>株式会社黒沢商事</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -16521,7 +16521,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -16546,52 +16546,52 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>マンション・土地・賃貸管理</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K156" s="3" t="inlineStr">
-        <is>
-          <t>https://omika.jp/company/</t>
-        </is>
-      </c>
-      <c r="L156" s="3" t="inlineStr">
-        <is>
-          <t>https://ouchi-hitachi.com/</t>
-        </is>
-      </c>
-      <c r="M156" s="3" t="inlineStr">
-        <is>
-          <t>https://omika.jp/company/</t>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
         <is>
-          <t>0294-53-5878</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
-          <t>公式サイトを自動確認。問い合わせ導線あり</t>
+          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
         </is>
       </c>
       <c r="P156" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2 | https://omika.jp/company/ | https://ouchi-hitachi.com/</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R156" s="2" t="inlineStr">
         <is>
-          <t>自動確認済み</t>
+          <t>公的登録確認・公式サイト要確認</t>
         </is>
       </c>
       <c r="S156" s="2" t="inlineStr">
@@ -16601,19 +16601,19 @@
       </c>
       <c r="T156" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001278号; 自動追加日: 2026-07-30; 公式サイト自動確認日: 2026-08-02</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001331号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="157" ht="42" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000036</t>
+          <t>RE-MLIT-10-00001355</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>平和不動産株式会社</t>
+          <t>橋本商事株式会社</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -16623,7 +16623,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -16633,7 +16633,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -16683,12 +16683,12 @@
       </c>
       <c r="P157" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R157" s="2" t="inlineStr">
@@ -16703,19 +16703,19 @@
       </c>
       <c r="T157" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000036号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001355号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="158" ht="42" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001437</t>
+          <t>RE-MLIT-10-00000230</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>斉丸土地</t>
+          <t>石橋建設工業株式会社 ※</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -16725,7 +16725,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -16735,7 +16735,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="P158" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R158" s="2" t="inlineStr">
@@ -16805,19 +16805,19 @@
       </c>
       <c r="T158" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001437号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000230号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="159" ht="42" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000106</t>
+          <t>RE-MLIT-10-00000227</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>有限会社岩田不動産</t>
+          <t>群馬不動産株式会社 ※</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -16827,7 +16827,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -16837,7 +16837,7 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -16887,12 +16887,12 @@
       </c>
       <c r="P159" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R159" s="2" t="inlineStr">
@@ -16907,19 +16907,19 @@
       </c>
       <c r="T159" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000106号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000227号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="160" ht="42" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001391</t>
+          <t>RE-MLIT-10-00001324</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>有限会社東栄</t>
+          <t>高前産業株式会社</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -16929,7 +16929,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -16939,7 +16939,7 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
@@ -16989,12 +16989,12 @@
       </c>
       <c r="P160" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R160" s="2" t="inlineStr">
@@ -17009,19 +17009,19 @@
       </c>
       <c r="T160" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001391号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第001324号; 自動追加日: 2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="161" ht="42" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000058</t>
+          <t>RE-MLIT-10-00000075</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>有限会社栄進</t>
+          <t>鵜川興業株式会社</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -17031,7 +17031,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -17041,7 +17041,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -17091,12 +17091,12 @@
       </c>
       <c r="P161" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=10&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="R161" s="2" t="inlineStr">
@@ -17111,19 +17111,19 @@
       </c>
       <c r="T161" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000058号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 群馬県; 免許番号: 第000075号; 自動追加日: 2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="162" ht="42" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000021</t>
+          <t>RE-MLIT-08-00001443</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>有限会社高橋商事</t>
+          <t>マルカン商事有限会社</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -17193,12 +17193,12 @@
       </c>
       <c r="P162" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R162" s="2" t="inlineStr">
@@ -17213,19 +17213,19 @@
       </c>
       <c r="T162" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000021号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第001443号; 自動追加日: 2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="163" ht="42" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001345</t>
+          <t>RE-MLIT-08-00000204</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>株式会社中野商事</t>
+          <t>一般財団法人笠間市開発公社</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -17295,12 +17295,12 @@
       </c>
       <c r="P163" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q163" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R163" s="2" t="inlineStr">
@@ -17315,19 +17315,19 @@
       </c>
       <c r="T163" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001345号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000204号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="164" ht="42" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001306</t>
+          <t>RE-MLIT-08-00000014</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>株式会社新栄土地</t>
+          <t>下館土地株式会社</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -17397,12 +17397,12 @@
       </c>
       <c r="P164" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q164" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R164" s="2" t="inlineStr">
@@ -17417,19 +17417,19 @@
       </c>
       <c r="T164" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001306号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000014号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="165" ht="42" customHeight="1">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001321</t>
+          <t>RE-MLIT-08-00000167</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>株式会社水戸地産</t>
+          <t>公益財団法人茨城県開発公社</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -17499,12 +17499,12 @@
       </c>
       <c r="P165" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=1&amp;pageListNo2=1</t>
         </is>
       </c>
       <c r="Q165" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R165" s="2" t="inlineStr">
@@ -17519,19 +17519,19 @@
       </c>
       <c r="T165" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001321号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000167号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="166" ht="42" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001262</t>
+          <t>RE-MLIT-08-00001278</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>株式会社赤尾杉</t>
+          <t>大みか不動産株式会社</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -17566,52 +17566,52 @@
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>マンション・土地・賃貸管理</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K166" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="L166" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M166" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="K166" s="3" t="inlineStr">
+        <is>
+          <t>https://omika.jp/company/</t>
+        </is>
+      </c>
+      <c r="L166" s="3" t="inlineStr">
+        <is>
+          <t>https://ouchi-hitachi.com/</t>
+        </is>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>https://omika.jp/company/</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>0294-53-5878</t>
         </is>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
-          <t>国土交通省の企業情報検索システムで宅地建物取引業者登録を確認</t>
+          <t>公式サイトを自動確認。問い合わせ導線あり</t>
         </is>
       </c>
       <c r="P166" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2 | https://omika.jp/company/ | https://ouchi-hitachi.com/</t>
         </is>
       </c>
       <c r="Q166" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="R166" s="2" t="inlineStr">
         <is>
-          <t>公的登録確認・公式サイト要確認</t>
+          <t>自動確認済み</t>
         </is>
       </c>
       <c r="S166" s="2" t="inlineStr">
@@ -17621,19 +17621,19 @@
       </c>
       <c r="T166" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001262号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第001278号; 自動追加日: 2026-07-30; 公式サイト自動確認日: 2026-08-02</t>
         </is>
       </c>
     </row>
     <row r="167" ht="42" customHeight="1">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00000110</t>
+          <t>RE-MLIT-08-00000036</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>株式会社野口物産</t>
+          <t>平和不動産株式会社</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -17723,19 +17723,19 @@
       </c>
       <c r="T167" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第000110号; 自動追加日: 2026-07-23</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第000036号; 自動追加日: 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="168" ht="42" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001434</t>
+          <t>RE-MLIT-08-00001437</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>池田林業株式会社</t>
+          <t>斉丸土地</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -17825,19 +17825,19 @@
       </c>
       <c r="T168" s="2" t="inlineStr">
         <is>
-          <t>免許行政庁: 茨城県; 免許番号: 第001434号; 自動追加日: 2026-07-30</t>
+          <t>免許行政庁: 茨城県; 免許番号: 第001437号; 自動追加日: 2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="169" ht="42" customHeight="1">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>RE-MLIT-08-00001302</t>
+          <t>RE-MLIT-08-00000106</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>荒沢不動産</t>
+          <t>有限会社岩田不動産</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -17907,12 +17907,12 @@
       </c>
       <c r="P169" s="3" t="inlineStr">
         <is>
-          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=2&amp;pageListNo1=2&amp;pageListNo2=2</t>
+          <t>https://etsuran2.mlit.go.jp/TAKKEN/takkenKensaku.do?CMD=selectPage&amp;caller=TK&amp;choice=1&amp;rdoSelect=1&amp;rdoSelectJoken=1&amp;rdoSelectSort=1&amp;sortValue=1&amp;dispCount=50&amp;licenseNoKbn=08&amp;pageCount=1&amp;pageListNo1=